--- a/data/input/contract_history.xlsx
+++ b/data/input/contract_history.xlsx
@@ -8,15 +8,25 @@
   </bookViews>
   <sheets>
     <sheet name="成約履歴" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="入力例" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="項目説明" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'成約履歴'!$A$1:$T$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'入力例'!$A$1:$T$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'項目説明'!$A$1:$D$21</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;円&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -30,7 +40,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +50,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,11 +75,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,25 +456,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:T1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -462,67 +497,7226 @@
           <t>district_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>station_name</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>station_line</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>station_latitude</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>station_longitude</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>area_m2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>floor_plan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>building_age</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>structure</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>renovation</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>use</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>city_planning</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>coverage_ratio</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>floor_area_ratio</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>listing_date</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>asking_price</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>contract_date</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>contract_price</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="H2" s="4" t="n"/>
+      <c r="Q2" s="5" t="n"/>
+      <c r="R2" s="6" t="n"/>
+      <c r="S2" s="5" t="n"/>
+      <c r="T2" s="6" t="n"/>
+    </row>
+    <row r="3">
+      <c r="H3" s="4" t="n"/>
+      <c r="Q3" s="5" t="n"/>
+      <c r="R3" s="6" t="n"/>
+      <c r="S3" s="5" t="n"/>
+      <c r="T3" s="6" t="n"/>
+    </row>
+    <row r="4">
+      <c r="H4" s="4" t="n"/>
+      <c r="Q4" s="5" t="n"/>
+      <c r="R4" s="6" t="n"/>
+      <c r="S4" s="5" t="n"/>
+      <c r="T4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="H5" s="4" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="6" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="H6" s="4" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="H7" s="4" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="H8" s="4" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="H9" s="4" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="H10" s="4" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="6" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="H11" s="4" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="6" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="H12" s="4" t="n"/>
+      <c r="Q12" s="5" t="n"/>
+      <c r="R12" s="6" t="n"/>
+      <c r="S12" s="5" t="n"/>
+      <c r="T12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="H13" s="4" t="n"/>
+      <c r="Q13" s="5" t="n"/>
+      <c r="R13" s="6" t="n"/>
+      <c r="S13" s="5" t="n"/>
+      <c r="T13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="H14" s="4" t="n"/>
+      <c r="Q14" s="5" t="n"/>
+      <c r="R14" s="6" t="n"/>
+      <c r="S14" s="5" t="n"/>
+      <c r="T14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="H15" s="4" t="n"/>
+      <c r="Q15" s="5" t="n"/>
+      <c r="R15" s="6" t="n"/>
+      <c r="S15" s="5" t="n"/>
+      <c r="T15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="H16" s="4" t="n"/>
+      <c r="Q16" s="5" t="n"/>
+      <c r="R16" s="6" t="n"/>
+      <c r="S16" s="5" t="n"/>
+      <c r="T16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="H17" s="4" t="n"/>
+      <c r="Q17" s="5" t="n"/>
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="5" t="n"/>
+      <c r="T17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="H18" s="4" t="n"/>
+      <c r="Q18" s="5" t="n"/>
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="5" t="n"/>
+      <c r="T18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="H19" s="4" t="n"/>
+      <c r="Q19" s="5" t="n"/>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="5" t="n"/>
+      <c r="T19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="H20" s="4" t="n"/>
+      <c r="Q20" s="5" t="n"/>
+      <c r="R20" s="6" t="n"/>
+      <c r="S20" s="5" t="n"/>
+      <c r="T20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="H21" s="4" t="n"/>
+      <c r="Q21" s="5" t="n"/>
+      <c r="R21" s="6" t="n"/>
+      <c r="S21" s="5" t="n"/>
+      <c r="T21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="H22" s="4" t="n"/>
+      <c r="Q22" s="5" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="5" t="n"/>
+      <c r="T22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="H23" s="4" t="n"/>
+      <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="6" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="H24" s="4" t="n"/>
+      <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="6" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="H25" s="4" t="n"/>
+      <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="6" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="H26" s="4" t="n"/>
+      <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="6" t="n"/>
+      <c r="S26" s="5" t="n"/>
+      <c r="T26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="H27" s="4" t="n"/>
+      <c r="Q27" s="5" t="n"/>
+      <c r="R27" s="6" t="n"/>
+      <c r="S27" s="5" t="n"/>
+      <c r="T27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="H28" s="4" t="n"/>
+      <c r="Q28" s="5" t="n"/>
+      <c r="R28" s="6" t="n"/>
+      <c r="S28" s="5" t="n"/>
+      <c r="T28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="H29" s="4" t="n"/>
+      <c r="Q29" s="5" t="n"/>
+      <c r="R29" s="6" t="n"/>
+      <c r="S29" s="5" t="n"/>
+      <c r="T29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="H30" s="4" t="n"/>
+      <c r="Q30" s="5" t="n"/>
+      <c r="R30" s="6" t="n"/>
+      <c r="S30" s="5" t="n"/>
+      <c r="T30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="H31" s="4" t="n"/>
+      <c r="Q31" s="5" t="n"/>
+      <c r="R31" s="6" t="n"/>
+      <c r="S31" s="5" t="n"/>
+      <c r="T31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="H32" s="4" t="n"/>
+      <c r="Q32" s="5" t="n"/>
+      <c r="R32" s="6" t="n"/>
+      <c r="S32" s="5" t="n"/>
+      <c r="T32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="H33" s="4" t="n"/>
+      <c r="Q33" s="5" t="n"/>
+      <c r="R33" s="6" t="n"/>
+      <c r="S33" s="5" t="n"/>
+      <c r="T33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="H34" s="4" t="n"/>
+      <c r="Q34" s="5" t="n"/>
+      <c r="R34" s="6" t="n"/>
+      <c r="S34" s="5" t="n"/>
+      <c r="T34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="H35" s="4" t="n"/>
+      <c r="Q35" s="5" t="n"/>
+      <c r="R35" s="6" t="n"/>
+      <c r="S35" s="5" t="n"/>
+      <c r="T35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="H36" s="4" t="n"/>
+      <c r="Q36" s="5" t="n"/>
+      <c r="R36" s="6" t="n"/>
+      <c r="S36" s="5" t="n"/>
+      <c r="T36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="H37" s="4" t="n"/>
+      <c r="Q37" s="5" t="n"/>
+      <c r="R37" s="6" t="n"/>
+      <c r="S37" s="5" t="n"/>
+      <c r="T37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="H38" s="4" t="n"/>
+      <c r="Q38" s="5" t="n"/>
+      <c r="R38" s="6" t="n"/>
+      <c r="S38" s="5" t="n"/>
+      <c r="T38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="H39" s="4" t="n"/>
+      <c r="Q39" s="5" t="n"/>
+      <c r="R39" s="6" t="n"/>
+      <c r="S39" s="5" t="n"/>
+      <c r="T39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="H40" s="4" t="n"/>
+      <c r="Q40" s="5" t="n"/>
+      <c r="R40" s="6" t="n"/>
+      <c r="S40" s="5" t="n"/>
+      <c r="T40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="H41" s="4" t="n"/>
+      <c r="Q41" s="5" t="n"/>
+      <c r="R41" s="6" t="n"/>
+      <c r="S41" s="5" t="n"/>
+      <c r="T41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="H42" s="4" t="n"/>
+      <c r="Q42" s="5" t="n"/>
+      <c r="R42" s="6" t="n"/>
+      <c r="S42" s="5" t="n"/>
+      <c r="T42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="H43" s="4" t="n"/>
+      <c r="Q43" s="5" t="n"/>
+      <c r="R43" s="6" t="n"/>
+      <c r="S43" s="5" t="n"/>
+      <c r="T43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="H44" s="4" t="n"/>
+      <c r="Q44" s="5" t="n"/>
+      <c r="R44" s="6" t="n"/>
+      <c r="S44" s="5" t="n"/>
+      <c r="T44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="H45" s="4" t="n"/>
+      <c r="Q45" s="5" t="n"/>
+      <c r="R45" s="6" t="n"/>
+      <c r="S45" s="5" t="n"/>
+      <c r="T45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="H46" s="4" t="n"/>
+      <c r="Q46" s="5" t="n"/>
+      <c r="R46" s="6" t="n"/>
+      <c r="S46" s="5" t="n"/>
+      <c r="T46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="H47" s="4" t="n"/>
+      <c r="Q47" s="5" t="n"/>
+      <c r="R47" s="6" t="n"/>
+      <c r="S47" s="5" t="n"/>
+      <c r="T47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="H48" s="4" t="n"/>
+      <c r="Q48" s="5" t="n"/>
+      <c r="R48" s="6" t="n"/>
+      <c r="S48" s="5" t="n"/>
+      <c r="T48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="H49" s="4" t="n"/>
+      <c r="Q49" s="5" t="n"/>
+      <c r="R49" s="6" t="n"/>
+      <c r="S49" s="5" t="n"/>
+      <c r="T49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="H50" s="4" t="n"/>
+      <c r="Q50" s="5" t="n"/>
+      <c r="R50" s="6" t="n"/>
+      <c r="S50" s="5" t="n"/>
+      <c r="T50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="H51" s="4" t="n"/>
+      <c r="Q51" s="5" t="n"/>
+      <c r="R51" s="6" t="n"/>
+      <c r="S51" s="5" t="n"/>
+      <c r="T51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="H52" s="4" t="n"/>
+      <c r="Q52" s="5" t="n"/>
+      <c r="R52" s="6" t="n"/>
+      <c r="S52" s="5" t="n"/>
+      <c r="T52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="H53" s="4" t="n"/>
+      <c r="Q53" s="5" t="n"/>
+      <c r="R53" s="6" t="n"/>
+      <c r="S53" s="5" t="n"/>
+      <c r="T53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="H54" s="4" t="n"/>
+      <c r="Q54" s="5" t="n"/>
+      <c r="R54" s="6" t="n"/>
+      <c r="S54" s="5" t="n"/>
+      <c r="T54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="H55" s="4" t="n"/>
+      <c r="Q55" s="5" t="n"/>
+      <c r="R55" s="6" t="n"/>
+      <c r="S55" s="5" t="n"/>
+      <c r="T55" s="6" t="n"/>
+    </row>
+    <row r="56">
+      <c r="H56" s="4" t="n"/>
+      <c r="Q56" s="5" t="n"/>
+      <c r="R56" s="6" t="n"/>
+      <c r="S56" s="5" t="n"/>
+      <c r="T56" s="6" t="n"/>
+    </row>
+    <row r="57">
+      <c r="H57" s="4" t="n"/>
+      <c r="Q57" s="5" t="n"/>
+      <c r="R57" s="6" t="n"/>
+      <c r="S57" s="5" t="n"/>
+      <c r="T57" s="6" t="n"/>
+    </row>
+    <row r="58">
+      <c r="H58" s="4" t="n"/>
+      <c r="Q58" s="5" t="n"/>
+      <c r="R58" s="6" t="n"/>
+      <c r="S58" s="5" t="n"/>
+      <c r="T58" s="6" t="n"/>
+    </row>
+    <row r="59">
+      <c r="H59" s="4" t="n"/>
+      <c r="Q59" s="5" t="n"/>
+      <c r="R59" s="6" t="n"/>
+      <c r="S59" s="5" t="n"/>
+      <c r="T59" s="6" t="n"/>
+    </row>
+    <row r="60">
+      <c r="H60" s="4" t="n"/>
+      <c r="Q60" s="5" t="n"/>
+      <c r="R60" s="6" t="n"/>
+      <c r="S60" s="5" t="n"/>
+      <c r="T60" s="6" t="n"/>
+    </row>
+    <row r="61">
+      <c r="H61" s="4" t="n"/>
+      <c r="Q61" s="5" t="n"/>
+      <c r="R61" s="6" t="n"/>
+      <c r="S61" s="5" t="n"/>
+      <c r="T61" s="6" t="n"/>
+    </row>
+    <row r="62">
+      <c r="H62" s="4" t="n"/>
+      <c r="Q62" s="5" t="n"/>
+      <c r="R62" s="6" t="n"/>
+      <c r="S62" s="5" t="n"/>
+      <c r="T62" s="6" t="n"/>
+    </row>
+    <row r="63">
+      <c r="H63" s="4" t="n"/>
+      <c r="Q63" s="5" t="n"/>
+      <c r="R63" s="6" t="n"/>
+      <c r="S63" s="5" t="n"/>
+      <c r="T63" s="6" t="n"/>
+    </row>
+    <row r="64">
+      <c r="H64" s="4" t="n"/>
+      <c r="Q64" s="5" t="n"/>
+      <c r="R64" s="6" t="n"/>
+      <c r="S64" s="5" t="n"/>
+      <c r="T64" s="6" t="n"/>
+    </row>
+    <row r="65">
+      <c r="H65" s="4" t="n"/>
+      <c r="Q65" s="5" t="n"/>
+      <c r="R65" s="6" t="n"/>
+      <c r="S65" s="5" t="n"/>
+      <c r="T65" s="6" t="n"/>
+    </row>
+    <row r="66">
+      <c r="H66" s="4" t="n"/>
+      <c r="Q66" s="5" t="n"/>
+      <c r="R66" s="6" t="n"/>
+      <c r="S66" s="5" t="n"/>
+      <c r="T66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="H67" s="4" t="n"/>
+      <c r="Q67" s="5" t="n"/>
+      <c r="R67" s="6" t="n"/>
+      <c r="S67" s="5" t="n"/>
+      <c r="T67" s="6" t="n"/>
+    </row>
+    <row r="68">
+      <c r="H68" s="4" t="n"/>
+      <c r="Q68" s="5" t="n"/>
+      <c r="R68" s="6" t="n"/>
+      <c r="S68" s="5" t="n"/>
+      <c r="T68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="H69" s="4" t="n"/>
+      <c r="Q69" s="5" t="n"/>
+      <c r="R69" s="6" t="n"/>
+      <c r="S69" s="5" t="n"/>
+      <c r="T69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="H70" s="4" t="n"/>
+      <c r="Q70" s="5" t="n"/>
+      <c r="R70" s="6" t="n"/>
+      <c r="S70" s="5" t="n"/>
+      <c r="T70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="H71" s="4" t="n"/>
+      <c r="Q71" s="5" t="n"/>
+      <c r="R71" s="6" t="n"/>
+      <c r="S71" s="5" t="n"/>
+      <c r="T71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="H72" s="4" t="n"/>
+      <c r="Q72" s="5" t="n"/>
+      <c r="R72" s="6" t="n"/>
+      <c r="S72" s="5" t="n"/>
+      <c r="T72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="H73" s="4" t="n"/>
+      <c r="Q73" s="5" t="n"/>
+      <c r="R73" s="6" t="n"/>
+      <c r="S73" s="5" t="n"/>
+      <c r="T73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="H74" s="4" t="n"/>
+      <c r="Q74" s="5" t="n"/>
+      <c r="R74" s="6" t="n"/>
+      <c r="S74" s="5" t="n"/>
+      <c r="T74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="H75" s="4" t="n"/>
+      <c r="Q75" s="5" t="n"/>
+      <c r="R75" s="6" t="n"/>
+      <c r="S75" s="5" t="n"/>
+      <c r="T75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="H76" s="4" t="n"/>
+      <c r="Q76" s="5" t="n"/>
+      <c r="R76" s="6" t="n"/>
+      <c r="S76" s="5" t="n"/>
+      <c r="T76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="H77" s="4" t="n"/>
+      <c r="Q77" s="5" t="n"/>
+      <c r="R77" s="6" t="n"/>
+      <c r="S77" s="5" t="n"/>
+      <c r="T77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="H78" s="4" t="n"/>
+      <c r="Q78" s="5" t="n"/>
+      <c r="R78" s="6" t="n"/>
+      <c r="S78" s="5" t="n"/>
+      <c r="T78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="H79" s="4" t="n"/>
+      <c r="Q79" s="5" t="n"/>
+      <c r="R79" s="6" t="n"/>
+      <c r="S79" s="5" t="n"/>
+      <c r="T79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="H80" s="4" t="n"/>
+      <c r="Q80" s="5" t="n"/>
+      <c r="R80" s="6" t="n"/>
+      <c r="S80" s="5" t="n"/>
+      <c r="T80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="H81" s="4" t="n"/>
+      <c r="Q81" s="5" t="n"/>
+      <c r="R81" s="6" t="n"/>
+      <c r="S81" s="5" t="n"/>
+      <c r="T81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="H82" s="4" t="n"/>
+      <c r="Q82" s="5" t="n"/>
+      <c r="R82" s="6" t="n"/>
+      <c r="S82" s="5" t="n"/>
+      <c r="T82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="H83" s="4" t="n"/>
+      <c r="Q83" s="5" t="n"/>
+      <c r="R83" s="6" t="n"/>
+      <c r="S83" s="5" t="n"/>
+      <c r="T83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="H84" s="4" t="n"/>
+      <c r="Q84" s="5" t="n"/>
+      <c r="R84" s="6" t="n"/>
+      <c r="S84" s="5" t="n"/>
+      <c r="T84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="H85" s="4" t="n"/>
+      <c r="Q85" s="5" t="n"/>
+      <c r="R85" s="6" t="n"/>
+      <c r="S85" s="5" t="n"/>
+      <c r="T85" s="6" t="n"/>
+    </row>
+    <row r="86">
+      <c r="H86" s="4" t="n"/>
+      <c r="Q86" s="5" t="n"/>
+      <c r="R86" s="6" t="n"/>
+      <c r="S86" s="5" t="n"/>
+      <c r="T86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="H87" s="4" t="n"/>
+      <c r="Q87" s="5" t="n"/>
+      <c r="R87" s="6" t="n"/>
+      <c r="S87" s="5" t="n"/>
+      <c r="T87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="H88" s="4" t="n"/>
+      <c r="Q88" s="5" t="n"/>
+      <c r="R88" s="6" t="n"/>
+      <c r="S88" s="5" t="n"/>
+      <c r="T88" s="6" t="n"/>
+    </row>
+    <row r="89">
+      <c r="H89" s="4" t="n"/>
+      <c r="Q89" s="5" t="n"/>
+      <c r="R89" s="6" t="n"/>
+      <c r="S89" s="5" t="n"/>
+      <c r="T89" s="6" t="n"/>
+    </row>
+    <row r="90">
+      <c r="H90" s="4" t="n"/>
+      <c r="Q90" s="5" t="n"/>
+      <c r="R90" s="6" t="n"/>
+      <c r="S90" s="5" t="n"/>
+      <c r="T90" s="6" t="n"/>
+    </row>
+    <row r="91">
+      <c r="H91" s="4" t="n"/>
+      <c r="Q91" s="5" t="n"/>
+      <c r="R91" s="6" t="n"/>
+      <c r="S91" s="5" t="n"/>
+      <c r="T91" s="6" t="n"/>
+    </row>
+    <row r="92">
+      <c r="H92" s="4" t="n"/>
+      <c r="Q92" s="5" t="n"/>
+      <c r="R92" s="6" t="n"/>
+      <c r="S92" s="5" t="n"/>
+      <c r="T92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="H93" s="4" t="n"/>
+      <c r="Q93" s="5" t="n"/>
+      <c r="R93" s="6" t="n"/>
+      <c r="S93" s="5" t="n"/>
+      <c r="T93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="H94" s="4" t="n"/>
+      <c r="Q94" s="5" t="n"/>
+      <c r="R94" s="6" t="n"/>
+      <c r="S94" s="5" t="n"/>
+      <c r="T94" s="6" t="n"/>
+    </row>
+    <row r="95">
+      <c r="H95" s="4" t="n"/>
+      <c r="Q95" s="5" t="n"/>
+      <c r="R95" s="6" t="n"/>
+      <c r="S95" s="5" t="n"/>
+      <c r="T95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="H96" s="4" t="n"/>
+      <c r="Q96" s="5" t="n"/>
+      <c r="R96" s="6" t="n"/>
+      <c r="S96" s="5" t="n"/>
+      <c r="T96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="H97" s="4" t="n"/>
+      <c r="Q97" s="5" t="n"/>
+      <c r="R97" s="6" t="n"/>
+      <c r="S97" s="5" t="n"/>
+      <c r="T97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="H98" s="4" t="n"/>
+      <c r="Q98" s="5" t="n"/>
+      <c r="R98" s="6" t="n"/>
+      <c r="S98" s="5" t="n"/>
+      <c r="T98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="H99" s="4" t="n"/>
+      <c r="Q99" s="5" t="n"/>
+      <c r="R99" s="6" t="n"/>
+      <c r="S99" s="5" t="n"/>
+      <c r="T99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="H100" s="4" t="n"/>
+      <c r="Q100" s="5" t="n"/>
+      <c r="R100" s="6" t="n"/>
+      <c r="S100" s="5" t="n"/>
+      <c r="T100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="H101" s="4" t="n"/>
+      <c r="Q101" s="5" t="n"/>
+      <c r="R101" s="6" t="n"/>
+      <c r="S101" s="5" t="n"/>
+      <c r="T101" s="6" t="n"/>
+    </row>
+    <row r="102">
+      <c r="H102" s="4" t="n"/>
+      <c r="Q102" s="5" t="n"/>
+      <c r="R102" s="6" t="n"/>
+      <c r="S102" s="5" t="n"/>
+      <c r="T102" s="6" t="n"/>
+    </row>
+    <row r="103">
+      <c r="H103" s="4" t="n"/>
+      <c r="Q103" s="5" t="n"/>
+      <c r="R103" s="6" t="n"/>
+      <c r="S103" s="5" t="n"/>
+      <c r="T103" s="6" t="n"/>
+    </row>
+    <row r="104">
+      <c r="H104" s="4" t="n"/>
+      <c r="Q104" s="5" t="n"/>
+      <c r="R104" s="6" t="n"/>
+      <c r="S104" s="5" t="n"/>
+      <c r="T104" s="6" t="n"/>
+    </row>
+    <row r="105">
+      <c r="H105" s="4" t="n"/>
+      <c r="Q105" s="5" t="n"/>
+      <c r="R105" s="6" t="n"/>
+      <c r="S105" s="5" t="n"/>
+      <c r="T105" s="6" t="n"/>
+    </row>
+    <row r="106">
+      <c r="H106" s="4" t="n"/>
+      <c r="Q106" s="5" t="n"/>
+      <c r="R106" s="6" t="n"/>
+      <c r="S106" s="5" t="n"/>
+      <c r="T106" s="6" t="n"/>
+    </row>
+    <row r="107">
+      <c r="H107" s="4" t="n"/>
+      <c r="Q107" s="5" t="n"/>
+      <c r="R107" s="6" t="n"/>
+      <c r="S107" s="5" t="n"/>
+      <c r="T107" s="6" t="n"/>
+    </row>
+    <row r="108">
+      <c r="H108" s="4" t="n"/>
+      <c r="Q108" s="5" t="n"/>
+      <c r="R108" s="6" t="n"/>
+      <c r="S108" s="5" t="n"/>
+      <c r="T108" s="6" t="n"/>
+    </row>
+    <row r="109">
+      <c r="H109" s="4" t="n"/>
+      <c r="Q109" s="5" t="n"/>
+      <c r="R109" s="6" t="n"/>
+      <c r="S109" s="5" t="n"/>
+      <c r="T109" s="6" t="n"/>
+    </row>
+    <row r="110">
+      <c r="H110" s="4" t="n"/>
+      <c r="Q110" s="5" t="n"/>
+      <c r="R110" s="6" t="n"/>
+      <c r="S110" s="5" t="n"/>
+      <c r="T110" s="6" t="n"/>
+    </row>
+    <row r="111">
+      <c r="H111" s="4" t="n"/>
+      <c r="Q111" s="5" t="n"/>
+      <c r="R111" s="6" t="n"/>
+      <c r="S111" s="5" t="n"/>
+      <c r="T111" s="6" t="n"/>
+    </row>
+    <row r="112">
+      <c r="H112" s="4" t="n"/>
+      <c r="Q112" s="5" t="n"/>
+      <c r="R112" s="6" t="n"/>
+      <c r="S112" s="5" t="n"/>
+      <c r="T112" s="6" t="n"/>
+    </row>
+    <row r="113">
+      <c r="H113" s="4" t="n"/>
+      <c r="Q113" s="5" t="n"/>
+      <c r="R113" s="6" t="n"/>
+      <c r="S113" s="5" t="n"/>
+      <c r="T113" s="6" t="n"/>
+    </row>
+    <row r="114">
+      <c r="H114" s="4" t="n"/>
+      <c r="Q114" s="5" t="n"/>
+      <c r="R114" s="6" t="n"/>
+      <c r="S114" s="5" t="n"/>
+      <c r="T114" s="6" t="n"/>
+    </row>
+    <row r="115">
+      <c r="H115" s="4" t="n"/>
+      <c r="Q115" s="5" t="n"/>
+      <c r="R115" s="6" t="n"/>
+      <c r="S115" s="5" t="n"/>
+      <c r="T115" s="6" t="n"/>
+    </row>
+    <row r="116">
+      <c r="H116" s="4" t="n"/>
+      <c r="Q116" s="5" t="n"/>
+      <c r="R116" s="6" t="n"/>
+      <c r="S116" s="5" t="n"/>
+      <c r="T116" s="6" t="n"/>
+    </row>
+    <row r="117">
+      <c r="H117" s="4" t="n"/>
+      <c r="Q117" s="5" t="n"/>
+      <c r="R117" s="6" t="n"/>
+      <c r="S117" s="5" t="n"/>
+      <c r="T117" s="6" t="n"/>
+    </row>
+    <row r="118">
+      <c r="H118" s="4" t="n"/>
+      <c r="Q118" s="5" t="n"/>
+      <c r="R118" s="6" t="n"/>
+      <c r="S118" s="5" t="n"/>
+      <c r="T118" s="6" t="n"/>
+    </row>
+    <row r="119">
+      <c r="H119" s="4" t="n"/>
+      <c r="Q119" s="5" t="n"/>
+      <c r="R119" s="6" t="n"/>
+      <c r="S119" s="5" t="n"/>
+      <c r="T119" s="6" t="n"/>
+    </row>
+    <row r="120">
+      <c r="H120" s="4" t="n"/>
+      <c r="Q120" s="5" t="n"/>
+      <c r="R120" s="6" t="n"/>
+      <c r="S120" s="5" t="n"/>
+      <c r="T120" s="6" t="n"/>
+    </row>
+    <row r="121">
+      <c r="H121" s="4" t="n"/>
+      <c r="Q121" s="5" t="n"/>
+      <c r="R121" s="6" t="n"/>
+      <c r="S121" s="5" t="n"/>
+      <c r="T121" s="6" t="n"/>
+    </row>
+    <row r="122">
+      <c r="H122" s="4" t="n"/>
+      <c r="Q122" s="5" t="n"/>
+      <c r="R122" s="6" t="n"/>
+      <c r="S122" s="5" t="n"/>
+      <c r="T122" s="6" t="n"/>
+    </row>
+    <row r="123">
+      <c r="H123" s="4" t="n"/>
+      <c r="Q123" s="5" t="n"/>
+      <c r="R123" s="6" t="n"/>
+      <c r="S123" s="5" t="n"/>
+      <c r="T123" s="6" t="n"/>
+    </row>
+    <row r="124">
+      <c r="H124" s="4" t="n"/>
+      <c r="Q124" s="5" t="n"/>
+      <c r="R124" s="6" t="n"/>
+      <c r="S124" s="5" t="n"/>
+      <c r="T124" s="6" t="n"/>
+    </row>
+    <row r="125">
+      <c r="H125" s="4" t="n"/>
+      <c r="Q125" s="5" t="n"/>
+      <c r="R125" s="6" t="n"/>
+      <c r="S125" s="5" t="n"/>
+      <c r="T125" s="6" t="n"/>
+    </row>
+    <row r="126">
+      <c r="H126" s="4" t="n"/>
+      <c r="Q126" s="5" t="n"/>
+      <c r="R126" s="6" t="n"/>
+      <c r="S126" s="5" t="n"/>
+      <c r="T126" s="6" t="n"/>
+    </row>
+    <row r="127">
+      <c r="H127" s="4" t="n"/>
+      <c r="Q127" s="5" t="n"/>
+      <c r="R127" s="6" t="n"/>
+      <c r="S127" s="5" t="n"/>
+      <c r="T127" s="6" t="n"/>
+    </row>
+    <row r="128">
+      <c r="H128" s="4" t="n"/>
+      <c r="Q128" s="5" t="n"/>
+      <c r="R128" s="6" t="n"/>
+      <c r="S128" s="5" t="n"/>
+      <c r="T128" s="6" t="n"/>
+    </row>
+    <row r="129">
+      <c r="H129" s="4" t="n"/>
+      <c r="Q129" s="5" t="n"/>
+      <c r="R129" s="6" t="n"/>
+      <c r="S129" s="5" t="n"/>
+      <c r="T129" s="6" t="n"/>
+    </row>
+    <row r="130">
+      <c r="H130" s="4" t="n"/>
+      <c r="Q130" s="5" t="n"/>
+      <c r="R130" s="6" t="n"/>
+      <c r="S130" s="5" t="n"/>
+      <c r="T130" s="6" t="n"/>
+    </row>
+    <row r="131">
+      <c r="H131" s="4" t="n"/>
+      <c r="Q131" s="5" t="n"/>
+      <c r="R131" s="6" t="n"/>
+      <c r="S131" s="5" t="n"/>
+      <c r="T131" s="6" t="n"/>
+    </row>
+    <row r="132">
+      <c r="H132" s="4" t="n"/>
+      <c r="Q132" s="5" t="n"/>
+      <c r="R132" s="6" t="n"/>
+      <c r="S132" s="5" t="n"/>
+      <c r="T132" s="6" t="n"/>
+    </row>
+    <row r="133">
+      <c r="H133" s="4" t="n"/>
+      <c r="Q133" s="5" t="n"/>
+      <c r="R133" s="6" t="n"/>
+      <c r="S133" s="5" t="n"/>
+      <c r="T133" s="6" t="n"/>
+    </row>
+    <row r="134">
+      <c r="H134" s="4" t="n"/>
+      <c r="Q134" s="5" t="n"/>
+      <c r="R134" s="6" t="n"/>
+      <c r="S134" s="5" t="n"/>
+      <c r="T134" s="6" t="n"/>
+    </row>
+    <row r="135">
+      <c r="H135" s="4" t="n"/>
+      <c r="Q135" s="5" t="n"/>
+      <c r="R135" s="6" t="n"/>
+      <c r="S135" s="5" t="n"/>
+      <c r="T135" s="6" t="n"/>
+    </row>
+    <row r="136">
+      <c r="H136" s="4" t="n"/>
+      <c r="Q136" s="5" t="n"/>
+      <c r="R136" s="6" t="n"/>
+      <c r="S136" s="5" t="n"/>
+      <c r="T136" s="6" t="n"/>
+    </row>
+    <row r="137">
+      <c r="H137" s="4" t="n"/>
+      <c r="Q137" s="5" t="n"/>
+      <c r="R137" s="6" t="n"/>
+      <c r="S137" s="5" t="n"/>
+      <c r="T137" s="6" t="n"/>
+    </row>
+    <row r="138">
+      <c r="H138" s="4" t="n"/>
+      <c r="Q138" s="5" t="n"/>
+      <c r="R138" s="6" t="n"/>
+      <c r="S138" s="5" t="n"/>
+      <c r="T138" s="6" t="n"/>
+    </row>
+    <row r="139">
+      <c r="H139" s="4" t="n"/>
+      <c r="Q139" s="5" t="n"/>
+      <c r="R139" s="6" t="n"/>
+      <c r="S139" s="5" t="n"/>
+      <c r="T139" s="6" t="n"/>
+    </row>
+    <row r="140">
+      <c r="H140" s="4" t="n"/>
+      <c r="Q140" s="5" t="n"/>
+      <c r="R140" s="6" t="n"/>
+      <c r="S140" s="5" t="n"/>
+      <c r="T140" s="6" t="n"/>
+    </row>
+    <row r="141">
+      <c r="H141" s="4" t="n"/>
+      <c r="Q141" s="5" t="n"/>
+      <c r="R141" s="6" t="n"/>
+      <c r="S141" s="5" t="n"/>
+      <c r="T141" s="6" t="n"/>
+    </row>
+    <row r="142">
+      <c r="H142" s="4" t="n"/>
+      <c r="Q142" s="5" t="n"/>
+      <c r="R142" s="6" t="n"/>
+      <c r="S142" s="5" t="n"/>
+      <c r="T142" s="6" t="n"/>
+    </row>
+    <row r="143">
+      <c r="H143" s="4" t="n"/>
+      <c r="Q143" s="5" t="n"/>
+      <c r="R143" s="6" t="n"/>
+      <c r="S143" s="5" t="n"/>
+      <c r="T143" s="6" t="n"/>
+    </row>
+    <row r="144">
+      <c r="H144" s="4" t="n"/>
+      <c r="Q144" s="5" t="n"/>
+      <c r="R144" s="6" t="n"/>
+      <c r="S144" s="5" t="n"/>
+      <c r="T144" s="6" t="n"/>
+    </row>
+    <row r="145">
+      <c r="H145" s="4" t="n"/>
+      <c r="Q145" s="5" t="n"/>
+      <c r="R145" s="6" t="n"/>
+      <c r="S145" s="5" t="n"/>
+      <c r="T145" s="6" t="n"/>
+    </row>
+    <row r="146">
+      <c r="H146" s="4" t="n"/>
+      <c r="Q146" s="5" t="n"/>
+      <c r="R146" s="6" t="n"/>
+      <c r="S146" s="5" t="n"/>
+      <c r="T146" s="6" t="n"/>
+    </row>
+    <row r="147">
+      <c r="H147" s="4" t="n"/>
+      <c r="Q147" s="5" t="n"/>
+      <c r="R147" s="6" t="n"/>
+      <c r="S147" s="5" t="n"/>
+      <c r="T147" s="6" t="n"/>
+    </row>
+    <row r="148">
+      <c r="H148" s="4" t="n"/>
+      <c r="Q148" s="5" t="n"/>
+      <c r="R148" s="6" t="n"/>
+      <c r="S148" s="5" t="n"/>
+      <c r="T148" s="6" t="n"/>
+    </row>
+    <row r="149">
+      <c r="H149" s="4" t="n"/>
+      <c r="Q149" s="5" t="n"/>
+      <c r="R149" s="6" t="n"/>
+      <c r="S149" s="5" t="n"/>
+      <c r="T149" s="6" t="n"/>
+    </row>
+    <row r="150">
+      <c r="H150" s="4" t="n"/>
+      <c r="Q150" s="5" t="n"/>
+      <c r="R150" s="6" t="n"/>
+      <c r="S150" s="5" t="n"/>
+      <c r="T150" s="6" t="n"/>
+    </row>
+    <row r="151">
+      <c r="H151" s="4" t="n"/>
+      <c r="Q151" s="5" t="n"/>
+      <c r="R151" s="6" t="n"/>
+      <c r="S151" s="5" t="n"/>
+      <c r="T151" s="6" t="n"/>
+    </row>
+    <row r="152">
+      <c r="H152" s="4" t="n"/>
+      <c r="Q152" s="5" t="n"/>
+      <c r="R152" s="6" t="n"/>
+      <c r="S152" s="5" t="n"/>
+      <c r="T152" s="6" t="n"/>
+    </row>
+    <row r="153">
+      <c r="H153" s="4" t="n"/>
+      <c r="Q153" s="5" t="n"/>
+      <c r="R153" s="6" t="n"/>
+      <c r="S153" s="5" t="n"/>
+      <c r="T153" s="6" t="n"/>
+    </row>
+    <row r="154">
+      <c r="H154" s="4" t="n"/>
+      <c r="Q154" s="5" t="n"/>
+      <c r="R154" s="6" t="n"/>
+      <c r="S154" s="5" t="n"/>
+      <c r="T154" s="6" t="n"/>
+    </row>
+    <row r="155">
+      <c r="H155" s="4" t="n"/>
+      <c r="Q155" s="5" t="n"/>
+      <c r="R155" s="6" t="n"/>
+      <c r="S155" s="5" t="n"/>
+      <c r="T155" s="6" t="n"/>
+    </row>
+    <row r="156">
+      <c r="H156" s="4" t="n"/>
+      <c r="Q156" s="5" t="n"/>
+      <c r="R156" s="6" t="n"/>
+      <c r="S156" s="5" t="n"/>
+      <c r="T156" s="6" t="n"/>
+    </row>
+    <row r="157">
+      <c r="H157" s="4" t="n"/>
+      <c r="Q157" s="5" t="n"/>
+      <c r="R157" s="6" t="n"/>
+      <c r="S157" s="5" t="n"/>
+      <c r="T157" s="6" t="n"/>
+    </row>
+    <row r="158">
+      <c r="H158" s="4" t="n"/>
+      <c r="Q158" s="5" t="n"/>
+      <c r="R158" s="6" t="n"/>
+      <c r="S158" s="5" t="n"/>
+      <c r="T158" s="6" t="n"/>
+    </row>
+    <row r="159">
+      <c r="H159" s="4" t="n"/>
+      <c r="Q159" s="5" t="n"/>
+      <c r="R159" s="6" t="n"/>
+      <c r="S159" s="5" t="n"/>
+      <c r="T159" s="6" t="n"/>
+    </row>
+    <row r="160">
+      <c r="H160" s="4" t="n"/>
+      <c r="Q160" s="5" t="n"/>
+      <c r="R160" s="6" t="n"/>
+      <c r="S160" s="5" t="n"/>
+      <c r="T160" s="6" t="n"/>
+    </row>
+    <row r="161">
+      <c r="H161" s="4" t="n"/>
+      <c r="Q161" s="5" t="n"/>
+      <c r="R161" s="6" t="n"/>
+      <c r="S161" s="5" t="n"/>
+      <c r="T161" s="6" t="n"/>
+    </row>
+    <row r="162">
+      <c r="H162" s="4" t="n"/>
+      <c r="Q162" s="5" t="n"/>
+      <c r="R162" s="6" t="n"/>
+      <c r="S162" s="5" t="n"/>
+      <c r="T162" s="6" t="n"/>
+    </row>
+    <row r="163">
+      <c r="H163" s="4" t="n"/>
+      <c r="Q163" s="5" t="n"/>
+      <c r="R163" s="6" t="n"/>
+      <c r="S163" s="5" t="n"/>
+      <c r="T163" s="6" t="n"/>
+    </row>
+    <row r="164">
+      <c r="H164" s="4" t="n"/>
+      <c r="Q164" s="5" t="n"/>
+      <c r="R164" s="6" t="n"/>
+      <c r="S164" s="5" t="n"/>
+      <c r="T164" s="6" t="n"/>
+    </row>
+    <row r="165">
+      <c r="H165" s="4" t="n"/>
+      <c r="Q165" s="5" t="n"/>
+      <c r="R165" s="6" t="n"/>
+      <c r="S165" s="5" t="n"/>
+      <c r="T165" s="6" t="n"/>
+    </row>
+    <row r="166">
+      <c r="H166" s="4" t="n"/>
+      <c r="Q166" s="5" t="n"/>
+      <c r="R166" s="6" t="n"/>
+      <c r="S166" s="5" t="n"/>
+      <c r="T166" s="6" t="n"/>
+    </row>
+    <row r="167">
+      <c r="H167" s="4" t="n"/>
+      <c r="Q167" s="5" t="n"/>
+      <c r="R167" s="6" t="n"/>
+      <c r="S167" s="5" t="n"/>
+      <c r="T167" s="6" t="n"/>
+    </row>
+    <row r="168">
+      <c r="H168" s="4" t="n"/>
+      <c r="Q168" s="5" t="n"/>
+      <c r="R168" s="6" t="n"/>
+      <c r="S168" s="5" t="n"/>
+      <c r="T168" s="6" t="n"/>
+    </row>
+    <row r="169">
+      <c r="H169" s="4" t="n"/>
+      <c r="Q169" s="5" t="n"/>
+      <c r="R169" s="6" t="n"/>
+      <c r="S169" s="5" t="n"/>
+      <c r="T169" s="6" t="n"/>
+    </row>
+    <row r="170">
+      <c r="H170" s="4" t="n"/>
+      <c r="Q170" s="5" t="n"/>
+      <c r="R170" s="6" t="n"/>
+      <c r="S170" s="5" t="n"/>
+      <c r="T170" s="6" t="n"/>
+    </row>
+    <row r="171">
+      <c r="H171" s="4" t="n"/>
+      <c r="Q171" s="5" t="n"/>
+      <c r="R171" s="6" t="n"/>
+      <c r="S171" s="5" t="n"/>
+      <c r="T171" s="6" t="n"/>
+    </row>
+    <row r="172">
+      <c r="H172" s="4" t="n"/>
+      <c r="Q172" s="5" t="n"/>
+      <c r="R172" s="6" t="n"/>
+      <c r="S172" s="5" t="n"/>
+      <c r="T172" s="6" t="n"/>
+    </row>
+    <row r="173">
+      <c r="H173" s="4" t="n"/>
+      <c r="Q173" s="5" t="n"/>
+      <c r="R173" s="6" t="n"/>
+      <c r="S173" s="5" t="n"/>
+      <c r="T173" s="6" t="n"/>
+    </row>
+    <row r="174">
+      <c r="H174" s="4" t="n"/>
+      <c r="Q174" s="5" t="n"/>
+      <c r="R174" s="6" t="n"/>
+      <c r="S174" s="5" t="n"/>
+      <c r="T174" s="6" t="n"/>
+    </row>
+    <row r="175">
+      <c r="H175" s="4" t="n"/>
+      <c r="Q175" s="5" t="n"/>
+      <c r="R175" s="6" t="n"/>
+      <c r="S175" s="5" t="n"/>
+      <c r="T175" s="6" t="n"/>
+    </row>
+    <row r="176">
+      <c r="H176" s="4" t="n"/>
+      <c r="Q176" s="5" t="n"/>
+      <c r="R176" s="6" t="n"/>
+      <c r="S176" s="5" t="n"/>
+      <c r="T176" s="6" t="n"/>
+    </row>
+    <row r="177">
+      <c r="H177" s="4" t="n"/>
+      <c r="Q177" s="5" t="n"/>
+      <c r="R177" s="6" t="n"/>
+      <c r="S177" s="5" t="n"/>
+      <c r="T177" s="6" t="n"/>
+    </row>
+    <row r="178">
+      <c r="H178" s="4" t="n"/>
+      <c r="Q178" s="5" t="n"/>
+      <c r="R178" s="6" t="n"/>
+      <c r="S178" s="5" t="n"/>
+      <c r="T178" s="6" t="n"/>
+    </row>
+    <row r="179">
+      <c r="H179" s="4" t="n"/>
+      <c r="Q179" s="5" t="n"/>
+      <c r="R179" s="6" t="n"/>
+      <c r="S179" s="5" t="n"/>
+      <c r="T179" s="6" t="n"/>
+    </row>
+    <row r="180">
+      <c r="H180" s="4" t="n"/>
+      <c r="Q180" s="5" t="n"/>
+      <c r="R180" s="6" t="n"/>
+      <c r="S180" s="5" t="n"/>
+      <c r="T180" s="6" t="n"/>
+    </row>
+    <row r="181">
+      <c r="H181" s="4" t="n"/>
+      <c r="Q181" s="5" t="n"/>
+      <c r="R181" s="6" t="n"/>
+      <c r="S181" s="5" t="n"/>
+      <c r="T181" s="6" t="n"/>
+    </row>
+    <row r="182">
+      <c r="H182" s="4" t="n"/>
+      <c r="Q182" s="5" t="n"/>
+      <c r="R182" s="6" t="n"/>
+      <c r="S182" s="5" t="n"/>
+      <c r="T182" s="6" t="n"/>
+    </row>
+    <row r="183">
+      <c r="H183" s="4" t="n"/>
+      <c r="Q183" s="5" t="n"/>
+      <c r="R183" s="6" t="n"/>
+      <c r="S183" s="5" t="n"/>
+      <c r="T183" s="6" t="n"/>
+    </row>
+    <row r="184">
+      <c r="H184" s="4" t="n"/>
+      <c r="Q184" s="5" t="n"/>
+      <c r="R184" s="6" t="n"/>
+      <c r="S184" s="5" t="n"/>
+      <c r="T184" s="6" t="n"/>
+    </row>
+    <row r="185">
+      <c r="H185" s="4" t="n"/>
+      <c r="Q185" s="5" t="n"/>
+      <c r="R185" s="6" t="n"/>
+      <c r="S185" s="5" t="n"/>
+      <c r="T185" s="6" t="n"/>
+    </row>
+    <row r="186">
+      <c r="H186" s="4" t="n"/>
+      <c r="Q186" s="5" t="n"/>
+      <c r="R186" s="6" t="n"/>
+      <c r="S186" s="5" t="n"/>
+      <c r="T186" s="6" t="n"/>
+    </row>
+    <row r="187">
+      <c r="H187" s="4" t="n"/>
+      <c r="Q187" s="5" t="n"/>
+      <c r="R187" s="6" t="n"/>
+      <c r="S187" s="5" t="n"/>
+      <c r="T187" s="6" t="n"/>
+    </row>
+    <row r="188">
+      <c r="H188" s="4" t="n"/>
+      <c r="Q188" s="5" t="n"/>
+      <c r="R188" s="6" t="n"/>
+      <c r="S188" s="5" t="n"/>
+      <c r="T188" s="6" t="n"/>
+    </row>
+    <row r="189">
+      <c r="H189" s="4" t="n"/>
+      <c r="Q189" s="5" t="n"/>
+      <c r="R189" s="6" t="n"/>
+      <c r="S189" s="5" t="n"/>
+      <c r="T189" s="6" t="n"/>
+    </row>
+    <row r="190">
+      <c r="H190" s="4" t="n"/>
+      <c r="Q190" s="5" t="n"/>
+      <c r="R190" s="6" t="n"/>
+      <c r="S190" s="5" t="n"/>
+      <c r="T190" s="6" t="n"/>
+    </row>
+    <row r="191">
+      <c r="H191" s="4" t="n"/>
+      <c r="Q191" s="5" t="n"/>
+      <c r="R191" s="6" t="n"/>
+      <c r="S191" s="5" t="n"/>
+      <c r="T191" s="6" t="n"/>
+    </row>
+    <row r="192">
+      <c r="H192" s="4" t="n"/>
+      <c r="Q192" s="5" t="n"/>
+      <c r="R192" s="6" t="n"/>
+      <c r="S192" s="5" t="n"/>
+      <c r="T192" s="6" t="n"/>
+    </row>
+    <row r="193">
+      <c r="H193" s="4" t="n"/>
+      <c r="Q193" s="5" t="n"/>
+      <c r="R193" s="6" t="n"/>
+      <c r="S193" s="5" t="n"/>
+      <c r="T193" s="6" t="n"/>
+    </row>
+    <row r="194">
+      <c r="H194" s="4" t="n"/>
+      <c r="Q194" s="5" t="n"/>
+      <c r="R194" s="6" t="n"/>
+      <c r="S194" s="5" t="n"/>
+      <c r="T194" s="6" t="n"/>
+    </row>
+    <row r="195">
+      <c r="H195" s="4" t="n"/>
+      <c r="Q195" s="5" t="n"/>
+      <c r="R195" s="6" t="n"/>
+      <c r="S195" s="5" t="n"/>
+      <c r="T195" s="6" t="n"/>
+    </row>
+    <row r="196">
+      <c r="H196" s="4" t="n"/>
+      <c r="Q196" s="5" t="n"/>
+      <c r="R196" s="6" t="n"/>
+      <c r="S196" s="5" t="n"/>
+      <c r="T196" s="6" t="n"/>
+    </row>
+    <row r="197">
+      <c r="H197" s="4" t="n"/>
+      <c r="Q197" s="5" t="n"/>
+      <c r="R197" s="6" t="n"/>
+      <c r="S197" s="5" t="n"/>
+      <c r="T197" s="6" t="n"/>
+    </row>
+    <row r="198">
+      <c r="H198" s="4" t="n"/>
+      <c r="Q198" s="5" t="n"/>
+      <c r="R198" s="6" t="n"/>
+      <c r="S198" s="5" t="n"/>
+      <c r="T198" s="6" t="n"/>
+    </row>
+    <row r="199">
+      <c r="H199" s="4" t="n"/>
+      <c r="Q199" s="5" t="n"/>
+      <c r="R199" s="6" t="n"/>
+      <c r="S199" s="5" t="n"/>
+      <c r="T199" s="6" t="n"/>
+    </row>
+    <row r="200">
+      <c r="H200" s="4" t="n"/>
+      <c r="Q200" s="5" t="n"/>
+      <c r="R200" s="6" t="n"/>
+      <c r="S200" s="5" t="n"/>
+      <c r="T200" s="6" t="n"/>
+    </row>
+    <row r="201">
+      <c r="H201" s="4" t="n"/>
+      <c r="Q201" s="5" t="n"/>
+      <c r="R201" s="6" t="n"/>
+      <c r="S201" s="5" t="n"/>
+      <c r="T201" s="6" t="n"/>
+    </row>
+    <row r="202">
+      <c r="H202" s="4" t="n"/>
+      <c r="Q202" s="5" t="n"/>
+      <c r="R202" s="6" t="n"/>
+      <c r="S202" s="5" t="n"/>
+      <c r="T202" s="6" t="n"/>
+    </row>
+    <row r="203">
+      <c r="H203" s="4" t="n"/>
+      <c r="Q203" s="5" t="n"/>
+      <c r="R203" s="6" t="n"/>
+      <c r="S203" s="5" t="n"/>
+      <c r="T203" s="6" t="n"/>
+    </row>
+    <row r="204">
+      <c r="H204" s="4" t="n"/>
+      <c r="Q204" s="5" t="n"/>
+      <c r="R204" s="6" t="n"/>
+      <c r="S204" s="5" t="n"/>
+      <c r="T204" s="6" t="n"/>
+    </row>
+    <row r="205">
+      <c r="H205" s="4" t="n"/>
+      <c r="Q205" s="5" t="n"/>
+      <c r="R205" s="6" t="n"/>
+      <c r="S205" s="5" t="n"/>
+      <c r="T205" s="6" t="n"/>
+    </row>
+    <row r="206">
+      <c r="H206" s="4" t="n"/>
+      <c r="Q206" s="5" t="n"/>
+      <c r="R206" s="6" t="n"/>
+      <c r="S206" s="5" t="n"/>
+      <c r="T206" s="6" t="n"/>
+    </row>
+    <row r="207">
+      <c r="H207" s="4" t="n"/>
+      <c r="Q207" s="5" t="n"/>
+      <c r="R207" s="6" t="n"/>
+      <c r="S207" s="5" t="n"/>
+      <c r="T207" s="6" t="n"/>
+    </row>
+    <row r="208">
+      <c r="H208" s="4" t="n"/>
+      <c r="Q208" s="5" t="n"/>
+      <c r="R208" s="6" t="n"/>
+      <c r="S208" s="5" t="n"/>
+      <c r="T208" s="6" t="n"/>
+    </row>
+    <row r="209">
+      <c r="H209" s="4" t="n"/>
+      <c r="Q209" s="5" t="n"/>
+      <c r="R209" s="6" t="n"/>
+      <c r="S209" s="5" t="n"/>
+      <c r="T209" s="6" t="n"/>
+    </row>
+    <row r="210">
+      <c r="H210" s="4" t="n"/>
+      <c r="Q210" s="5" t="n"/>
+      <c r="R210" s="6" t="n"/>
+      <c r="S210" s="5" t="n"/>
+      <c r="T210" s="6" t="n"/>
+    </row>
+    <row r="211">
+      <c r="H211" s="4" t="n"/>
+      <c r="Q211" s="5" t="n"/>
+      <c r="R211" s="6" t="n"/>
+      <c r="S211" s="5" t="n"/>
+      <c r="T211" s="6" t="n"/>
+    </row>
+    <row r="212">
+      <c r="H212" s="4" t="n"/>
+      <c r="Q212" s="5" t="n"/>
+      <c r="R212" s="6" t="n"/>
+      <c r="S212" s="5" t="n"/>
+      <c r="T212" s="6" t="n"/>
+    </row>
+    <row r="213">
+      <c r="H213" s="4" t="n"/>
+      <c r="Q213" s="5" t="n"/>
+      <c r="R213" s="6" t="n"/>
+      <c r="S213" s="5" t="n"/>
+      <c r="T213" s="6" t="n"/>
+    </row>
+    <row r="214">
+      <c r="H214" s="4" t="n"/>
+      <c r="Q214" s="5" t="n"/>
+      <c r="R214" s="6" t="n"/>
+      <c r="S214" s="5" t="n"/>
+      <c r="T214" s="6" t="n"/>
+    </row>
+    <row r="215">
+      <c r="H215" s="4" t="n"/>
+      <c r="Q215" s="5" t="n"/>
+      <c r="R215" s="6" t="n"/>
+      <c r="S215" s="5" t="n"/>
+      <c r="T215" s="6" t="n"/>
+    </row>
+    <row r="216">
+      <c r="H216" s="4" t="n"/>
+      <c r="Q216" s="5" t="n"/>
+      <c r="R216" s="6" t="n"/>
+      <c r="S216" s="5" t="n"/>
+      <c r="T216" s="6" t="n"/>
+    </row>
+    <row r="217">
+      <c r="H217" s="4" t="n"/>
+      <c r="Q217" s="5" t="n"/>
+      <c r="R217" s="6" t="n"/>
+      <c r="S217" s="5" t="n"/>
+      <c r="T217" s="6" t="n"/>
+    </row>
+    <row r="218">
+      <c r="H218" s="4" t="n"/>
+      <c r="Q218" s="5" t="n"/>
+      <c r="R218" s="6" t="n"/>
+      <c r="S218" s="5" t="n"/>
+      <c r="T218" s="6" t="n"/>
+    </row>
+    <row r="219">
+      <c r="H219" s="4" t="n"/>
+      <c r="Q219" s="5" t="n"/>
+      <c r="R219" s="6" t="n"/>
+      <c r="S219" s="5" t="n"/>
+      <c r="T219" s="6" t="n"/>
+    </row>
+    <row r="220">
+      <c r="H220" s="4" t="n"/>
+      <c r="Q220" s="5" t="n"/>
+      <c r="R220" s="6" t="n"/>
+      <c r="S220" s="5" t="n"/>
+      <c r="T220" s="6" t="n"/>
+    </row>
+    <row r="221">
+      <c r="H221" s="4" t="n"/>
+      <c r="Q221" s="5" t="n"/>
+      <c r="R221" s="6" t="n"/>
+      <c r="S221" s="5" t="n"/>
+      <c r="T221" s="6" t="n"/>
+    </row>
+    <row r="222">
+      <c r="H222" s="4" t="n"/>
+      <c r="Q222" s="5" t="n"/>
+      <c r="R222" s="6" t="n"/>
+      <c r="S222" s="5" t="n"/>
+      <c r="T222" s="6" t="n"/>
+    </row>
+    <row r="223">
+      <c r="H223" s="4" t="n"/>
+      <c r="Q223" s="5" t="n"/>
+      <c r="R223" s="6" t="n"/>
+      <c r="S223" s="5" t="n"/>
+      <c r="T223" s="6" t="n"/>
+    </row>
+    <row r="224">
+      <c r="H224" s="4" t="n"/>
+      <c r="Q224" s="5" t="n"/>
+      <c r="R224" s="6" t="n"/>
+      <c r="S224" s="5" t="n"/>
+      <c r="T224" s="6" t="n"/>
+    </row>
+    <row r="225">
+      <c r="H225" s="4" t="n"/>
+      <c r="Q225" s="5" t="n"/>
+      <c r="R225" s="6" t="n"/>
+      <c r="S225" s="5" t="n"/>
+      <c r="T225" s="6" t="n"/>
+    </row>
+    <row r="226">
+      <c r="H226" s="4" t="n"/>
+      <c r="Q226" s="5" t="n"/>
+      <c r="R226" s="6" t="n"/>
+      <c r="S226" s="5" t="n"/>
+      <c r="T226" s="6" t="n"/>
+    </row>
+    <row r="227">
+      <c r="H227" s="4" t="n"/>
+      <c r="Q227" s="5" t="n"/>
+      <c r="R227" s="6" t="n"/>
+      <c r="S227" s="5" t="n"/>
+      <c r="T227" s="6" t="n"/>
+    </row>
+    <row r="228">
+      <c r="H228" s="4" t="n"/>
+      <c r="Q228" s="5" t="n"/>
+      <c r="R228" s="6" t="n"/>
+      <c r="S228" s="5" t="n"/>
+      <c r="T228" s="6" t="n"/>
+    </row>
+    <row r="229">
+      <c r="H229" s="4" t="n"/>
+      <c r="Q229" s="5" t="n"/>
+      <c r="R229" s="6" t="n"/>
+      <c r="S229" s="5" t="n"/>
+      <c r="T229" s="6" t="n"/>
+    </row>
+    <row r="230">
+      <c r="H230" s="4" t="n"/>
+      <c r="Q230" s="5" t="n"/>
+      <c r="R230" s="6" t="n"/>
+      <c r="S230" s="5" t="n"/>
+      <c r="T230" s="6" t="n"/>
+    </row>
+    <row r="231">
+      <c r="H231" s="4" t="n"/>
+      <c r="Q231" s="5" t="n"/>
+      <c r="R231" s="6" t="n"/>
+      <c r="S231" s="5" t="n"/>
+      <c r="T231" s="6" t="n"/>
+    </row>
+    <row r="232">
+      <c r="H232" s="4" t="n"/>
+      <c r="Q232" s="5" t="n"/>
+      <c r="R232" s="6" t="n"/>
+      <c r="S232" s="5" t="n"/>
+      <c r="T232" s="6" t="n"/>
+    </row>
+    <row r="233">
+      <c r="H233" s="4" t="n"/>
+      <c r="Q233" s="5" t="n"/>
+      <c r="R233" s="6" t="n"/>
+      <c r="S233" s="5" t="n"/>
+      <c r="T233" s="6" t="n"/>
+    </row>
+    <row r="234">
+      <c r="H234" s="4" t="n"/>
+      <c r="Q234" s="5" t="n"/>
+      <c r="R234" s="6" t="n"/>
+      <c r="S234" s="5" t="n"/>
+      <c r="T234" s="6" t="n"/>
+    </row>
+    <row r="235">
+      <c r="H235" s="4" t="n"/>
+      <c r="Q235" s="5" t="n"/>
+      <c r="R235" s="6" t="n"/>
+      <c r="S235" s="5" t="n"/>
+      <c r="T235" s="6" t="n"/>
+    </row>
+    <row r="236">
+      <c r="H236" s="4" t="n"/>
+      <c r="Q236" s="5" t="n"/>
+      <c r="R236" s="6" t="n"/>
+      <c r="S236" s="5" t="n"/>
+      <c r="T236" s="6" t="n"/>
+    </row>
+    <row r="237">
+      <c r="H237" s="4" t="n"/>
+      <c r="Q237" s="5" t="n"/>
+      <c r="R237" s="6" t="n"/>
+      <c r="S237" s="5" t="n"/>
+      <c r="T237" s="6" t="n"/>
+    </row>
+    <row r="238">
+      <c r="H238" s="4" t="n"/>
+      <c r="Q238" s="5" t="n"/>
+      <c r="R238" s="6" t="n"/>
+      <c r="S238" s="5" t="n"/>
+      <c r="T238" s="6" t="n"/>
+    </row>
+    <row r="239">
+      <c r="H239" s="4" t="n"/>
+      <c r="Q239" s="5" t="n"/>
+      <c r="R239" s="6" t="n"/>
+      <c r="S239" s="5" t="n"/>
+      <c r="T239" s="6" t="n"/>
+    </row>
+    <row r="240">
+      <c r="H240" s="4" t="n"/>
+      <c r="Q240" s="5" t="n"/>
+      <c r="R240" s="6" t="n"/>
+      <c r="S240" s="5" t="n"/>
+      <c r="T240" s="6" t="n"/>
+    </row>
+    <row r="241">
+      <c r="H241" s="4" t="n"/>
+      <c r="Q241" s="5" t="n"/>
+      <c r="R241" s="6" t="n"/>
+      <c r="S241" s="5" t="n"/>
+      <c r="T241" s="6" t="n"/>
+    </row>
+    <row r="242">
+      <c r="H242" s="4" t="n"/>
+      <c r="Q242" s="5" t="n"/>
+      <c r="R242" s="6" t="n"/>
+      <c r="S242" s="5" t="n"/>
+      <c r="T242" s="6" t="n"/>
+    </row>
+    <row r="243">
+      <c r="H243" s="4" t="n"/>
+      <c r="Q243" s="5" t="n"/>
+      <c r="R243" s="6" t="n"/>
+      <c r="S243" s="5" t="n"/>
+      <c r="T243" s="6" t="n"/>
+    </row>
+    <row r="244">
+      <c r="H244" s="4" t="n"/>
+      <c r="Q244" s="5" t="n"/>
+      <c r="R244" s="6" t="n"/>
+      <c r="S244" s="5" t="n"/>
+      <c r="T244" s="6" t="n"/>
+    </row>
+    <row r="245">
+      <c r="H245" s="4" t="n"/>
+      <c r="Q245" s="5" t="n"/>
+      <c r="R245" s="6" t="n"/>
+      <c r="S245" s="5" t="n"/>
+      <c r="T245" s="6" t="n"/>
+    </row>
+    <row r="246">
+      <c r="H246" s="4" t="n"/>
+      <c r="Q246" s="5" t="n"/>
+      <c r="R246" s="6" t="n"/>
+      <c r="S246" s="5" t="n"/>
+      <c r="T246" s="6" t="n"/>
+    </row>
+    <row r="247">
+      <c r="H247" s="4" t="n"/>
+      <c r="Q247" s="5" t="n"/>
+      <c r="R247" s="6" t="n"/>
+      <c r="S247" s="5" t="n"/>
+      <c r="T247" s="6" t="n"/>
+    </row>
+    <row r="248">
+      <c r="H248" s="4" t="n"/>
+      <c r="Q248" s="5" t="n"/>
+      <c r="R248" s="6" t="n"/>
+      <c r="S248" s="5" t="n"/>
+      <c r="T248" s="6" t="n"/>
+    </row>
+    <row r="249">
+      <c r="H249" s="4" t="n"/>
+      <c r="Q249" s="5" t="n"/>
+      <c r="R249" s="6" t="n"/>
+      <c r="S249" s="5" t="n"/>
+      <c r="T249" s="6" t="n"/>
+    </row>
+    <row r="250">
+      <c r="H250" s="4" t="n"/>
+      <c r="Q250" s="5" t="n"/>
+      <c r="R250" s="6" t="n"/>
+      <c r="S250" s="5" t="n"/>
+      <c r="T250" s="6" t="n"/>
+    </row>
+    <row r="251">
+      <c r="H251" s="4" t="n"/>
+      <c r="Q251" s="5" t="n"/>
+      <c r="R251" s="6" t="n"/>
+      <c r="S251" s="5" t="n"/>
+      <c r="T251" s="6" t="n"/>
+    </row>
+    <row r="252">
+      <c r="H252" s="4" t="n"/>
+      <c r="Q252" s="5" t="n"/>
+      <c r="R252" s="6" t="n"/>
+      <c r="S252" s="5" t="n"/>
+      <c r="T252" s="6" t="n"/>
+    </row>
+    <row r="253">
+      <c r="H253" s="4" t="n"/>
+      <c r="Q253" s="5" t="n"/>
+      <c r="R253" s="6" t="n"/>
+      <c r="S253" s="5" t="n"/>
+      <c r="T253" s="6" t="n"/>
+    </row>
+    <row r="254">
+      <c r="H254" s="4" t="n"/>
+      <c r="Q254" s="5" t="n"/>
+      <c r="R254" s="6" t="n"/>
+      <c r="S254" s="5" t="n"/>
+      <c r="T254" s="6" t="n"/>
+    </row>
+    <row r="255">
+      <c r="H255" s="4" t="n"/>
+      <c r="Q255" s="5" t="n"/>
+      <c r="R255" s="6" t="n"/>
+      <c r="S255" s="5" t="n"/>
+      <c r="T255" s="6" t="n"/>
+    </row>
+    <row r="256">
+      <c r="H256" s="4" t="n"/>
+      <c r="Q256" s="5" t="n"/>
+      <c r="R256" s="6" t="n"/>
+      <c r="S256" s="5" t="n"/>
+      <c r="T256" s="6" t="n"/>
+    </row>
+    <row r="257">
+      <c r="H257" s="4" t="n"/>
+      <c r="Q257" s="5" t="n"/>
+      <c r="R257" s="6" t="n"/>
+      <c r="S257" s="5" t="n"/>
+      <c r="T257" s="6" t="n"/>
+    </row>
+    <row r="258">
+      <c r="H258" s="4" t="n"/>
+      <c r="Q258" s="5" t="n"/>
+      <c r="R258" s="6" t="n"/>
+      <c r="S258" s="5" t="n"/>
+      <c r="T258" s="6" t="n"/>
+    </row>
+    <row r="259">
+      <c r="H259" s="4" t="n"/>
+      <c r="Q259" s="5" t="n"/>
+      <c r="R259" s="6" t="n"/>
+      <c r="S259" s="5" t="n"/>
+      <c r="T259" s="6" t="n"/>
+    </row>
+    <row r="260">
+      <c r="H260" s="4" t="n"/>
+      <c r="Q260" s="5" t="n"/>
+      <c r="R260" s="6" t="n"/>
+      <c r="S260" s="5" t="n"/>
+      <c r="T260" s="6" t="n"/>
+    </row>
+    <row r="261">
+      <c r="H261" s="4" t="n"/>
+      <c r="Q261" s="5" t="n"/>
+      <c r="R261" s="6" t="n"/>
+      <c r="S261" s="5" t="n"/>
+      <c r="T261" s="6" t="n"/>
+    </row>
+    <row r="262">
+      <c r="H262" s="4" t="n"/>
+      <c r="Q262" s="5" t="n"/>
+      <c r="R262" s="6" t="n"/>
+      <c r="S262" s="5" t="n"/>
+      <c r="T262" s="6" t="n"/>
+    </row>
+    <row r="263">
+      <c r="H263" s="4" t="n"/>
+      <c r="Q263" s="5" t="n"/>
+      <c r="R263" s="6" t="n"/>
+      <c r="S263" s="5" t="n"/>
+      <c r="T263" s="6" t="n"/>
+    </row>
+    <row r="264">
+      <c r="H264" s="4" t="n"/>
+      <c r="Q264" s="5" t="n"/>
+      <c r="R264" s="6" t="n"/>
+      <c r="S264" s="5" t="n"/>
+      <c r="T264" s="6" t="n"/>
+    </row>
+    <row r="265">
+      <c r="H265" s="4" t="n"/>
+      <c r="Q265" s="5" t="n"/>
+      <c r="R265" s="6" t="n"/>
+      <c r="S265" s="5" t="n"/>
+      <c r="T265" s="6" t="n"/>
+    </row>
+    <row r="266">
+      <c r="H266" s="4" t="n"/>
+      <c r="Q266" s="5" t="n"/>
+      <c r="R266" s="6" t="n"/>
+      <c r="S266" s="5" t="n"/>
+      <c r="T266" s="6" t="n"/>
+    </row>
+    <row r="267">
+      <c r="H267" s="4" t="n"/>
+      <c r="Q267" s="5" t="n"/>
+      <c r="R267" s="6" t="n"/>
+      <c r="S267" s="5" t="n"/>
+      <c r="T267" s="6" t="n"/>
+    </row>
+    <row r="268">
+      <c r="H268" s="4" t="n"/>
+      <c r="Q268" s="5" t="n"/>
+      <c r="R268" s="6" t="n"/>
+      <c r="S268" s="5" t="n"/>
+      <c r="T268" s="6" t="n"/>
+    </row>
+    <row r="269">
+      <c r="H269" s="4" t="n"/>
+      <c r="Q269" s="5" t="n"/>
+      <c r="R269" s="6" t="n"/>
+      <c r="S269" s="5" t="n"/>
+      <c r="T269" s="6" t="n"/>
+    </row>
+    <row r="270">
+      <c r="H270" s="4" t="n"/>
+      <c r="Q270" s="5" t="n"/>
+      <c r="R270" s="6" t="n"/>
+      <c r="S270" s="5" t="n"/>
+      <c r="T270" s="6" t="n"/>
+    </row>
+    <row r="271">
+      <c r="H271" s="4" t="n"/>
+      <c r="Q271" s="5" t="n"/>
+      <c r="R271" s="6" t="n"/>
+      <c r="S271" s="5" t="n"/>
+      <c r="T271" s="6" t="n"/>
+    </row>
+    <row r="272">
+      <c r="H272" s="4" t="n"/>
+      <c r="Q272" s="5" t="n"/>
+      <c r="R272" s="6" t="n"/>
+      <c r="S272" s="5" t="n"/>
+      <c r="T272" s="6" t="n"/>
+    </row>
+    <row r="273">
+      <c r="H273" s="4" t="n"/>
+      <c r="Q273" s="5" t="n"/>
+      <c r="R273" s="6" t="n"/>
+      <c r="S273" s="5" t="n"/>
+      <c r="T273" s="6" t="n"/>
+    </row>
+    <row r="274">
+      <c r="H274" s="4" t="n"/>
+      <c r="Q274" s="5" t="n"/>
+      <c r="R274" s="6" t="n"/>
+      <c r="S274" s="5" t="n"/>
+      <c r="T274" s="6" t="n"/>
+    </row>
+    <row r="275">
+      <c r="H275" s="4" t="n"/>
+      <c r="Q275" s="5" t="n"/>
+      <c r="R275" s="6" t="n"/>
+      <c r="S275" s="5" t="n"/>
+      <c r="T275" s="6" t="n"/>
+    </row>
+    <row r="276">
+      <c r="H276" s="4" t="n"/>
+      <c r="Q276" s="5" t="n"/>
+      <c r="R276" s="6" t="n"/>
+      <c r="S276" s="5" t="n"/>
+      <c r="T276" s="6" t="n"/>
+    </row>
+    <row r="277">
+      <c r="H277" s="4" t="n"/>
+      <c r="Q277" s="5" t="n"/>
+      <c r="R277" s="6" t="n"/>
+      <c r="S277" s="5" t="n"/>
+      <c r="T277" s="6" t="n"/>
+    </row>
+    <row r="278">
+      <c r="H278" s="4" t="n"/>
+      <c r="Q278" s="5" t="n"/>
+      <c r="R278" s="6" t="n"/>
+      <c r="S278" s="5" t="n"/>
+      <c r="T278" s="6" t="n"/>
+    </row>
+    <row r="279">
+      <c r="H279" s="4" t="n"/>
+      <c r="Q279" s="5" t="n"/>
+      <c r="R279" s="6" t="n"/>
+      <c r="S279" s="5" t="n"/>
+      <c r="T279" s="6" t="n"/>
+    </row>
+    <row r="280">
+      <c r="H280" s="4" t="n"/>
+      <c r="Q280" s="5" t="n"/>
+      <c r="R280" s="6" t="n"/>
+      <c r="S280" s="5" t="n"/>
+      <c r="T280" s="6" t="n"/>
+    </row>
+    <row r="281">
+      <c r="H281" s="4" t="n"/>
+      <c r="Q281" s="5" t="n"/>
+      <c r="R281" s="6" t="n"/>
+      <c r="S281" s="5" t="n"/>
+      <c r="T281" s="6" t="n"/>
+    </row>
+    <row r="282">
+      <c r="H282" s="4" t="n"/>
+      <c r="Q282" s="5" t="n"/>
+      <c r="R282" s="6" t="n"/>
+      <c r="S282" s="5" t="n"/>
+      <c r="T282" s="6" t="n"/>
+    </row>
+    <row r="283">
+      <c r="H283" s="4" t="n"/>
+      <c r="Q283" s="5" t="n"/>
+      <c r="R283" s="6" t="n"/>
+      <c r="S283" s="5" t="n"/>
+      <c r="T283" s="6" t="n"/>
+    </row>
+    <row r="284">
+      <c r="H284" s="4" t="n"/>
+      <c r="Q284" s="5" t="n"/>
+      <c r="R284" s="6" t="n"/>
+      <c r="S284" s="5" t="n"/>
+      <c r="T284" s="6" t="n"/>
+    </row>
+    <row r="285">
+      <c r="H285" s="4" t="n"/>
+      <c r="Q285" s="5" t="n"/>
+      <c r="R285" s="6" t="n"/>
+      <c r="S285" s="5" t="n"/>
+      <c r="T285" s="6" t="n"/>
+    </row>
+    <row r="286">
+      <c r="H286" s="4" t="n"/>
+      <c r="Q286" s="5" t="n"/>
+      <c r="R286" s="6" t="n"/>
+      <c r="S286" s="5" t="n"/>
+      <c r="T286" s="6" t="n"/>
+    </row>
+    <row r="287">
+      <c r="H287" s="4" t="n"/>
+      <c r="Q287" s="5" t="n"/>
+      <c r="R287" s="6" t="n"/>
+      <c r="S287" s="5" t="n"/>
+      <c r="T287" s="6" t="n"/>
+    </row>
+    <row r="288">
+      <c r="H288" s="4" t="n"/>
+      <c r="Q288" s="5" t="n"/>
+      <c r="R288" s="6" t="n"/>
+      <c r="S288" s="5" t="n"/>
+      <c r="T288" s="6" t="n"/>
+    </row>
+    <row r="289">
+      <c r="H289" s="4" t="n"/>
+      <c r="Q289" s="5" t="n"/>
+      <c r="R289" s="6" t="n"/>
+      <c r="S289" s="5" t="n"/>
+      <c r="T289" s="6" t="n"/>
+    </row>
+    <row r="290">
+      <c r="H290" s="4" t="n"/>
+      <c r="Q290" s="5" t="n"/>
+      <c r="R290" s="6" t="n"/>
+      <c r="S290" s="5" t="n"/>
+      <c r="T290" s="6" t="n"/>
+    </row>
+    <row r="291">
+      <c r="H291" s="4" t="n"/>
+      <c r="Q291" s="5" t="n"/>
+      <c r="R291" s="6" t="n"/>
+      <c r="S291" s="5" t="n"/>
+      <c r="T291" s="6" t="n"/>
+    </row>
+    <row r="292">
+      <c r="H292" s="4" t="n"/>
+      <c r="Q292" s="5" t="n"/>
+      <c r="R292" s="6" t="n"/>
+      <c r="S292" s="5" t="n"/>
+      <c r="T292" s="6" t="n"/>
+    </row>
+    <row r="293">
+      <c r="H293" s="4" t="n"/>
+      <c r="Q293" s="5" t="n"/>
+      <c r="R293" s="6" t="n"/>
+      <c r="S293" s="5" t="n"/>
+      <c r="T293" s="6" t="n"/>
+    </row>
+    <row r="294">
+      <c r="H294" s="4" t="n"/>
+      <c r="Q294" s="5" t="n"/>
+      <c r="R294" s="6" t="n"/>
+      <c r="S294" s="5" t="n"/>
+      <c r="T294" s="6" t="n"/>
+    </row>
+    <row r="295">
+      <c r="H295" s="4" t="n"/>
+      <c r="Q295" s="5" t="n"/>
+      <c r="R295" s="6" t="n"/>
+      <c r="S295" s="5" t="n"/>
+      <c r="T295" s="6" t="n"/>
+    </row>
+    <row r="296">
+      <c r="H296" s="4" t="n"/>
+      <c r="Q296" s="5" t="n"/>
+      <c r="R296" s="6" t="n"/>
+      <c r="S296" s="5" t="n"/>
+      <c r="T296" s="6" t="n"/>
+    </row>
+    <row r="297">
+      <c r="H297" s="4" t="n"/>
+      <c r="Q297" s="5" t="n"/>
+      <c r="R297" s="6" t="n"/>
+      <c r="S297" s="5" t="n"/>
+      <c r="T297" s="6" t="n"/>
+    </row>
+    <row r="298">
+      <c r="H298" s="4" t="n"/>
+      <c r="Q298" s="5" t="n"/>
+      <c r="R298" s="6" t="n"/>
+      <c r="S298" s="5" t="n"/>
+      <c r="T298" s="6" t="n"/>
+    </row>
+    <row r="299">
+      <c r="H299" s="4" t="n"/>
+      <c r="Q299" s="5" t="n"/>
+      <c r="R299" s="6" t="n"/>
+      <c r="S299" s="5" t="n"/>
+      <c r="T299" s="6" t="n"/>
+    </row>
+    <row r="300">
+      <c r="H300" s="4" t="n"/>
+      <c r="Q300" s="5" t="n"/>
+      <c r="R300" s="6" t="n"/>
+      <c r="S300" s="5" t="n"/>
+      <c r="T300" s="6" t="n"/>
+    </row>
+    <row r="301">
+      <c r="H301" s="4" t="n"/>
+      <c r="Q301" s="5" t="n"/>
+      <c r="R301" s="6" t="n"/>
+      <c r="S301" s="5" t="n"/>
+      <c r="T301" s="6" t="n"/>
+    </row>
+    <row r="302">
+      <c r="H302" s="4" t="n"/>
+      <c r="Q302" s="5" t="n"/>
+      <c r="R302" s="6" t="n"/>
+      <c r="S302" s="5" t="n"/>
+      <c r="T302" s="6" t="n"/>
+    </row>
+    <row r="303">
+      <c r="H303" s="4" t="n"/>
+      <c r="Q303" s="5" t="n"/>
+      <c r="R303" s="6" t="n"/>
+      <c r="S303" s="5" t="n"/>
+      <c r="T303" s="6" t="n"/>
+    </row>
+    <row r="304">
+      <c r="H304" s="4" t="n"/>
+      <c r="Q304" s="5" t="n"/>
+      <c r="R304" s="6" t="n"/>
+      <c r="S304" s="5" t="n"/>
+      <c r="T304" s="6" t="n"/>
+    </row>
+    <row r="305">
+      <c r="H305" s="4" t="n"/>
+      <c r="Q305" s="5" t="n"/>
+      <c r="R305" s="6" t="n"/>
+      <c r="S305" s="5" t="n"/>
+      <c r="T305" s="6" t="n"/>
+    </row>
+    <row r="306">
+      <c r="H306" s="4" t="n"/>
+      <c r="Q306" s="5" t="n"/>
+      <c r="R306" s="6" t="n"/>
+      <c r="S306" s="5" t="n"/>
+      <c r="T306" s="6" t="n"/>
+    </row>
+    <row r="307">
+      <c r="H307" s="4" t="n"/>
+      <c r="Q307" s="5" t="n"/>
+      <c r="R307" s="6" t="n"/>
+      <c r="S307" s="5" t="n"/>
+      <c r="T307" s="6" t="n"/>
+    </row>
+    <row r="308">
+      <c r="H308" s="4" t="n"/>
+      <c r="Q308" s="5" t="n"/>
+      <c r="R308" s="6" t="n"/>
+      <c r="S308" s="5" t="n"/>
+      <c r="T308" s="6" t="n"/>
+    </row>
+    <row r="309">
+      <c r="H309" s="4" t="n"/>
+      <c r="Q309" s="5" t="n"/>
+      <c r="R309" s="6" t="n"/>
+      <c r="S309" s="5" t="n"/>
+      <c r="T309" s="6" t="n"/>
+    </row>
+    <row r="310">
+      <c r="H310" s="4" t="n"/>
+      <c r="Q310" s="5" t="n"/>
+      <c r="R310" s="6" t="n"/>
+      <c r="S310" s="5" t="n"/>
+      <c r="T310" s="6" t="n"/>
+    </row>
+    <row r="311">
+      <c r="H311" s="4" t="n"/>
+      <c r="Q311" s="5" t="n"/>
+      <c r="R311" s="6" t="n"/>
+      <c r="S311" s="5" t="n"/>
+      <c r="T311" s="6" t="n"/>
+    </row>
+    <row r="312">
+      <c r="H312" s="4" t="n"/>
+      <c r="Q312" s="5" t="n"/>
+      <c r="R312" s="6" t="n"/>
+      <c r="S312" s="5" t="n"/>
+      <c r="T312" s="6" t="n"/>
+    </row>
+    <row r="313">
+      <c r="H313" s="4" t="n"/>
+      <c r="Q313" s="5" t="n"/>
+      <c r="R313" s="6" t="n"/>
+      <c r="S313" s="5" t="n"/>
+      <c r="T313" s="6" t="n"/>
+    </row>
+    <row r="314">
+      <c r="H314" s="4" t="n"/>
+      <c r="Q314" s="5" t="n"/>
+      <c r="R314" s="6" t="n"/>
+      <c r="S314" s="5" t="n"/>
+      <c r="T314" s="6" t="n"/>
+    </row>
+    <row r="315">
+      <c r="H315" s="4" t="n"/>
+      <c r="Q315" s="5" t="n"/>
+      <c r="R315" s="6" t="n"/>
+      <c r="S315" s="5" t="n"/>
+      <c r="T315" s="6" t="n"/>
+    </row>
+    <row r="316">
+      <c r="H316" s="4" t="n"/>
+      <c r="Q316" s="5" t="n"/>
+      <c r="R316" s="6" t="n"/>
+      <c r="S316" s="5" t="n"/>
+      <c r="T316" s="6" t="n"/>
+    </row>
+    <row r="317">
+      <c r="H317" s="4" t="n"/>
+      <c r="Q317" s="5" t="n"/>
+      <c r="R317" s="6" t="n"/>
+      <c r="S317" s="5" t="n"/>
+      <c r="T317" s="6" t="n"/>
+    </row>
+    <row r="318">
+      <c r="H318" s="4" t="n"/>
+      <c r="Q318" s="5" t="n"/>
+      <c r="R318" s="6" t="n"/>
+      <c r="S318" s="5" t="n"/>
+      <c r="T318" s="6" t="n"/>
+    </row>
+    <row r="319">
+      <c r="H319" s="4" t="n"/>
+      <c r="Q319" s="5" t="n"/>
+      <c r="R319" s="6" t="n"/>
+      <c r="S319" s="5" t="n"/>
+      <c r="T319" s="6" t="n"/>
+    </row>
+    <row r="320">
+      <c r="H320" s="4" t="n"/>
+      <c r="Q320" s="5" t="n"/>
+      <c r="R320" s="6" t="n"/>
+      <c r="S320" s="5" t="n"/>
+      <c r="T320" s="6" t="n"/>
+    </row>
+    <row r="321">
+      <c r="H321" s="4" t="n"/>
+      <c r="Q321" s="5" t="n"/>
+      <c r="R321" s="6" t="n"/>
+      <c r="S321" s="5" t="n"/>
+      <c r="T321" s="6" t="n"/>
+    </row>
+    <row r="322">
+      <c r="H322" s="4" t="n"/>
+      <c r="Q322" s="5" t="n"/>
+      <c r="R322" s="6" t="n"/>
+      <c r="S322" s="5" t="n"/>
+      <c r="T322" s="6" t="n"/>
+    </row>
+    <row r="323">
+      <c r="H323" s="4" t="n"/>
+      <c r="Q323" s="5" t="n"/>
+      <c r="R323" s="6" t="n"/>
+      <c r="S323" s="5" t="n"/>
+      <c r="T323" s="6" t="n"/>
+    </row>
+    <row r="324">
+      <c r="H324" s="4" t="n"/>
+      <c r="Q324" s="5" t="n"/>
+      <c r="R324" s="6" t="n"/>
+      <c r="S324" s="5" t="n"/>
+      <c r="T324" s="6" t="n"/>
+    </row>
+    <row r="325">
+      <c r="H325" s="4" t="n"/>
+      <c r="Q325" s="5" t="n"/>
+      <c r="R325" s="6" t="n"/>
+      <c r="S325" s="5" t="n"/>
+      <c r="T325" s="6" t="n"/>
+    </row>
+    <row r="326">
+      <c r="H326" s="4" t="n"/>
+      <c r="Q326" s="5" t="n"/>
+      <c r="R326" s="6" t="n"/>
+      <c r="S326" s="5" t="n"/>
+      <c r="T326" s="6" t="n"/>
+    </row>
+    <row r="327">
+      <c r="H327" s="4" t="n"/>
+      <c r="Q327" s="5" t="n"/>
+      <c r="R327" s="6" t="n"/>
+      <c r="S327" s="5" t="n"/>
+      <c r="T327" s="6" t="n"/>
+    </row>
+    <row r="328">
+      <c r="H328" s="4" t="n"/>
+      <c r="Q328" s="5" t="n"/>
+      <c r="R328" s="6" t="n"/>
+      <c r="S328" s="5" t="n"/>
+      <c r="T328" s="6" t="n"/>
+    </row>
+    <row r="329">
+      <c r="H329" s="4" t="n"/>
+      <c r="Q329" s="5" t="n"/>
+      <c r="R329" s="6" t="n"/>
+      <c r="S329" s="5" t="n"/>
+      <c r="T329" s="6" t="n"/>
+    </row>
+    <row r="330">
+      <c r="H330" s="4" t="n"/>
+      <c r="Q330" s="5" t="n"/>
+      <c r="R330" s="6" t="n"/>
+      <c r="S330" s="5" t="n"/>
+      <c r="T330" s="6" t="n"/>
+    </row>
+    <row r="331">
+      <c r="H331" s="4" t="n"/>
+      <c r="Q331" s="5" t="n"/>
+      <c r="R331" s="6" t="n"/>
+      <c r="S331" s="5" t="n"/>
+      <c r="T331" s="6" t="n"/>
+    </row>
+    <row r="332">
+      <c r="H332" s="4" t="n"/>
+      <c r="Q332" s="5" t="n"/>
+      <c r="R332" s="6" t="n"/>
+      <c r="S332" s="5" t="n"/>
+      <c r="T332" s="6" t="n"/>
+    </row>
+    <row r="333">
+      <c r="H333" s="4" t="n"/>
+      <c r="Q333" s="5" t="n"/>
+      <c r="R333" s="6" t="n"/>
+      <c r="S333" s="5" t="n"/>
+      <c r="T333" s="6" t="n"/>
+    </row>
+    <row r="334">
+      <c r="H334" s="4" t="n"/>
+      <c r="Q334" s="5" t="n"/>
+      <c r="R334" s="6" t="n"/>
+      <c r="S334" s="5" t="n"/>
+      <c r="T334" s="6" t="n"/>
+    </row>
+    <row r="335">
+      <c r="H335" s="4" t="n"/>
+      <c r="Q335" s="5" t="n"/>
+      <c r="R335" s="6" t="n"/>
+      <c r="S335" s="5" t="n"/>
+      <c r="T335" s="6" t="n"/>
+    </row>
+    <row r="336">
+      <c r="H336" s="4" t="n"/>
+      <c r="Q336" s="5" t="n"/>
+      <c r="R336" s="6" t="n"/>
+      <c r="S336" s="5" t="n"/>
+      <c r="T336" s="6" t="n"/>
+    </row>
+    <row r="337">
+      <c r="H337" s="4" t="n"/>
+      <c r="Q337" s="5" t="n"/>
+      <c r="R337" s="6" t="n"/>
+      <c r="S337" s="5" t="n"/>
+      <c r="T337" s="6" t="n"/>
+    </row>
+    <row r="338">
+      <c r="H338" s="4" t="n"/>
+      <c r="Q338" s="5" t="n"/>
+      <c r="R338" s="6" t="n"/>
+      <c r="S338" s="5" t="n"/>
+      <c r="T338" s="6" t="n"/>
+    </row>
+    <row r="339">
+      <c r="H339" s="4" t="n"/>
+      <c r="Q339" s="5" t="n"/>
+      <c r="R339" s="6" t="n"/>
+      <c r="S339" s="5" t="n"/>
+      <c r="T339" s="6" t="n"/>
+    </row>
+    <row r="340">
+      <c r="H340" s="4" t="n"/>
+      <c r="Q340" s="5" t="n"/>
+      <c r="R340" s="6" t="n"/>
+      <c r="S340" s="5" t="n"/>
+      <c r="T340" s="6" t="n"/>
+    </row>
+    <row r="341">
+      <c r="H341" s="4" t="n"/>
+      <c r="Q341" s="5" t="n"/>
+      <c r="R341" s="6" t="n"/>
+      <c r="S341" s="5" t="n"/>
+      <c r="T341" s="6" t="n"/>
+    </row>
+    <row r="342">
+      <c r="H342" s="4" t="n"/>
+      <c r="Q342" s="5" t="n"/>
+      <c r="R342" s="6" t="n"/>
+      <c r="S342" s="5" t="n"/>
+      <c r="T342" s="6" t="n"/>
+    </row>
+    <row r="343">
+      <c r="H343" s="4" t="n"/>
+      <c r="Q343" s="5" t="n"/>
+      <c r="R343" s="6" t="n"/>
+      <c r="S343" s="5" t="n"/>
+      <c r="T343" s="6" t="n"/>
+    </row>
+    <row r="344">
+      <c r="H344" s="4" t="n"/>
+      <c r="Q344" s="5" t="n"/>
+      <c r="R344" s="6" t="n"/>
+      <c r="S344" s="5" t="n"/>
+      <c r="T344" s="6" t="n"/>
+    </row>
+    <row r="345">
+      <c r="H345" s="4" t="n"/>
+      <c r="Q345" s="5" t="n"/>
+      <c r="R345" s="6" t="n"/>
+      <c r="S345" s="5" t="n"/>
+      <c r="T345" s="6" t="n"/>
+    </row>
+    <row r="346">
+      <c r="H346" s="4" t="n"/>
+      <c r="Q346" s="5" t="n"/>
+      <c r="R346" s="6" t="n"/>
+      <c r="S346" s="5" t="n"/>
+      <c r="T346" s="6" t="n"/>
+    </row>
+    <row r="347">
+      <c r="H347" s="4" t="n"/>
+      <c r="Q347" s="5" t="n"/>
+      <c r="R347" s="6" t="n"/>
+      <c r="S347" s="5" t="n"/>
+      <c r="T347" s="6" t="n"/>
+    </row>
+    <row r="348">
+      <c r="H348" s="4" t="n"/>
+      <c r="Q348" s="5" t="n"/>
+      <c r="R348" s="6" t="n"/>
+      <c r="S348" s="5" t="n"/>
+      <c r="T348" s="6" t="n"/>
+    </row>
+    <row r="349">
+      <c r="H349" s="4" t="n"/>
+      <c r="Q349" s="5" t="n"/>
+      <c r="R349" s="6" t="n"/>
+      <c r="S349" s="5" t="n"/>
+      <c r="T349" s="6" t="n"/>
+    </row>
+    <row r="350">
+      <c r="H350" s="4" t="n"/>
+      <c r="Q350" s="5" t="n"/>
+      <c r="R350" s="6" t="n"/>
+      <c r="S350" s="5" t="n"/>
+      <c r="T350" s="6" t="n"/>
+    </row>
+    <row r="351">
+      <c r="H351" s="4" t="n"/>
+      <c r="Q351" s="5" t="n"/>
+      <c r="R351" s="6" t="n"/>
+      <c r="S351" s="5" t="n"/>
+      <c r="T351" s="6" t="n"/>
+    </row>
+    <row r="352">
+      <c r="H352" s="4" t="n"/>
+      <c r="Q352" s="5" t="n"/>
+      <c r="R352" s="6" t="n"/>
+      <c r="S352" s="5" t="n"/>
+      <c r="T352" s="6" t="n"/>
+    </row>
+    <row r="353">
+      <c r="H353" s="4" t="n"/>
+      <c r="Q353" s="5" t="n"/>
+      <c r="R353" s="6" t="n"/>
+      <c r="S353" s="5" t="n"/>
+      <c r="T353" s="6" t="n"/>
+    </row>
+    <row r="354">
+      <c r="H354" s="4" t="n"/>
+      <c r="Q354" s="5" t="n"/>
+      <c r="R354" s="6" t="n"/>
+      <c r="S354" s="5" t="n"/>
+      <c r="T354" s="6" t="n"/>
+    </row>
+    <row r="355">
+      <c r="H355" s="4" t="n"/>
+      <c r="Q355" s="5" t="n"/>
+      <c r="R355" s="6" t="n"/>
+      <c r="S355" s="5" t="n"/>
+      <c r="T355" s="6" t="n"/>
+    </row>
+    <row r="356">
+      <c r="H356" s="4" t="n"/>
+      <c r="Q356" s="5" t="n"/>
+      <c r="R356" s="6" t="n"/>
+      <c r="S356" s="5" t="n"/>
+      <c r="T356" s="6" t="n"/>
+    </row>
+    <row r="357">
+      <c r="H357" s="4" t="n"/>
+      <c r="Q357" s="5" t="n"/>
+      <c r="R357" s="6" t="n"/>
+      <c r="S357" s="5" t="n"/>
+      <c r="T357" s="6" t="n"/>
+    </row>
+    <row r="358">
+      <c r="H358" s="4" t="n"/>
+      <c r="Q358" s="5" t="n"/>
+      <c r="R358" s="6" t="n"/>
+      <c r="S358" s="5" t="n"/>
+      <c r="T358" s="6" t="n"/>
+    </row>
+    <row r="359">
+      <c r="H359" s="4" t="n"/>
+      <c r="Q359" s="5" t="n"/>
+      <c r="R359" s="6" t="n"/>
+      <c r="S359" s="5" t="n"/>
+      <c r="T359" s="6" t="n"/>
+    </row>
+    <row r="360">
+      <c r="H360" s="4" t="n"/>
+      <c r="Q360" s="5" t="n"/>
+      <c r="R360" s="6" t="n"/>
+      <c r="S360" s="5" t="n"/>
+      <c r="T360" s="6" t="n"/>
+    </row>
+    <row r="361">
+      <c r="H361" s="4" t="n"/>
+      <c r="Q361" s="5" t="n"/>
+      <c r="R361" s="6" t="n"/>
+      <c r="S361" s="5" t="n"/>
+      <c r="T361" s="6" t="n"/>
+    </row>
+    <row r="362">
+      <c r="H362" s="4" t="n"/>
+      <c r="Q362" s="5" t="n"/>
+      <c r="R362" s="6" t="n"/>
+      <c r="S362" s="5" t="n"/>
+      <c r="T362" s="6" t="n"/>
+    </row>
+    <row r="363">
+      <c r="H363" s="4" t="n"/>
+      <c r="Q363" s="5" t="n"/>
+      <c r="R363" s="6" t="n"/>
+      <c r="S363" s="5" t="n"/>
+      <c r="T363" s="6" t="n"/>
+    </row>
+    <row r="364">
+      <c r="H364" s="4" t="n"/>
+      <c r="Q364" s="5" t="n"/>
+      <c r="R364" s="6" t="n"/>
+      <c r="S364" s="5" t="n"/>
+      <c r="T364" s="6" t="n"/>
+    </row>
+    <row r="365">
+      <c r="H365" s="4" t="n"/>
+      <c r="Q365" s="5" t="n"/>
+      <c r="R365" s="6" t="n"/>
+      <c r="S365" s="5" t="n"/>
+      <c r="T365" s="6" t="n"/>
+    </row>
+    <row r="366">
+      <c r="H366" s="4" t="n"/>
+      <c r="Q366" s="5" t="n"/>
+      <c r="R366" s="6" t="n"/>
+      <c r="S366" s="5" t="n"/>
+      <c r="T366" s="6" t="n"/>
+    </row>
+    <row r="367">
+      <c r="H367" s="4" t="n"/>
+      <c r="Q367" s="5" t="n"/>
+      <c r="R367" s="6" t="n"/>
+      <c r="S367" s="5" t="n"/>
+      <c r="T367" s="6" t="n"/>
+    </row>
+    <row r="368">
+      <c r="H368" s="4" t="n"/>
+      <c r="Q368" s="5" t="n"/>
+      <c r="R368" s="6" t="n"/>
+      <c r="S368" s="5" t="n"/>
+      <c r="T368" s="6" t="n"/>
+    </row>
+    <row r="369">
+      <c r="H369" s="4" t="n"/>
+      <c r="Q369" s="5" t="n"/>
+      <c r="R369" s="6" t="n"/>
+      <c r="S369" s="5" t="n"/>
+      <c r="T369" s="6" t="n"/>
+    </row>
+    <row r="370">
+      <c r="H370" s="4" t="n"/>
+      <c r="Q370" s="5" t="n"/>
+      <c r="R370" s="6" t="n"/>
+      <c r="S370" s="5" t="n"/>
+      <c r="T370" s="6" t="n"/>
+    </row>
+    <row r="371">
+      <c r="H371" s="4" t="n"/>
+      <c r="Q371" s="5" t="n"/>
+      <c r="R371" s="6" t="n"/>
+      <c r="S371" s="5" t="n"/>
+      <c r="T371" s="6" t="n"/>
+    </row>
+    <row r="372">
+      <c r="H372" s="4" t="n"/>
+      <c r="Q372" s="5" t="n"/>
+      <c r="R372" s="6" t="n"/>
+      <c r="S372" s="5" t="n"/>
+      <c r="T372" s="6" t="n"/>
+    </row>
+    <row r="373">
+      <c r="H373" s="4" t="n"/>
+      <c r="Q373" s="5" t="n"/>
+      <c r="R373" s="6" t="n"/>
+      <c r="S373" s="5" t="n"/>
+      <c r="T373" s="6" t="n"/>
+    </row>
+    <row r="374">
+      <c r="H374" s="4" t="n"/>
+      <c r="Q374" s="5" t="n"/>
+      <c r="R374" s="6" t="n"/>
+      <c r="S374" s="5" t="n"/>
+      <c r="T374" s="6" t="n"/>
+    </row>
+    <row r="375">
+      <c r="H375" s="4" t="n"/>
+      <c r="Q375" s="5" t="n"/>
+      <c r="R375" s="6" t="n"/>
+      <c r="S375" s="5" t="n"/>
+      <c r="T375" s="6" t="n"/>
+    </row>
+    <row r="376">
+      <c r="H376" s="4" t="n"/>
+      <c r="Q376" s="5" t="n"/>
+      <c r="R376" s="6" t="n"/>
+      <c r="S376" s="5" t="n"/>
+      <c r="T376" s="6" t="n"/>
+    </row>
+    <row r="377">
+      <c r="H377" s="4" t="n"/>
+      <c r="Q377" s="5" t="n"/>
+      <c r="R377" s="6" t="n"/>
+      <c r="S377" s="5" t="n"/>
+      <c r="T377" s="6" t="n"/>
+    </row>
+    <row r="378">
+      <c r="H378" s="4" t="n"/>
+      <c r="Q378" s="5" t="n"/>
+      <c r="R378" s="6" t="n"/>
+      <c r="S378" s="5" t="n"/>
+      <c r="T378" s="6" t="n"/>
+    </row>
+    <row r="379">
+      <c r="H379" s="4" t="n"/>
+      <c r="Q379" s="5" t="n"/>
+      <c r="R379" s="6" t="n"/>
+      <c r="S379" s="5" t="n"/>
+      <c r="T379" s="6" t="n"/>
+    </row>
+    <row r="380">
+      <c r="H380" s="4" t="n"/>
+      <c r="Q380" s="5" t="n"/>
+      <c r="R380" s="6" t="n"/>
+      <c r="S380" s="5" t="n"/>
+      <c r="T380" s="6" t="n"/>
+    </row>
+    <row r="381">
+      <c r="H381" s="4" t="n"/>
+      <c r="Q381" s="5" t="n"/>
+      <c r="R381" s="6" t="n"/>
+      <c r="S381" s="5" t="n"/>
+      <c r="T381" s="6" t="n"/>
+    </row>
+    <row r="382">
+      <c r="H382" s="4" t="n"/>
+      <c r="Q382" s="5" t="n"/>
+      <c r="R382" s="6" t="n"/>
+      <c r="S382" s="5" t="n"/>
+      <c r="T382" s="6" t="n"/>
+    </row>
+    <row r="383">
+      <c r="H383" s="4" t="n"/>
+      <c r="Q383" s="5" t="n"/>
+      <c r="R383" s="6" t="n"/>
+      <c r="S383" s="5" t="n"/>
+      <c r="T383" s="6" t="n"/>
+    </row>
+    <row r="384">
+      <c r="H384" s="4" t="n"/>
+      <c r="Q384" s="5" t="n"/>
+      <c r="R384" s="6" t="n"/>
+      <c r="S384" s="5" t="n"/>
+      <c r="T384" s="6" t="n"/>
+    </row>
+    <row r="385">
+      <c r="H385" s="4" t="n"/>
+      <c r="Q385" s="5" t="n"/>
+      <c r="R385" s="6" t="n"/>
+      <c r="S385" s="5" t="n"/>
+      <c r="T385" s="6" t="n"/>
+    </row>
+    <row r="386">
+      <c r="H386" s="4" t="n"/>
+      <c r="Q386" s="5" t="n"/>
+      <c r="R386" s="6" t="n"/>
+      <c r="S386" s="5" t="n"/>
+      <c r="T386" s="6" t="n"/>
+    </row>
+    <row r="387">
+      <c r="H387" s="4" t="n"/>
+      <c r="Q387" s="5" t="n"/>
+      <c r="R387" s="6" t="n"/>
+      <c r="S387" s="5" t="n"/>
+      <c r="T387" s="6" t="n"/>
+    </row>
+    <row r="388">
+      <c r="H388" s="4" t="n"/>
+      <c r="Q388" s="5" t="n"/>
+      <c r="R388" s="6" t="n"/>
+      <c r="S388" s="5" t="n"/>
+      <c r="T388" s="6" t="n"/>
+    </row>
+    <row r="389">
+      <c r="H389" s="4" t="n"/>
+      <c r="Q389" s="5" t="n"/>
+      <c r="R389" s="6" t="n"/>
+      <c r="S389" s="5" t="n"/>
+      <c r="T389" s="6" t="n"/>
+    </row>
+    <row r="390">
+      <c r="H390" s="4" t="n"/>
+      <c r="Q390" s="5" t="n"/>
+      <c r="R390" s="6" t="n"/>
+      <c r="S390" s="5" t="n"/>
+      <c r="T390" s="6" t="n"/>
+    </row>
+    <row r="391">
+      <c r="H391" s="4" t="n"/>
+      <c r="Q391" s="5" t="n"/>
+      <c r="R391" s="6" t="n"/>
+      <c r="S391" s="5" t="n"/>
+      <c r="T391" s="6" t="n"/>
+    </row>
+    <row r="392">
+      <c r="H392" s="4" t="n"/>
+      <c r="Q392" s="5" t="n"/>
+      <c r="R392" s="6" t="n"/>
+      <c r="S392" s="5" t="n"/>
+      <c r="T392" s="6" t="n"/>
+    </row>
+    <row r="393">
+      <c r="H393" s="4" t="n"/>
+      <c r="Q393" s="5" t="n"/>
+      <c r="R393" s="6" t="n"/>
+      <c r="S393" s="5" t="n"/>
+      <c r="T393" s="6" t="n"/>
+    </row>
+    <row r="394">
+      <c r="H394" s="4" t="n"/>
+      <c r="Q394" s="5" t="n"/>
+      <c r="R394" s="6" t="n"/>
+      <c r="S394" s="5" t="n"/>
+      <c r="T394" s="6" t="n"/>
+    </row>
+    <row r="395">
+      <c r="H395" s="4" t="n"/>
+      <c r="Q395" s="5" t="n"/>
+      <c r="R395" s="6" t="n"/>
+      <c r="S395" s="5" t="n"/>
+      <c r="T395" s="6" t="n"/>
+    </row>
+    <row r="396">
+      <c r="H396" s="4" t="n"/>
+      <c r="Q396" s="5" t="n"/>
+      <c r="R396" s="6" t="n"/>
+      <c r="S396" s="5" t="n"/>
+      <c r="T396" s="6" t="n"/>
+    </row>
+    <row r="397">
+      <c r="H397" s="4" t="n"/>
+      <c r="Q397" s="5" t="n"/>
+      <c r="R397" s="6" t="n"/>
+      <c r="S397" s="5" t="n"/>
+      <c r="T397" s="6" t="n"/>
+    </row>
+    <row r="398">
+      <c r="H398" s="4" t="n"/>
+      <c r="Q398" s="5" t="n"/>
+      <c r="R398" s="6" t="n"/>
+      <c r="S398" s="5" t="n"/>
+      <c r="T398" s="6" t="n"/>
+    </row>
+    <row r="399">
+      <c r="H399" s="4" t="n"/>
+      <c r="Q399" s="5" t="n"/>
+      <c r="R399" s="6" t="n"/>
+      <c r="S399" s="5" t="n"/>
+      <c r="T399" s="6" t="n"/>
+    </row>
+    <row r="400">
+      <c r="H400" s="4" t="n"/>
+      <c r="Q400" s="5" t="n"/>
+      <c r="R400" s="6" t="n"/>
+      <c r="S400" s="5" t="n"/>
+      <c r="T400" s="6" t="n"/>
+    </row>
+    <row r="401">
+      <c r="H401" s="4" t="n"/>
+      <c r="Q401" s="5" t="n"/>
+      <c r="R401" s="6" t="n"/>
+      <c r="S401" s="5" t="n"/>
+      <c r="T401" s="6" t="n"/>
+    </row>
+    <row r="402">
+      <c r="H402" s="4" t="n"/>
+      <c r="Q402" s="5" t="n"/>
+      <c r="R402" s="6" t="n"/>
+      <c r="S402" s="5" t="n"/>
+      <c r="T402" s="6" t="n"/>
+    </row>
+    <row r="403">
+      <c r="H403" s="4" t="n"/>
+      <c r="Q403" s="5" t="n"/>
+      <c r="R403" s="6" t="n"/>
+      <c r="S403" s="5" t="n"/>
+      <c r="T403" s="6" t="n"/>
+    </row>
+    <row r="404">
+      <c r="H404" s="4" t="n"/>
+      <c r="Q404" s="5" t="n"/>
+      <c r="R404" s="6" t="n"/>
+      <c r="S404" s="5" t="n"/>
+      <c r="T404" s="6" t="n"/>
+    </row>
+    <row r="405">
+      <c r="H405" s="4" t="n"/>
+      <c r="Q405" s="5" t="n"/>
+      <c r="R405" s="6" t="n"/>
+      <c r="S405" s="5" t="n"/>
+      <c r="T405" s="6" t="n"/>
+    </row>
+    <row r="406">
+      <c r="H406" s="4" t="n"/>
+      <c r="Q406" s="5" t="n"/>
+      <c r="R406" s="6" t="n"/>
+      <c r="S406" s="5" t="n"/>
+      <c r="T406" s="6" t="n"/>
+    </row>
+    <row r="407">
+      <c r="H407" s="4" t="n"/>
+      <c r="Q407" s="5" t="n"/>
+      <c r="R407" s="6" t="n"/>
+      <c r="S407" s="5" t="n"/>
+      <c r="T407" s="6" t="n"/>
+    </row>
+    <row r="408">
+      <c r="H408" s="4" t="n"/>
+      <c r="Q408" s="5" t="n"/>
+      <c r="R408" s="6" t="n"/>
+      <c r="S408" s="5" t="n"/>
+      <c r="T408" s="6" t="n"/>
+    </row>
+    <row r="409">
+      <c r="H409" s="4" t="n"/>
+      <c r="Q409" s="5" t="n"/>
+      <c r="R409" s="6" t="n"/>
+      <c r="S409" s="5" t="n"/>
+      <c r="T409" s="6" t="n"/>
+    </row>
+    <row r="410">
+      <c r="H410" s="4" t="n"/>
+      <c r="Q410" s="5" t="n"/>
+      <c r="R410" s="6" t="n"/>
+      <c r="S410" s="5" t="n"/>
+      <c r="T410" s="6" t="n"/>
+    </row>
+    <row r="411">
+      <c r="H411" s="4" t="n"/>
+      <c r="Q411" s="5" t="n"/>
+      <c r="R411" s="6" t="n"/>
+      <c r="S411" s="5" t="n"/>
+      <c r="T411" s="6" t="n"/>
+    </row>
+    <row r="412">
+      <c r="H412" s="4" t="n"/>
+      <c r="Q412" s="5" t="n"/>
+      <c r="R412" s="6" t="n"/>
+      <c r="S412" s="5" t="n"/>
+      <c r="T412" s="6" t="n"/>
+    </row>
+    <row r="413">
+      <c r="H413" s="4" t="n"/>
+      <c r="Q413" s="5" t="n"/>
+      <c r="R413" s="6" t="n"/>
+      <c r="S413" s="5" t="n"/>
+      <c r="T413" s="6" t="n"/>
+    </row>
+    <row r="414">
+      <c r="H414" s="4" t="n"/>
+      <c r="Q414" s="5" t="n"/>
+      <c r="R414" s="6" t="n"/>
+      <c r="S414" s="5" t="n"/>
+      <c r="T414" s="6" t="n"/>
+    </row>
+    <row r="415">
+      <c r="H415" s="4" t="n"/>
+      <c r="Q415" s="5" t="n"/>
+      <c r="R415" s="6" t="n"/>
+      <c r="S415" s="5" t="n"/>
+      <c r="T415" s="6" t="n"/>
+    </row>
+    <row r="416">
+      <c r="H416" s="4" t="n"/>
+      <c r="Q416" s="5" t="n"/>
+      <c r="R416" s="6" t="n"/>
+      <c r="S416" s="5" t="n"/>
+      <c r="T416" s="6" t="n"/>
+    </row>
+    <row r="417">
+      <c r="H417" s="4" t="n"/>
+      <c r="Q417" s="5" t="n"/>
+      <c r="R417" s="6" t="n"/>
+      <c r="S417" s="5" t="n"/>
+      <c r="T417" s="6" t="n"/>
+    </row>
+    <row r="418">
+      <c r="H418" s="4" t="n"/>
+      <c r="Q418" s="5" t="n"/>
+      <c r="R418" s="6" t="n"/>
+      <c r="S418" s="5" t="n"/>
+      <c r="T418" s="6" t="n"/>
+    </row>
+    <row r="419">
+      <c r="H419" s="4" t="n"/>
+      <c r="Q419" s="5" t="n"/>
+      <c r="R419" s="6" t="n"/>
+      <c r="S419" s="5" t="n"/>
+      <c r="T419" s="6" t="n"/>
+    </row>
+    <row r="420">
+      <c r="H420" s="4" t="n"/>
+      <c r="Q420" s="5" t="n"/>
+      <c r="R420" s="6" t="n"/>
+      <c r="S420" s="5" t="n"/>
+      <c r="T420" s="6" t="n"/>
+    </row>
+    <row r="421">
+      <c r="H421" s="4" t="n"/>
+      <c r="Q421" s="5" t="n"/>
+      <c r="R421" s="6" t="n"/>
+      <c r="S421" s="5" t="n"/>
+      <c r="T421" s="6" t="n"/>
+    </row>
+    <row r="422">
+      <c r="H422" s="4" t="n"/>
+      <c r="Q422" s="5" t="n"/>
+      <c r="R422" s="6" t="n"/>
+      <c r="S422" s="5" t="n"/>
+      <c r="T422" s="6" t="n"/>
+    </row>
+    <row r="423">
+      <c r="H423" s="4" t="n"/>
+      <c r="Q423" s="5" t="n"/>
+      <c r="R423" s="6" t="n"/>
+      <c r="S423" s="5" t="n"/>
+      <c r="T423" s="6" t="n"/>
+    </row>
+    <row r="424">
+      <c r="H424" s="4" t="n"/>
+      <c r="Q424" s="5" t="n"/>
+      <c r="R424" s="6" t="n"/>
+      <c r="S424" s="5" t="n"/>
+      <c r="T424" s="6" t="n"/>
+    </row>
+    <row r="425">
+      <c r="H425" s="4" t="n"/>
+      <c r="Q425" s="5" t="n"/>
+      <c r="R425" s="6" t="n"/>
+      <c r="S425" s="5" t="n"/>
+      <c r="T425" s="6" t="n"/>
+    </row>
+    <row r="426">
+      <c r="H426" s="4" t="n"/>
+      <c r="Q426" s="5" t="n"/>
+      <c r="R426" s="6" t="n"/>
+      <c r="S426" s="5" t="n"/>
+      <c r="T426" s="6" t="n"/>
+    </row>
+    <row r="427">
+      <c r="H427" s="4" t="n"/>
+      <c r="Q427" s="5" t="n"/>
+      <c r="R427" s="6" t="n"/>
+      <c r="S427" s="5" t="n"/>
+      <c r="T427" s="6" t="n"/>
+    </row>
+    <row r="428">
+      <c r="H428" s="4" t="n"/>
+      <c r="Q428" s="5" t="n"/>
+      <c r="R428" s="6" t="n"/>
+      <c r="S428" s="5" t="n"/>
+      <c r="T428" s="6" t="n"/>
+    </row>
+    <row r="429">
+      <c r="H429" s="4" t="n"/>
+      <c r="Q429" s="5" t="n"/>
+      <c r="R429" s="6" t="n"/>
+      <c r="S429" s="5" t="n"/>
+      <c r="T429" s="6" t="n"/>
+    </row>
+    <row r="430">
+      <c r="H430" s="4" t="n"/>
+      <c r="Q430" s="5" t="n"/>
+      <c r="R430" s="6" t="n"/>
+      <c r="S430" s="5" t="n"/>
+      <c r="T430" s="6" t="n"/>
+    </row>
+    <row r="431">
+      <c r="H431" s="4" t="n"/>
+      <c r="Q431" s="5" t="n"/>
+      <c r="R431" s="6" t="n"/>
+      <c r="S431" s="5" t="n"/>
+      <c r="T431" s="6" t="n"/>
+    </row>
+    <row r="432">
+      <c r="H432" s="4" t="n"/>
+      <c r="Q432" s="5" t="n"/>
+      <c r="R432" s="6" t="n"/>
+      <c r="S432" s="5" t="n"/>
+      <c r="T432" s="6" t="n"/>
+    </row>
+    <row r="433">
+      <c r="H433" s="4" t="n"/>
+      <c r="Q433" s="5" t="n"/>
+      <c r="R433" s="6" t="n"/>
+      <c r="S433" s="5" t="n"/>
+      <c r="T433" s="6" t="n"/>
+    </row>
+    <row r="434">
+      <c r="H434" s="4" t="n"/>
+      <c r="Q434" s="5" t="n"/>
+      <c r="R434" s="6" t="n"/>
+      <c r="S434" s="5" t="n"/>
+      <c r="T434" s="6" t="n"/>
+    </row>
+    <row r="435">
+      <c r="H435" s="4" t="n"/>
+      <c r="Q435" s="5" t="n"/>
+      <c r="R435" s="6" t="n"/>
+      <c r="S435" s="5" t="n"/>
+      <c r="T435" s="6" t="n"/>
+    </row>
+    <row r="436">
+      <c r="H436" s="4" t="n"/>
+      <c r="Q436" s="5" t="n"/>
+      <c r="R436" s="6" t="n"/>
+      <c r="S436" s="5" t="n"/>
+      <c r="T436" s="6" t="n"/>
+    </row>
+    <row r="437">
+      <c r="H437" s="4" t="n"/>
+      <c r="Q437" s="5" t="n"/>
+      <c r="R437" s="6" t="n"/>
+      <c r="S437" s="5" t="n"/>
+      <c r="T437" s="6" t="n"/>
+    </row>
+    <row r="438">
+      <c r="H438" s="4" t="n"/>
+      <c r="Q438" s="5" t="n"/>
+      <c r="R438" s="6" t="n"/>
+      <c r="S438" s="5" t="n"/>
+      <c r="T438" s="6" t="n"/>
+    </row>
+    <row r="439">
+      <c r="H439" s="4" t="n"/>
+      <c r="Q439" s="5" t="n"/>
+      <c r="R439" s="6" t="n"/>
+      <c r="S439" s="5" t="n"/>
+      <c r="T439" s="6" t="n"/>
+    </row>
+    <row r="440">
+      <c r="H440" s="4" t="n"/>
+      <c r="Q440" s="5" t="n"/>
+      <c r="R440" s="6" t="n"/>
+      <c r="S440" s="5" t="n"/>
+      <c r="T440" s="6" t="n"/>
+    </row>
+    <row r="441">
+      <c r="H441" s="4" t="n"/>
+      <c r="Q441" s="5" t="n"/>
+      <c r="R441" s="6" t="n"/>
+      <c r="S441" s="5" t="n"/>
+      <c r="T441" s="6" t="n"/>
+    </row>
+    <row r="442">
+      <c r="H442" s="4" t="n"/>
+      <c r="Q442" s="5" t="n"/>
+      <c r="R442" s="6" t="n"/>
+      <c r="S442" s="5" t="n"/>
+      <c r="T442" s="6" t="n"/>
+    </row>
+    <row r="443">
+      <c r="H443" s="4" t="n"/>
+      <c r="Q443" s="5" t="n"/>
+      <c r="R443" s="6" t="n"/>
+      <c r="S443" s="5" t="n"/>
+      <c r="T443" s="6" t="n"/>
+    </row>
+    <row r="444">
+      <c r="H444" s="4" t="n"/>
+      <c r="Q444" s="5" t="n"/>
+      <c r="R444" s="6" t="n"/>
+      <c r="S444" s="5" t="n"/>
+      <c r="T444" s="6" t="n"/>
+    </row>
+    <row r="445">
+      <c r="H445" s="4" t="n"/>
+      <c r="Q445" s="5" t="n"/>
+      <c r="R445" s="6" t="n"/>
+      <c r="S445" s="5" t="n"/>
+      <c r="T445" s="6" t="n"/>
+    </row>
+    <row r="446">
+      <c r="H446" s="4" t="n"/>
+      <c r="Q446" s="5" t="n"/>
+      <c r="R446" s="6" t="n"/>
+      <c r="S446" s="5" t="n"/>
+      <c r="T446" s="6" t="n"/>
+    </row>
+    <row r="447">
+      <c r="H447" s="4" t="n"/>
+      <c r="Q447" s="5" t="n"/>
+      <c r="R447" s="6" t="n"/>
+      <c r="S447" s="5" t="n"/>
+      <c r="T447" s="6" t="n"/>
+    </row>
+    <row r="448">
+      <c r="H448" s="4" t="n"/>
+      <c r="Q448" s="5" t="n"/>
+      <c r="R448" s="6" t="n"/>
+      <c r="S448" s="5" t="n"/>
+      <c r="T448" s="6" t="n"/>
+    </row>
+    <row r="449">
+      <c r="H449" s="4" t="n"/>
+      <c r="Q449" s="5" t="n"/>
+      <c r="R449" s="6" t="n"/>
+      <c r="S449" s="5" t="n"/>
+      <c r="T449" s="6" t="n"/>
+    </row>
+    <row r="450">
+      <c r="H450" s="4" t="n"/>
+      <c r="Q450" s="5" t="n"/>
+      <c r="R450" s="6" t="n"/>
+      <c r="S450" s="5" t="n"/>
+      <c r="T450" s="6" t="n"/>
+    </row>
+    <row r="451">
+      <c r="H451" s="4" t="n"/>
+      <c r="Q451" s="5" t="n"/>
+      <c r="R451" s="6" t="n"/>
+      <c r="S451" s="5" t="n"/>
+      <c r="T451" s="6" t="n"/>
+    </row>
+    <row r="452">
+      <c r="H452" s="4" t="n"/>
+      <c r="Q452" s="5" t="n"/>
+      <c r="R452" s="6" t="n"/>
+      <c r="S452" s="5" t="n"/>
+      <c r="T452" s="6" t="n"/>
+    </row>
+    <row r="453">
+      <c r="H453" s="4" t="n"/>
+      <c r="Q453" s="5" t="n"/>
+      <c r="R453" s="6" t="n"/>
+      <c r="S453" s="5" t="n"/>
+      <c r="T453" s="6" t="n"/>
+    </row>
+    <row r="454">
+      <c r="H454" s="4" t="n"/>
+      <c r="Q454" s="5" t="n"/>
+      <c r="R454" s="6" t="n"/>
+      <c r="S454" s="5" t="n"/>
+      <c r="T454" s="6" t="n"/>
+    </row>
+    <row r="455">
+      <c r="H455" s="4" t="n"/>
+      <c r="Q455" s="5" t="n"/>
+      <c r="R455" s="6" t="n"/>
+      <c r="S455" s="5" t="n"/>
+      <c r="T455" s="6" t="n"/>
+    </row>
+    <row r="456">
+      <c r="H456" s="4" t="n"/>
+      <c r="Q456" s="5" t="n"/>
+      <c r="R456" s="6" t="n"/>
+      <c r="S456" s="5" t="n"/>
+      <c r="T456" s="6" t="n"/>
+    </row>
+    <row r="457">
+      <c r="H457" s="4" t="n"/>
+      <c r="Q457" s="5" t="n"/>
+      <c r="R457" s="6" t="n"/>
+      <c r="S457" s="5" t="n"/>
+      <c r="T457" s="6" t="n"/>
+    </row>
+    <row r="458">
+      <c r="H458" s="4" t="n"/>
+      <c r="Q458" s="5" t="n"/>
+      <c r="R458" s="6" t="n"/>
+      <c r="S458" s="5" t="n"/>
+      <c r="T458" s="6" t="n"/>
+    </row>
+    <row r="459">
+      <c r="H459" s="4" t="n"/>
+      <c r="Q459" s="5" t="n"/>
+      <c r="R459" s="6" t="n"/>
+      <c r="S459" s="5" t="n"/>
+      <c r="T459" s="6" t="n"/>
+    </row>
+    <row r="460">
+      <c r="H460" s="4" t="n"/>
+      <c r="Q460" s="5" t="n"/>
+      <c r="R460" s="6" t="n"/>
+      <c r="S460" s="5" t="n"/>
+      <c r="T460" s="6" t="n"/>
+    </row>
+    <row r="461">
+      <c r="H461" s="4" t="n"/>
+      <c r="Q461" s="5" t="n"/>
+      <c r="R461" s="6" t="n"/>
+      <c r="S461" s="5" t="n"/>
+      <c r="T461" s="6" t="n"/>
+    </row>
+    <row r="462">
+      <c r="H462" s="4" t="n"/>
+      <c r="Q462" s="5" t="n"/>
+      <c r="R462" s="6" t="n"/>
+      <c r="S462" s="5" t="n"/>
+      <c r="T462" s="6" t="n"/>
+    </row>
+    <row r="463">
+      <c r="H463" s="4" t="n"/>
+      <c r="Q463" s="5" t="n"/>
+      <c r="R463" s="6" t="n"/>
+      <c r="S463" s="5" t="n"/>
+      <c r="T463" s="6" t="n"/>
+    </row>
+    <row r="464">
+      <c r="H464" s="4" t="n"/>
+      <c r="Q464" s="5" t="n"/>
+      <c r="R464" s="6" t="n"/>
+      <c r="S464" s="5" t="n"/>
+      <c r="T464" s="6" t="n"/>
+    </row>
+    <row r="465">
+      <c r="H465" s="4" t="n"/>
+      <c r="Q465" s="5" t="n"/>
+      <c r="R465" s="6" t="n"/>
+      <c r="S465" s="5" t="n"/>
+      <c r="T465" s="6" t="n"/>
+    </row>
+    <row r="466">
+      <c r="H466" s="4" t="n"/>
+      <c r="Q466" s="5" t="n"/>
+      <c r="R466" s="6" t="n"/>
+      <c r="S466" s="5" t="n"/>
+      <c r="T466" s="6" t="n"/>
+    </row>
+    <row r="467">
+      <c r="H467" s="4" t="n"/>
+      <c r="Q467" s="5" t="n"/>
+      <c r="R467" s="6" t="n"/>
+      <c r="S467" s="5" t="n"/>
+      <c r="T467" s="6" t="n"/>
+    </row>
+    <row r="468">
+      <c r="H468" s="4" t="n"/>
+      <c r="Q468" s="5" t="n"/>
+      <c r="R468" s="6" t="n"/>
+      <c r="S468" s="5" t="n"/>
+      <c r="T468" s="6" t="n"/>
+    </row>
+    <row r="469">
+      <c r="H469" s="4" t="n"/>
+      <c r="Q469" s="5" t="n"/>
+      <c r="R469" s="6" t="n"/>
+      <c r="S469" s="5" t="n"/>
+      <c r="T469" s="6" t="n"/>
+    </row>
+    <row r="470">
+      <c r="H470" s="4" t="n"/>
+      <c r="Q470" s="5" t="n"/>
+      <c r="R470" s="6" t="n"/>
+      <c r="S470" s="5" t="n"/>
+      <c r="T470" s="6" t="n"/>
+    </row>
+    <row r="471">
+      <c r="H471" s="4" t="n"/>
+      <c r="Q471" s="5" t="n"/>
+      <c r="R471" s="6" t="n"/>
+      <c r="S471" s="5" t="n"/>
+      <c r="T471" s="6" t="n"/>
+    </row>
+    <row r="472">
+      <c r="H472" s="4" t="n"/>
+      <c r="Q472" s="5" t="n"/>
+      <c r="R472" s="6" t="n"/>
+      <c r="S472" s="5" t="n"/>
+      <c r="T472" s="6" t="n"/>
+    </row>
+    <row r="473">
+      <c r="H473" s="4" t="n"/>
+      <c r="Q473" s="5" t="n"/>
+      <c r="R473" s="6" t="n"/>
+      <c r="S473" s="5" t="n"/>
+      <c r="T473" s="6" t="n"/>
+    </row>
+    <row r="474">
+      <c r="H474" s="4" t="n"/>
+      <c r="Q474" s="5" t="n"/>
+      <c r="R474" s="6" t="n"/>
+      <c r="S474" s="5" t="n"/>
+      <c r="T474" s="6" t="n"/>
+    </row>
+    <row r="475">
+      <c r="H475" s="4" t="n"/>
+      <c r="Q475" s="5" t="n"/>
+      <c r="R475" s="6" t="n"/>
+      <c r="S475" s="5" t="n"/>
+      <c r="T475" s="6" t="n"/>
+    </row>
+    <row r="476">
+      <c r="H476" s="4" t="n"/>
+      <c r="Q476" s="5" t="n"/>
+      <c r="R476" s="6" t="n"/>
+      <c r="S476" s="5" t="n"/>
+      <c r="T476" s="6" t="n"/>
+    </row>
+    <row r="477">
+      <c r="H477" s="4" t="n"/>
+      <c r="Q477" s="5" t="n"/>
+      <c r="R477" s="6" t="n"/>
+      <c r="S477" s="5" t="n"/>
+      <c r="T477" s="6" t="n"/>
+    </row>
+    <row r="478">
+      <c r="H478" s="4" t="n"/>
+      <c r="Q478" s="5" t="n"/>
+      <c r="R478" s="6" t="n"/>
+      <c r="S478" s="5" t="n"/>
+      <c r="T478" s="6" t="n"/>
+    </row>
+    <row r="479">
+      <c r="H479" s="4" t="n"/>
+      <c r="Q479" s="5" t="n"/>
+      <c r="R479" s="6" t="n"/>
+      <c r="S479" s="5" t="n"/>
+      <c r="T479" s="6" t="n"/>
+    </row>
+    <row r="480">
+      <c r="H480" s="4" t="n"/>
+      <c r="Q480" s="5" t="n"/>
+      <c r="R480" s="6" t="n"/>
+      <c r="S480" s="5" t="n"/>
+      <c r="T480" s="6" t="n"/>
+    </row>
+    <row r="481">
+      <c r="H481" s="4" t="n"/>
+      <c r="Q481" s="5" t="n"/>
+      <c r="R481" s="6" t="n"/>
+      <c r="S481" s="5" t="n"/>
+      <c r="T481" s="6" t="n"/>
+    </row>
+    <row r="482">
+      <c r="H482" s="4" t="n"/>
+      <c r="Q482" s="5" t="n"/>
+      <c r="R482" s="6" t="n"/>
+      <c r="S482" s="5" t="n"/>
+      <c r="T482" s="6" t="n"/>
+    </row>
+    <row r="483">
+      <c r="H483" s="4" t="n"/>
+      <c r="Q483" s="5" t="n"/>
+      <c r="R483" s="6" t="n"/>
+      <c r="S483" s="5" t="n"/>
+      <c r="T483" s="6" t="n"/>
+    </row>
+    <row r="484">
+      <c r="H484" s="4" t="n"/>
+      <c r="Q484" s="5" t="n"/>
+      <c r="R484" s="6" t="n"/>
+      <c r="S484" s="5" t="n"/>
+      <c r="T484" s="6" t="n"/>
+    </row>
+    <row r="485">
+      <c r="H485" s="4" t="n"/>
+      <c r="Q485" s="5" t="n"/>
+      <c r="R485" s="6" t="n"/>
+      <c r="S485" s="5" t="n"/>
+      <c r="T485" s="6" t="n"/>
+    </row>
+    <row r="486">
+      <c r="H486" s="4" t="n"/>
+      <c r="Q486" s="5" t="n"/>
+      <c r="R486" s="6" t="n"/>
+      <c r="S486" s="5" t="n"/>
+      <c r="T486" s="6" t="n"/>
+    </row>
+    <row r="487">
+      <c r="H487" s="4" t="n"/>
+      <c r="Q487" s="5" t="n"/>
+      <c r="R487" s="6" t="n"/>
+      <c r="S487" s="5" t="n"/>
+      <c r="T487" s="6" t="n"/>
+    </row>
+    <row r="488">
+      <c r="H488" s="4" t="n"/>
+      <c r="Q488" s="5" t="n"/>
+      <c r="R488" s="6" t="n"/>
+      <c r="S488" s="5" t="n"/>
+      <c r="T488" s="6" t="n"/>
+    </row>
+    <row r="489">
+      <c r="H489" s="4" t="n"/>
+      <c r="Q489" s="5" t="n"/>
+      <c r="R489" s="6" t="n"/>
+      <c r="S489" s="5" t="n"/>
+      <c r="T489" s="6" t="n"/>
+    </row>
+    <row r="490">
+      <c r="H490" s="4" t="n"/>
+      <c r="Q490" s="5" t="n"/>
+      <c r="R490" s="6" t="n"/>
+      <c r="S490" s="5" t="n"/>
+      <c r="T490" s="6" t="n"/>
+    </row>
+    <row r="491">
+      <c r="H491" s="4" t="n"/>
+      <c r="Q491" s="5" t="n"/>
+      <c r="R491" s="6" t="n"/>
+      <c r="S491" s="5" t="n"/>
+      <c r="T491" s="6" t="n"/>
+    </row>
+    <row r="492">
+      <c r="H492" s="4" t="n"/>
+      <c r="Q492" s="5" t="n"/>
+      <c r="R492" s="6" t="n"/>
+      <c r="S492" s="5" t="n"/>
+      <c r="T492" s="6" t="n"/>
+    </row>
+    <row r="493">
+      <c r="H493" s="4" t="n"/>
+      <c r="Q493" s="5" t="n"/>
+      <c r="R493" s="6" t="n"/>
+      <c r="S493" s="5" t="n"/>
+      <c r="T493" s="6" t="n"/>
+    </row>
+    <row r="494">
+      <c r="H494" s="4" t="n"/>
+      <c r="Q494" s="5" t="n"/>
+      <c r="R494" s="6" t="n"/>
+      <c r="S494" s="5" t="n"/>
+      <c r="T494" s="6" t="n"/>
+    </row>
+    <row r="495">
+      <c r="H495" s="4" t="n"/>
+      <c r="Q495" s="5" t="n"/>
+      <c r="R495" s="6" t="n"/>
+      <c r="S495" s="5" t="n"/>
+      <c r="T495" s="6" t="n"/>
+    </row>
+    <row r="496">
+      <c r="H496" s="4" t="n"/>
+      <c r="Q496" s="5" t="n"/>
+      <c r="R496" s="6" t="n"/>
+      <c r="S496" s="5" t="n"/>
+      <c r="T496" s="6" t="n"/>
+    </row>
+    <row r="497">
+      <c r="H497" s="4" t="n"/>
+      <c r="Q497" s="5" t="n"/>
+      <c r="R497" s="6" t="n"/>
+      <c r="S497" s="5" t="n"/>
+      <c r="T497" s="6" t="n"/>
+    </row>
+    <row r="498">
+      <c r="H498" s="4" t="n"/>
+      <c r="Q498" s="5" t="n"/>
+      <c r="R498" s="6" t="n"/>
+      <c r="S498" s="5" t="n"/>
+      <c r="T498" s="6" t="n"/>
+    </row>
+    <row r="499">
+      <c r="H499" s="4" t="n"/>
+      <c r="Q499" s="5" t="n"/>
+      <c r="R499" s="6" t="n"/>
+      <c r="S499" s="5" t="n"/>
+      <c r="T499" s="6" t="n"/>
+    </row>
+    <row r="500">
+      <c r="H500" s="4" t="n"/>
+      <c r="Q500" s="5" t="n"/>
+      <c r="R500" s="6" t="n"/>
+      <c r="S500" s="5" t="n"/>
+      <c r="T500" s="6" t="n"/>
+    </row>
+    <row r="501">
+      <c r="H501" s="4" t="n"/>
+      <c r="Q501" s="5" t="n"/>
+      <c r="R501" s="6" t="n"/>
+      <c r="S501" s="5" t="n"/>
+      <c r="T501" s="6" t="n"/>
+    </row>
+    <row r="502">
+      <c r="H502" s="4" t="n"/>
+      <c r="Q502" s="5" t="n"/>
+      <c r="R502" s="6" t="n"/>
+      <c r="S502" s="5" t="n"/>
+      <c r="T502" s="6" t="n"/>
+    </row>
+    <row r="503">
+      <c r="H503" s="4" t="n"/>
+      <c r="Q503" s="5" t="n"/>
+      <c r="R503" s="6" t="n"/>
+      <c r="S503" s="5" t="n"/>
+      <c r="T503" s="6" t="n"/>
+    </row>
+    <row r="504">
+      <c r="H504" s="4" t="n"/>
+      <c r="Q504" s="5" t="n"/>
+      <c r="R504" s="6" t="n"/>
+      <c r="S504" s="5" t="n"/>
+      <c r="T504" s="6" t="n"/>
+    </row>
+    <row r="505">
+      <c r="H505" s="4" t="n"/>
+      <c r="Q505" s="5" t="n"/>
+      <c r="R505" s="6" t="n"/>
+      <c r="S505" s="5" t="n"/>
+      <c r="T505" s="6" t="n"/>
+    </row>
+    <row r="506">
+      <c r="H506" s="4" t="n"/>
+      <c r="Q506" s="5" t="n"/>
+      <c r="R506" s="6" t="n"/>
+      <c r="S506" s="5" t="n"/>
+      <c r="T506" s="6" t="n"/>
+    </row>
+    <row r="507">
+      <c r="H507" s="4" t="n"/>
+      <c r="Q507" s="5" t="n"/>
+      <c r="R507" s="6" t="n"/>
+      <c r="S507" s="5" t="n"/>
+      <c r="T507" s="6" t="n"/>
+    </row>
+    <row r="508">
+      <c r="H508" s="4" t="n"/>
+      <c r="Q508" s="5" t="n"/>
+      <c r="R508" s="6" t="n"/>
+      <c r="S508" s="5" t="n"/>
+      <c r="T508" s="6" t="n"/>
+    </row>
+    <row r="509">
+      <c r="H509" s="4" t="n"/>
+      <c r="Q509" s="5" t="n"/>
+      <c r="R509" s="6" t="n"/>
+      <c r="S509" s="5" t="n"/>
+      <c r="T509" s="6" t="n"/>
+    </row>
+    <row r="510">
+      <c r="H510" s="4" t="n"/>
+      <c r="Q510" s="5" t="n"/>
+      <c r="R510" s="6" t="n"/>
+      <c r="S510" s="5" t="n"/>
+      <c r="T510" s="6" t="n"/>
+    </row>
+    <row r="511">
+      <c r="H511" s="4" t="n"/>
+      <c r="Q511" s="5" t="n"/>
+      <c r="R511" s="6" t="n"/>
+      <c r="S511" s="5" t="n"/>
+      <c r="T511" s="6" t="n"/>
+    </row>
+    <row r="512">
+      <c r="H512" s="4" t="n"/>
+      <c r="Q512" s="5" t="n"/>
+      <c r="R512" s="6" t="n"/>
+      <c r="S512" s="5" t="n"/>
+      <c r="T512" s="6" t="n"/>
+    </row>
+    <row r="513">
+      <c r="H513" s="4" t="n"/>
+      <c r="Q513" s="5" t="n"/>
+      <c r="R513" s="6" t="n"/>
+      <c r="S513" s="5" t="n"/>
+      <c r="T513" s="6" t="n"/>
+    </row>
+    <row r="514">
+      <c r="H514" s="4" t="n"/>
+      <c r="Q514" s="5" t="n"/>
+      <c r="R514" s="6" t="n"/>
+      <c r="S514" s="5" t="n"/>
+      <c r="T514" s="6" t="n"/>
+    </row>
+    <row r="515">
+      <c r="H515" s="4" t="n"/>
+      <c r="Q515" s="5" t="n"/>
+      <c r="R515" s="6" t="n"/>
+      <c r="S515" s="5" t="n"/>
+      <c r="T515" s="6" t="n"/>
+    </row>
+    <row r="516">
+      <c r="H516" s="4" t="n"/>
+      <c r="Q516" s="5" t="n"/>
+      <c r="R516" s="6" t="n"/>
+      <c r="S516" s="5" t="n"/>
+      <c r="T516" s="6" t="n"/>
+    </row>
+    <row r="517">
+      <c r="H517" s="4" t="n"/>
+      <c r="Q517" s="5" t="n"/>
+      <c r="R517" s="6" t="n"/>
+      <c r="S517" s="5" t="n"/>
+      <c r="T517" s="6" t="n"/>
+    </row>
+    <row r="518">
+      <c r="H518" s="4" t="n"/>
+      <c r="Q518" s="5" t="n"/>
+      <c r="R518" s="6" t="n"/>
+      <c r="S518" s="5" t="n"/>
+      <c r="T518" s="6" t="n"/>
+    </row>
+    <row r="519">
+      <c r="H519" s="4" t="n"/>
+      <c r="Q519" s="5" t="n"/>
+      <c r="R519" s="6" t="n"/>
+      <c r="S519" s="5" t="n"/>
+      <c r="T519" s="6" t="n"/>
+    </row>
+    <row r="520">
+      <c r="H520" s="4" t="n"/>
+      <c r="Q520" s="5" t="n"/>
+      <c r="R520" s="6" t="n"/>
+      <c r="S520" s="5" t="n"/>
+      <c r="T520" s="6" t="n"/>
+    </row>
+    <row r="521">
+      <c r="H521" s="4" t="n"/>
+      <c r="Q521" s="5" t="n"/>
+      <c r="R521" s="6" t="n"/>
+      <c r="S521" s="5" t="n"/>
+      <c r="T521" s="6" t="n"/>
+    </row>
+    <row r="522">
+      <c r="H522" s="4" t="n"/>
+      <c r="Q522" s="5" t="n"/>
+      <c r="R522" s="6" t="n"/>
+      <c r="S522" s="5" t="n"/>
+      <c r="T522" s="6" t="n"/>
+    </row>
+    <row r="523">
+      <c r="H523" s="4" t="n"/>
+      <c r="Q523" s="5" t="n"/>
+      <c r="R523" s="6" t="n"/>
+      <c r="S523" s="5" t="n"/>
+      <c r="T523" s="6" t="n"/>
+    </row>
+    <row r="524">
+      <c r="H524" s="4" t="n"/>
+      <c r="Q524" s="5" t="n"/>
+      <c r="R524" s="6" t="n"/>
+      <c r="S524" s="5" t="n"/>
+      <c r="T524" s="6" t="n"/>
+    </row>
+    <row r="525">
+      <c r="H525" s="4" t="n"/>
+      <c r="Q525" s="5" t="n"/>
+      <c r="R525" s="6" t="n"/>
+      <c r="S525" s="5" t="n"/>
+      <c r="T525" s="6" t="n"/>
+    </row>
+    <row r="526">
+      <c r="H526" s="4" t="n"/>
+      <c r="Q526" s="5" t="n"/>
+      <c r="R526" s="6" t="n"/>
+      <c r="S526" s="5" t="n"/>
+      <c r="T526" s="6" t="n"/>
+    </row>
+    <row r="527">
+      <c r="H527" s="4" t="n"/>
+      <c r="Q527" s="5" t="n"/>
+      <c r="R527" s="6" t="n"/>
+      <c r="S527" s="5" t="n"/>
+      <c r="T527" s="6" t="n"/>
+    </row>
+    <row r="528">
+      <c r="H528" s="4" t="n"/>
+      <c r="Q528" s="5" t="n"/>
+      <c r="R528" s="6" t="n"/>
+      <c r="S528" s="5" t="n"/>
+      <c r="T528" s="6" t="n"/>
+    </row>
+    <row r="529">
+      <c r="H529" s="4" t="n"/>
+      <c r="Q529" s="5" t="n"/>
+      <c r="R529" s="6" t="n"/>
+      <c r="S529" s="5" t="n"/>
+      <c r="T529" s="6" t="n"/>
+    </row>
+    <row r="530">
+      <c r="H530" s="4" t="n"/>
+      <c r="Q530" s="5" t="n"/>
+      <c r="R530" s="6" t="n"/>
+      <c r="S530" s="5" t="n"/>
+      <c r="T530" s="6" t="n"/>
+    </row>
+    <row r="531">
+      <c r="H531" s="4" t="n"/>
+      <c r="Q531" s="5" t="n"/>
+      <c r="R531" s="6" t="n"/>
+      <c r="S531" s="5" t="n"/>
+      <c r="T531" s="6" t="n"/>
+    </row>
+    <row r="532">
+      <c r="H532" s="4" t="n"/>
+      <c r="Q532" s="5" t="n"/>
+      <c r="R532" s="6" t="n"/>
+      <c r="S532" s="5" t="n"/>
+      <c r="T532" s="6" t="n"/>
+    </row>
+    <row r="533">
+      <c r="H533" s="4" t="n"/>
+      <c r="Q533" s="5" t="n"/>
+      <c r="R533" s="6" t="n"/>
+      <c r="S533" s="5" t="n"/>
+      <c r="T533" s="6" t="n"/>
+    </row>
+    <row r="534">
+      <c r="H534" s="4" t="n"/>
+      <c r="Q534" s="5" t="n"/>
+      <c r="R534" s="6" t="n"/>
+      <c r="S534" s="5" t="n"/>
+      <c r="T534" s="6" t="n"/>
+    </row>
+    <row r="535">
+      <c r="H535" s="4" t="n"/>
+      <c r="Q535" s="5" t="n"/>
+      <c r="R535" s="6" t="n"/>
+      <c r="S535" s="5" t="n"/>
+      <c r="T535" s="6" t="n"/>
+    </row>
+    <row r="536">
+      <c r="H536" s="4" t="n"/>
+      <c r="Q536" s="5" t="n"/>
+      <c r="R536" s="6" t="n"/>
+      <c r="S536" s="5" t="n"/>
+      <c r="T536" s="6" t="n"/>
+    </row>
+    <row r="537">
+      <c r="H537" s="4" t="n"/>
+      <c r="Q537" s="5" t="n"/>
+      <c r="R537" s="6" t="n"/>
+      <c r="S537" s="5" t="n"/>
+      <c r="T537" s="6" t="n"/>
+    </row>
+    <row r="538">
+      <c r="H538" s="4" t="n"/>
+      <c r="Q538" s="5" t="n"/>
+      <c r="R538" s="6" t="n"/>
+      <c r="S538" s="5" t="n"/>
+      <c r="T538" s="6" t="n"/>
+    </row>
+    <row r="539">
+      <c r="H539" s="4" t="n"/>
+      <c r="Q539" s="5" t="n"/>
+      <c r="R539" s="6" t="n"/>
+      <c r="S539" s="5" t="n"/>
+      <c r="T539" s="6" t="n"/>
+    </row>
+    <row r="540">
+      <c r="H540" s="4" t="n"/>
+      <c r="Q540" s="5" t="n"/>
+      <c r="R540" s="6" t="n"/>
+      <c r="S540" s="5" t="n"/>
+      <c r="T540" s="6" t="n"/>
+    </row>
+    <row r="541">
+      <c r="H541" s="4" t="n"/>
+      <c r="Q541" s="5" t="n"/>
+      <c r="R541" s="6" t="n"/>
+      <c r="S541" s="5" t="n"/>
+      <c r="T541" s="6" t="n"/>
+    </row>
+    <row r="542">
+      <c r="H542" s="4" t="n"/>
+      <c r="Q542" s="5" t="n"/>
+      <c r="R542" s="6" t="n"/>
+      <c r="S542" s="5" t="n"/>
+      <c r="T542" s="6" t="n"/>
+    </row>
+    <row r="543">
+      <c r="H543" s="4" t="n"/>
+      <c r="Q543" s="5" t="n"/>
+      <c r="R543" s="6" t="n"/>
+      <c r="S543" s="5" t="n"/>
+      <c r="T543" s="6" t="n"/>
+    </row>
+    <row r="544">
+      <c r="H544" s="4" t="n"/>
+      <c r="Q544" s="5" t="n"/>
+      <c r="R544" s="6" t="n"/>
+      <c r="S544" s="5" t="n"/>
+      <c r="T544" s="6" t="n"/>
+    </row>
+    <row r="545">
+      <c r="H545" s="4" t="n"/>
+      <c r="Q545" s="5" t="n"/>
+      <c r="R545" s="6" t="n"/>
+      <c r="S545" s="5" t="n"/>
+      <c r="T545" s="6" t="n"/>
+    </row>
+    <row r="546">
+      <c r="H546" s="4" t="n"/>
+      <c r="Q546" s="5" t="n"/>
+      <c r="R546" s="6" t="n"/>
+      <c r="S546" s="5" t="n"/>
+      <c r="T546" s="6" t="n"/>
+    </row>
+    <row r="547">
+      <c r="H547" s="4" t="n"/>
+      <c r="Q547" s="5" t="n"/>
+      <c r="R547" s="6" t="n"/>
+      <c r="S547" s="5" t="n"/>
+      <c r="T547" s="6" t="n"/>
+    </row>
+    <row r="548">
+      <c r="H548" s="4" t="n"/>
+      <c r="Q548" s="5" t="n"/>
+      <c r="R548" s="6" t="n"/>
+      <c r="S548" s="5" t="n"/>
+      <c r="T548" s="6" t="n"/>
+    </row>
+    <row r="549">
+      <c r="H549" s="4" t="n"/>
+      <c r="Q549" s="5" t="n"/>
+      <c r="R549" s="6" t="n"/>
+      <c r="S549" s="5" t="n"/>
+      <c r="T549" s="6" t="n"/>
+    </row>
+    <row r="550">
+      <c r="H550" s="4" t="n"/>
+      <c r="Q550" s="5" t="n"/>
+      <c r="R550" s="6" t="n"/>
+      <c r="S550" s="5" t="n"/>
+      <c r="T550" s="6" t="n"/>
+    </row>
+    <row r="551">
+      <c r="H551" s="4" t="n"/>
+      <c r="Q551" s="5" t="n"/>
+      <c r="R551" s="6" t="n"/>
+      <c r="S551" s="5" t="n"/>
+      <c r="T551" s="6" t="n"/>
+    </row>
+    <row r="552">
+      <c r="H552" s="4" t="n"/>
+      <c r="Q552" s="5" t="n"/>
+      <c r="R552" s="6" t="n"/>
+      <c r="S552" s="5" t="n"/>
+      <c r="T552" s="6" t="n"/>
+    </row>
+    <row r="553">
+      <c r="H553" s="4" t="n"/>
+      <c r="Q553" s="5" t="n"/>
+      <c r="R553" s="6" t="n"/>
+      <c r="S553" s="5" t="n"/>
+      <c r="T553" s="6" t="n"/>
+    </row>
+    <row r="554">
+      <c r="H554" s="4" t="n"/>
+      <c r="Q554" s="5" t="n"/>
+      <c r="R554" s="6" t="n"/>
+      <c r="S554" s="5" t="n"/>
+      <c r="T554" s="6" t="n"/>
+    </row>
+    <row r="555">
+      <c r="H555" s="4" t="n"/>
+      <c r="Q555" s="5" t="n"/>
+      <c r="R555" s="6" t="n"/>
+      <c r="S555" s="5" t="n"/>
+      <c r="T555" s="6" t="n"/>
+    </row>
+    <row r="556">
+      <c r="H556" s="4" t="n"/>
+      <c r="Q556" s="5" t="n"/>
+      <c r="R556" s="6" t="n"/>
+      <c r="S556" s="5" t="n"/>
+      <c r="T556" s="6" t="n"/>
+    </row>
+    <row r="557">
+      <c r="H557" s="4" t="n"/>
+      <c r="Q557" s="5" t="n"/>
+      <c r="R557" s="6" t="n"/>
+      <c r="S557" s="5" t="n"/>
+      <c r="T557" s="6" t="n"/>
+    </row>
+    <row r="558">
+      <c r="H558" s="4" t="n"/>
+      <c r="Q558" s="5" t="n"/>
+      <c r="R558" s="6" t="n"/>
+      <c r="S558" s="5" t="n"/>
+      <c r="T558" s="6" t="n"/>
+    </row>
+    <row r="559">
+      <c r="H559" s="4" t="n"/>
+      <c r="Q559" s="5" t="n"/>
+      <c r="R559" s="6" t="n"/>
+      <c r="S559" s="5" t="n"/>
+      <c r="T559" s="6" t="n"/>
+    </row>
+    <row r="560">
+      <c r="H560" s="4" t="n"/>
+      <c r="Q560" s="5" t="n"/>
+      <c r="R560" s="6" t="n"/>
+      <c r="S560" s="5" t="n"/>
+      <c r="T560" s="6" t="n"/>
+    </row>
+    <row r="561">
+      <c r="H561" s="4" t="n"/>
+      <c r="Q561" s="5" t="n"/>
+      <c r="R561" s="6" t="n"/>
+      <c r="S561" s="5" t="n"/>
+      <c r="T561" s="6" t="n"/>
+    </row>
+    <row r="562">
+      <c r="H562" s="4" t="n"/>
+      <c r="Q562" s="5" t="n"/>
+      <c r="R562" s="6" t="n"/>
+      <c r="S562" s="5" t="n"/>
+      <c r="T562" s="6" t="n"/>
+    </row>
+    <row r="563">
+      <c r="H563" s="4" t="n"/>
+      <c r="Q563" s="5" t="n"/>
+      <c r="R563" s="6" t="n"/>
+      <c r="S563" s="5" t="n"/>
+      <c r="T563" s="6" t="n"/>
+    </row>
+    <row r="564">
+      <c r="H564" s="4" t="n"/>
+      <c r="Q564" s="5" t="n"/>
+      <c r="R564" s="6" t="n"/>
+      <c r="S564" s="5" t="n"/>
+      <c r="T564" s="6" t="n"/>
+    </row>
+    <row r="565">
+      <c r="H565" s="4" t="n"/>
+      <c r="Q565" s="5" t="n"/>
+      <c r="R565" s="6" t="n"/>
+      <c r="S565" s="5" t="n"/>
+      <c r="T565" s="6" t="n"/>
+    </row>
+    <row r="566">
+      <c r="H566" s="4" t="n"/>
+      <c r="Q566" s="5" t="n"/>
+      <c r="R566" s="6" t="n"/>
+      <c r="S566" s="5" t="n"/>
+      <c r="T566" s="6" t="n"/>
+    </row>
+    <row r="567">
+      <c r="H567" s="4" t="n"/>
+      <c r="Q567" s="5" t="n"/>
+      <c r="R567" s="6" t="n"/>
+      <c r="S567" s="5" t="n"/>
+      <c r="T567" s="6" t="n"/>
+    </row>
+    <row r="568">
+      <c r="H568" s="4" t="n"/>
+      <c r="Q568" s="5" t="n"/>
+      <c r="R568" s="6" t="n"/>
+      <c r="S568" s="5" t="n"/>
+      <c r="T568" s="6" t="n"/>
+    </row>
+    <row r="569">
+      <c r="H569" s="4" t="n"/>
+      <c r="Q569" s="5" t="n"/>
+      <c r="R569" s="6" t="n"/>
+      <c r="S569" s="5" t="n"/>
+      <c r="T569" s="6" t="n"/>
+    </row>
+    <row r="570">
+      <c r="H570" s="4" t="n"/>
+      <c r="Q570" s="5" t="n"/>
+      <c r="R570" s="6" t="n"/>
+      <c r="S570" s="5" t="n"/>
+      <c r="T570" s="6" t="n"/>
+    </row>
+    <row r="571">
+      <c r="H571" s="4" t="n"/>
+      <c r="Q571" s="5" t="n"/>
+      <c r="R571" s="6" t="n"/>
+      <c r="S571" s="5" t="n"/>
+      <c r="T571" s="6" t="n"/>
+    </row>
+    <row r="572">
+      <c r="H572" s="4" t="n"/>
+      <c r="Q572" s="5" t="n"/>
+      <c r="R572" s="6" t="n"/>
+      <c r="S572" s="5" t="n"/>
+      <c r="T572" s="6" t="n"/>
+    </row>
+    <row r="573">
+      <c r="H573" s="4" t="n"/>
+      <c r="Q573" s="5" t="n"/>
+      <c r="R573" s="6" t="n"/>
+      <c r="S573" s="5" t="n"/>
+      <c r="T573" s="6" t="n"/>
+    </row>
+    <row r="574">
+      <c r="H574" s="4" t="n"/>
+      <c r="Q574" s="5" t="n"/>
+      <c r="R574" s="6" t="n"/>
+      <c r="S574" s="5" t="n"/>
+      <c r="T574" s="6" t="n"/>
+    </row>
+    <row r="575">
+      <c r="H575" s="4" t="n"/>
+      <c r="Q575" s="5" t="n"/>
+      <c r="R575" s="6" t="n"/>
+      <c r="S575" s="5" t="n"/>
+      <c r="T575" s="6" t="n"/>
+    </row>
+    <row r="576">
+      <c r="H576" s="4" t="n"/>
+      <c r="Q576" s="5" t="n"/>
+      <c r="R576" s="6" t="n"/>
+      <c r="S576" s="5" t="n"/>
+      <c r="T576" s="6" t="n"/>
+    </row>
+    <row r="577">
+      <c r="H577" s="4" t="n"/>
+      <c r="Q577" s="5" t="n"/>
+      <c r="R577" s="6" t="n"/>
+      <c r="S577" s="5" t="n"/>
+      <c r="T577" s="6" t="n"/>
+    </row>
+    <row r="578">
+      <c r="H578" s="4" t="n"/>
+      <c r="Q578" s="5" t="n"/>
+      <c r="R578" s="6" t="n"/>
+      <c r="S578" s="5" t="n"/>
+      <c r="T578" s="6" t="n"/>
+    </row>
+    <row r="579">
+      <c r="H579" s="4" t="n"/>
+      <c r="Q579" s="5" t="n"/>
+      <c r="R579" s="6" t="n"/>
+      <c r="S579" s="5" t="n"/>
+      <c r="T579" s="6" t="n"/>
+    </row>
+    <row r="580">
+      <c r="H580" s="4" t="n"/>
+      <c r="Q580" s="5" t="n"/>
+      <c r="R580" s="6" t="n"/>
+      <c r="S580" s="5" t="n"/>
+      <c r="T580" s="6" t="n"/>
+    </row>
+    <row r="581">
+      <c r="H581" s="4" t="n"/>
+      <c r="Q581" s="5" t="n"/>
+      <c r="R581" s="6" t="n"/>
+      <c r="S581" s="5" t="n"/>
+      <c r="T581" s="6" t="n"/>
+    </row>
+    <row r="582">
+      <c r="H582" s="4" t="n"/>
+      <c r="Q582" s="5" t="n"/>
+      <c r="R582" s="6" t="n"/>
+      <c r="S582" s="5" t="n"/>
+      <c r="T582" s="6" t="n"/>
+    </row>
+    <row r="583">
+      <c r="H583" s="4" t="n"/>
+      <c r="Q583" s="5" t="n"/>
+      <c r="R583" s="6" t="n"/>
+      <c r="S583" s="5" t="n"/>
+      <c r="T583" s="6" t="n"/>
+    </row>
+    <row r="584">
+      <c r="H584" s="4" t="n"/>
+      <c r="Q584" s="5" t="n"/>
+      <c r="R584" s="6" t="n"/>
+      <c r="S584" s="5" t="n"/>
+      <c r="T584" s="6" t="n"/>
+    </row>
+    <row r="585">
+      <c r="H585" s="4" t="n"/>
+      <c r="Q585" s="5" t="n"/>
+      <c r="R585" s="6" t="n"/>
+      <c r="S585" s="5" t="n"/>
+      <c r="T585" s="6" t="n"/>
+    </row>
+    <row r="586">
+      <c r="H586" s="4" t="n"/>
+      <c r="Q586" s="5" t="n"/>
+      <c r="R586" s="6" t="n"/>
+      <c r="S586" s="5" t="n"/>
+      <c r="T586" s="6" t="n"/>
+    </row>
+    <row r="587">
+      <c r="H587" s="4" t="n"/>
+      <c r="Q587" s="5" t="n"/>
+      <c r="R587" s="6" t="n"/>
+      <c r="S587" s="5" t="n"/>
+      <c r="T587" s="6" t="n"/>
+    </row>
+    <row r="588">
+      <c r="H588" s="4" t="n"/>
+      <c r="Q588" s="5" t="n"/>
+      <c r="R588" s="6" t="n"/>
+      <c r="S588" s="5" t="n"/>
+      <c r="T588" s="6" t="n"/>
+    </row>
+    <row r="589">
+      <c r="H589" s="4" t="n"/>
+      <c r="Q589" s="5" t="n"/>
+      <c r="R589" s="6" t="n"/>
+      <c r="S589" s="5" t="n"/>
+      <c r="T589" s="6" t="n"/>
+    </row>
+    <row r="590">
+      <c r="H590" s="4" t="n"/>
+      <c r="Q590" s="5" t="n"/>
+      <c r="R590" s="6" t="n"/>
+      <c r="S590" s="5" t="n"/>
+      <c r="T590" s="6" t="n"/>
+    </row>
+    <row r="591">
+      <c r="H591" s="4" t="n"/>
+      <c r="Q591" s="5" t="n"/>
+      <c r="R591" s="6" t="n"/>
+      <c r="S591" s="5" t="n"/>
+      <c r="T591" s="6" t="n"/>
+    </row>
+    <row r="592">
+      <c r="H592" s="4" t="n"/>
+      <c r="Q592" s="5" t="n"/>
+      <c r="R592" s="6" t="n"/>
+      <c r="S592" s="5" t="n"/>
+      <c r="T592" s="6" t="n"/>
+    </row>
+    <row r="593">
+      <c r="H593" s="4" t="n"/>
+      <c r="Q593" s="5" t="n"/>
+      <c r="R593" s="6" t="n"/>
+      <c r="S593" s="5" t="n"/>
+      <c r="T593" s="6" t="n"/>
+    </row>
+    <row r="594">
+      <c r="H594" s="4" t="n"/>
+      <c r="Q594" s="5" t="n"/>
+      <c r="R594" s="6" t="n"/>
+      <c r="S594" s="5" t="n"/>
+      <c r="T594" s="6" t="n"/>
+    </row>
+    <row r="595">
+      <c r="H595" s="4" t="n"/>
+      <c r="Q595" s="5" t="n"/>
+      <c r="R595" s="6" t="n"/>
+      <c r="S595" s="5" t="n"/>
+      <c r="T595" s="6" t="n"/>
+    </row>
+    <row r="596">
+      <c r="H596" s="4" t="n"/>
+      <c r="Q596" s="5" t="n"/>
+      <c r="R596" s="6" t="n"/>
+      <c r="S596" s="5" t="n"/>
+      <c r="T596" s="6" t="n"/>
+    </row>
+    <row r="597">
+      <c r="H597" s="4" t="n"/>
+      <c r="Q597" s="5" t="n"/>
+      <c r="R597" s="6" t="n"/>
+      <c r="S597" s="5" t="n"/>
+      <c r="T597" s="6" t="n"/>
+    </row>
+    <row r="598">
+      <c r="H598" s="4" t="n"/>
+      <c r="Q598" s="5" t="n"/>
+      <c r="R598" s="6" t="n"/>
+      <c r="S598" s="5" t="n"/>
+      <c r="T598" s="6" t="n"/>
+    </row>
+    <row r="599">
+      <c r="H599" s="4" t="n"/>
+      <c r="Q599" s="5" t="n"/>
+      <c r="R599" s="6" t="n"/>
+      <c r="S599" s="5" t="n"/>
+      <c r="T599" s="6" t="n"/>
+    </row>
+    <row r="600">
+      <c r="H600" s="4" t="n"/>
+      <c r="Q600" s="5" t="n"/>
+      <c r="R600" s="6" t="n"/>
+      <c r="S600" s="5" t="n"/>
+      <c r="T600" s="6" t="n"/>
+    </row>
+    <row r="601">
+      <c r="H601" s="4" t="n"/>
+      <c r="Q601" s="5" t="n"/>
+      <c r="R601" s="6" t="n"/>
+      <c r="S601" s="5" t="n"/>
+      <c r="T601" s="6" t="n"/>
+    </row>
+    <row r="602">
+      <c r="H602" s="4" t="n"/>
+      <c r="Q602" s="5" t="n"/>
+      <c r="R602" s="6" t="n"/>
+      <c r="S602" s="5" t="n"/>
+      <c r="T602" s="6" t="n"/>
+    </row>
+    <row r="603">
+      <c r="H603" s="4" t="n"/>
+      <c r="Q603" s="5" t="n"/>
+      <c r="R603" s="6" t="n"/>
+      <c r="S603" s="5" t="n"/>
+      <c r="T603" s="6" t="n"/>
+    </row>
+    <row r="604">
+      <c r="H604" s="4" t="n"/>
+      <c r="Q604" s="5" t="n"/>
+      <c r="R604" s="6" t="n"/>
+      <c r="S604" s="5" t="n"/>
+      <c r="T604" s="6" t="n"/>
+    </row>
+    <row r="605">
+      <c r="H605" s="4" t="n"/>
+      <c r="Q605" s="5" t="n"/>
+      <c r="R605" s="6" t="n"/>
+      <c r="S605" s="5" t="n"/>
+      <c r="T605" s="6" t="n"/>
+    </row>
+    <row r="606">
+      <c r="H606" s="4" t="n"/>
+      <c r="Q606" s="5" t="n"/>
+      <c r="R606" s="6" t="n"/>
+      <c r="S606" s="5" t="n"/>
+      <c r="T606" s="6" t="n"/>
+    </row>
+    <row r="607">
+      <c r="H607" s="4" t="n"/>
+      <c r="Q607" s="5" t="n"/>
+      <c r="R607" s="6" t="n"/>
+      <c r="S607" s="5" t="n"/>
+      <c r="T607" s="6" t="n"/>
+    </row>
+    <row r="608">
+      <c r="H608" s="4" t="n"/>
+      <c r="Q608" s="5" t="n"/>
+      <c r="R608" s="6" t="n"/>
+      <c r="S608" s="5" t="n"/>
+      <c r="T608" s="6" t="n"/>
+    </row>
+    <row r="609">
+      <c r="H609" s="4" t="n"/>
+      <c r="Q609" s="5" t="n"/>
+      <c r="R609" s="6" t="n"/>
+      <c r="S609" s="5" t="n"/>
+      <c r="T609" s="6" t="n"/>
+    </row>
+    <row r="610">
+      <c r="H610" s="4" t="n"/>
+      <c r="Q610" s="5" t="n"/>
+      <c r="R610" s="6" t="n"/>
+      <c r="S610" s="5" t="n"/>
+      <c r="T610" s="6" t="n"/>
+    </row>
+    <row r="611">
+      <c r="H611" s="4" t="n"/>
+      <c r="Q611" s="5" t="n"/>
+      <c r="R611" s="6" t="n"/>
+      <c r="S611" s="5" t="n"/>
+      <c r="T611" s="6" t="n"/>
+    </row>
+    <row r="612">
+      <c r="H612" s="4" t="n"/>
+      <c r="Q612" s="5" t="n"/>
+      <c r="R612" s="6" t="n"/>
+      <c r="S612" s="5" t="n"/>
+      <c r="T612" s="6" t="n"/>
+    </row>
+    <row r="613">
+      <c r="H613" s="4" t="n"/>
+      <c r="Q613" s="5" t="n"/>
+      <c r="R613" s="6" t="n"/>
+      <c r="S613" s="5" t="n"/>
+      <c r="T613" s="6" t="n"/>
+    </row>
+    <row r="614">
+      <c r="H614" s="4" t="n"/>
+      <c r="Q614" s="5" t="n"/>
+      <c r="R614" s="6" t="n"/>
+      <c r="S614" s="5" t="n"/>
+      <c r="T614" s="6" t="n"/>
+    </row>
+    <row r="615">
+      <c r="H615" s="4" t="n"/>
+      <c r="Q615" s="5" t="n"/>
+      <c r="R615" s="6" t="n"/>
+      <c r="S615" s="5" t="n"/>
+      <c r="T615" s="6" t="n"/>
+    </row>
+    <row r="616">
+      <c r="H616" s="4" t="n"/>
+      <c r="Q616" s="5" t="n"/>
+      <c r="R616" s="6" t="n"/>
+      <c r="S616" s="5" t="n"/>
+      <c r="T616" s="6" t="n"/>
+    </row>
+    <row r="617">
+      <c r="H617" s="4" t="n"/>
+      <c r="Q617" s="5" t="n"/>
+      <c r="R617" s="6" t="n"/>
+      <c r="S617" s="5" t="n"/>
+      <c r="T617" s="6" t="n"/>
+    </row>
+    <row r="618">
+      <c r="H618" s="4" t="n"/>
+      <c r="Q618" s="5" t="n"/>
+      <c r="R618" s="6" t="n"/>
+      <c r="S618" s="5" t="n"/>
+      <c r="T618" s="6" t="n"/>
+    </row>
+    <row r="619">
+      <c r="H619" s="4" t="n"/>
+      <c r="Q619" s="5" t="n"/>
+      <c r="R619" s="6" t="n"/>
+      <c r="S619" s="5" t="n"/>
+      <c r="T619" s="6" t="n"/>
+    </row>
+    <row r="620">
+      <c r="H620" s="4" t="n"/>
+      <c r="Q620" s="5" t="n"/>
+      <c r="R620" s="6" t="n"/>
+      <c r="S620" s="5" t="n"/>
+      <c r="T620" s="6" t="n"/>
+    </row>
+    <row r="621">
+      <c r="H621" s="4" t="n"/>
+      <c r="Q621" s="5" t="n"/>
+      <c r="R621" s="6" t="n"/>
+      <c r="S621" s="5" t="n"/>
+      <c r="T621" s="6" t="n"/>
+    </row>
+    <row r="622">
+      <c r="H622" s="4" t="n"/>
+      <c r="Q622" s="5" t="n"/>
+      <c r="R622" s="6" t="n"/>
+      <c r="S622" s="5" t="n"/>
+      <c r="T622" s="6" t="n"/>
+    </row>
+    <row r="623">
+      <c r="H623" s="4" t="n"/>
+      <c r="Q623" s="5" t="n"/>
+      <c r="R623" s="6" t="n"/>
+      <c r="S623" s="5" t="n"/>
+      <c r="T623" s="6" t="n"/>
+    </row>
+    <row r="624">
+      <c r="H624" s="4" t="n"/>
+      <c r="Q624" s="5" t="n"/>
+      <c r="R624" s="6" t="n"/>
+      <c r="S624" s="5" t="n"/>
+      <c r="T624" s="6" t="n"/>
+    </row>
+    <row r="625">
+      <c r="H625" s="4" t="n"/>
+      <c r="Q625" s="5" t="n"/>
+      <c r="R625" s="6" t="n"/>
+      <c r="S625" s="5" t="n"/>
+      <c r="T625" s="6" t="n"/>
+    </row>
+    <row r="626">
+      <c r="H626" s="4" t="n"/>
+      <c r="Q626" s="5" t="n"/>
+      <c r="R626" s="6" t="n"/>
+      <c r="S626" s="5" t="n"/>
+      <c r="T626" s="6" t="n"/>
+    </row>
+    <row r="627">
+      <c r="H627" s="4" t="n"/>
+      <c r="Q627" s="5" t="n"/>
+      <c r="R627" s="6" t="n"/>
+      <c r="S627" s="5" t="n"/>
+      <c r="T627" s="6" t="n"/>
+    </row>
+    <row r="628">
+      <c r="H628" s="4" t="n"/>
+      <c r="Q628" s="5" t="n"/>
+      <c r="R628" s="6" t="n"/>
+      <c r="S628" s="5" t="n"/>
+      <c r="T628" s="6" t="n"/>
+    </row>
+    <row r="629">
+      <c r="H629" s="4" t="n"/>
+      <c r="Q629" s="5" t="n"/>
+      <c r="R629" s="6" t="n"/>
+      <c r="S629" s="5" t="n"/>
+      <c r="T629" s="6" t="n"/>
+    </row>
+    <row r="630">
+      <c r="H630" s="4" t="n"/>
+      <c r="Q630" s="5" t="n"/>
+      <c r="R630" s="6" t="n"/>
+      <c r="S630" s="5" t="n"/>
+      <c r="T630" s="6" t="n"/>
+    </row>
+    <row r="631">
+      <c r="H631" s="4" t="n"/>
+      <c r="Q631" s="5" t="n"/>
+      <c r="R631" s="6" t="n"/>
+      <c r="S631" s="5" t="n"/>
+      <c r="T631" s="6" t="n"/>
+    </row>
+    <row r="632">
+      <c r="H632" s="4" t="n"/>
+      <c r="Q632" s="5" t="n"/>
+      <c r="R632" s="6" t="n"/>
+      <c r="S632" s="5" t="n"/>
+      <c r="T632" s="6" t="n"/>
+    </row>
+    <row r="633">
+      <c r="H633" s="4" t="n"/>
+      <c r="Q633" s="5" t="n"/>
+      <c r="R633" s="6" t="n"/>
+      <c r="S633" s="5" t="n"/>
+      <c r="T633" s="6" t="n"/>
+    </row>
+    <row r="634">
+      <c r="H634" s="4" t="n"/>
+      <c r="Q634" s="5" t="n"/>
+      <c r="R634" s="6" t="n"/>
+      <c r="S634" s="5" t="n"/>
+      <c r="T634" s="6" t="n"/>
+    </row>
+    <row r="635">
+      <c r="H635" s="4" t="n"/>
+      <c r="Q635" s="5" t="n"/>
+      <c r="R635" s="6" t="n"/>
+      <c r="S635" s="5" t="n"/>
+      <c r="T635" s="6" t="n"/>
+    </row>
+    <row r="636">
+      <c r="H636" s="4" t="n"/>
+      <c r="Q636" s="5" t="n"/>
+      <c r="R636" s="6" t="n"/>
+      <c r="S636" s="5" t="n"/>
+      <c r="T636" s="6" t="n"/>
+    </row>
+    <row r="637">
+      <c r="H637" s="4" t="n"/>
+      <c r="Q637" s="5" t="n"/>
+      <c r="R637" s="6" t="n"/>
+      <c r="S637" s="5" t="n"/>
+      <c r="T637" s="6" t="n"/>
+    </row>
+    <row r="638">
+      <c r="H638" s="4" t="n"/>
+      <c r="Q638" s="5" t="n"/>
+      <c r="R638" s="6" t="n"/>
+      <c r="S638" s="5" t="n"/>
+      <c r="T638" s="6" t="n"/>
+    </row>
+    <row r="639">
+      <c r="H639" s="4" t="n"/>
+      <c r="Q639" s="5" t="n"/>
+      <c r="R639" s="6" t="n"/>
+      <c r="S639" s="5" t="n"/>
+      <c r="T639" s="6" t="n"/>
+    </row>
+    <row r="640">
+      <c r="H640" s="4" t="n"/>
+      <c r="Q640" s="5" t="n"/>
+      <c r="R640" s="6" t="n"/>
+      <c r="S640" s="5" t="n"/>
+      <c r="T640" s="6" t="n"/>
+    </row>
+    <row r="641">
+      <c r="H641" s="4" t="n"/>
+      <c r="Q641" s="5" t="n"/>
+      <c r="R641" s="6" t="n"/>
+      <c r="S641" s="5" t="n"/>
+      <c r="T641" s="6" t="n"/>
+    </row>
+    <row r="642">
+      <c r="H642" s="4" t="n"/>
+      <c r="Q642" s="5" t="n"/>
+      <c r="R642" s="6" t="n"/>
+      <c r="S642" s="5" t="n"/>
+      <c r="T642" s="6" t="n"/>
+    </row>
+    <row r="643">
+      <c r="H643" s="4" t="n"/>
+      <c r="Q643" s="5" t="n"/>
+      <c r="R643" s="6" t="n"/>
+      <c r="S643" s="5" t="n"/>
+      <c r="T643" s="6" t="n"/>
+    </row>
+    <row r="644">
+      <c r="H644" s="4" t="n"/>
+      <c r="Q644" s="5" t="n"/>
+      <c r="R644" s="6" t="n"/>
+      <c r="S644" s="5" t="n"/>
+      <c r="T644" s="6" t="n"/>
+    </row>
+    <row r="645">
+      <c r="H645" s="4" t="n"/>
+      <c r="Q645" s="5" t="n"/>
+      <c r="R645" s="6" t="n"/>
+      <c r="S645" s="5" t="n"/>
+      <c r="T645" s="6" t="n"/>
+    </row>
+    <row r="646">
+      <c r="H646" s="4" t="n"/>
+      <c r="Q646" s="5" t="n"/>
+      <c r="R646" s="6" t="n"/>
+      <c r="S646" s="5" t="n"/>
+      <c r="T646" s="6" t="n"/>
+    </row>
+    <row r="647">
+      <c r="H647" s="4" t="n"/>
+      <c r="Q647" s="5" t="n"/>
+      <c r="R647" s="6" t="n"/>
+      <c r="S647" s="5" t="n"/>
+      <c r="T647" s="6" t="n"/>
+    </row>
+    <row r="648">
+      <c r="H648" s="4" t="n"/>
+      <c r="Q648" s="5" t="n"/>
+      <c r="R648" s="6" t="n"/>
+      <c r="S648" s="5" t="n"/>
+      <c r="T648" s="6" t="n"/>
+    </row>
+    <row r="649">
+      <c r="H649" s="4" t="n"/>
+      <c r="Q649" s="5" t="n"/>
+      <c r="R649" s="6" t="n"/>
+      <c r="S649" s="5" t="n"/>
+      <c r="T649" s="6" t="n"/>
+    </row>
+    <row r="650">
+      <c r="H650" s="4" t="n"/>
+      <c r="Q650" s="5" t="n"/>
+      <c r="R650" s="6" t="n"/>
+      <c r="S650" s="5" t="n"/>
+      <c r="T650" s="6" t="n"/>
+    </row>
+    <row r="651">
+      <c r="H651" s="4" t="n"/>
+      <c r="Q651" s="5" t="n"/>
+      <c r="R651" s="6" t="n"/>
+      <c r="S651" s="5" t="n"/>
+      <c r="T651" s="6" t="n"/>
+    </row>
+    <row r="652">
+      <c r="H652" s="4" t="n"/>
+      <c r="Q652" s="5" t="n"/>
+      <c r="R652" s="6" t="n"/>
+      <c r="S652" s="5" t="n"/>
+      <c r="T652" s="6" t="n"/>
+    </row>
+    <row r="653">
+      <c r="H653" s="4" t="n"/>
+      <c r="Q653" s="5" t="n"/>
+      <c r="R653" s="6" t="n"/>
+      <c r="S653" s="5" t="n"/>
+      <c r="T653" s="6" t="n"/>
+    </row>
+    <row r="654">
+      <c r="H654" s="4" t="n"/>
+      <c r="Q654" s="5" t="n"/>
+      <c r="R654" s="6" t="n"/>
+      <c r="S654" s="5" t="n"/>
+      <c r="T654" s="6" t="n"/>
+    </row>
+    <row r="655">
+      <c r="H655" s="4" t="n"/>
+      <c r="Q655" s="5" t="n"/>
+      <c r="R655" s="6" t="n"/>
+      <c r="S655" s="5" t="n"/>
+      <c r="T655" s="6" t="n"/>
+    </row>
+    <row r="656">
+      <c r="H656" s="4" t="n"/>
+      <c r="Q656" s="5" t="n"/>
+      <c r="R656" s="6" t="n"/>
+      <c r="S656" s="5" t="n"/>
+      <c r="T656" s="6" t="n"/>
+    </row>
+    <row r="657">
+      <c r="H657" s="4" t="n"/>
+      <c r="Q657" s="5" t="n"/>
+      <c r="R657" s="6" t="n"/>
+      <c r="S657" s="5" t="n"/>
+      <c r="T657" s="6" t="n"/>
+    </row>
+    <row r="658">
+      <c r="H658" s="4" t="n"/>
+      <c r="Q658" s="5" t="n"/>
+      <c r="R658" s="6" t="n"/>
+      <c r="S658" s="5" t="n"/>
+      <c r="T658" s="6" t="n"/>
+    </row>
+    <row r="659">
+      <c r="H659" s="4" t="n"/>
+      <c r="Q659" s="5" t="n"/>
+      <c r="R659" s="6" t="n"/>
+      <c r="S659" s="5" t="n"/>
+      <c r="T659" s="6" t="n"/>
+    </row>
+    <row r="660">
+      <c r="H660" s="4" t="n"/>
+      <c r="Q660" s="5" t="n"/>
+      <c r="R660" s="6" t="n"/>
+      <c r="S660" s="5" t="n"/>
+      <c r="T660" s="6" t="n"/>
+    </row>
+    <row r="661">
+      <c r="H661" s="4" t="n"/>
+      <c r="Q661" s="5" t="n"/>
+      <c r="R661" s="6" t="n"/>
+      <c r="S661" s="5" t="n"/>
+      <c r="T661" s="6" t="n"/>
+    </row>
+    <row r="662">
+      <c r="H662" s="4" t="n"/>
+      <c r="Q662" s="5" t="n"/>
+      <c r="R662" s="6" t="n"/>
+      <c r="S662" s="5" t="n"/>
+      <c r="T662" s="6" t="n"/>
+    </row>
+    <row r="663">
+      <c r="H663" s="4" t="n"/>
+      <c r="Q663" s="5" t="n"/>
+      <c r="R663" s="6" t="n"/>
+      <c r="S663" s="5" t="n"/>
+      <c r="T663" s="6" t="n"/>
+    </row>
+    <row r="664">
+      <c r="H664" s="4" t="n"/>
+      <c r="Q664" s="5" t="n"/>
+      <c r="R664" s="6" t="n"/>
+      <c r="S664" s="5" t="n"/>
+      <c r="T664" s="6" t="n"/>
+    </row>
+    <row r="665">
+      <c r="H665" s="4" t="n"/>
+      <c r="Q665" s="5" t="n"/>
+      <c r="R665" s="6" t="n"/>
+      <c r="S665" s="5" t="n"/>
+      <c r="T665" s="6" t="n"/>
+    </row>
+    <row r="666">
+      <c r="H666" s="4" t="n"/>
+      <c r="Q666" s="5" t="n"/>
+      <c r="R666" s="6" t="n"/>
+      <c r="S666" s="5" t="n"/>
+      <c r="T666" s="6" t="n"/>
+    </row>
+    <row r="667">
+      <c r="H667" s="4" t="n"/>
+      <c r="Q667" s="5" t="n"/>
+      <c r="R667" s="6" t="n"/>
+      <c r="S667" s="5" t="n"/>
+      <c r="T667" s="6" t="n"/>
+    </row>
+    <row r="668">
+      <c r="H668" s="4" t="n"/>
+      <c r="Q668" s="5" t="n"/>
+      <c r="R668" s="6" t="n"/>
+      <c r="S668" s="5" t="n"/>
+      <c r="T668" s="6" t="n"/>
+    </row>
+    <row r="669">
+      <c r="H669" s="4" t="n"/>
+      <c r="Q669" s="5" t="n"/>
+      <c r="R669" s="6" t="n"/>
+      <c r="S669" s="5" t="n"/>
+      <c r="T669" s="6" t="n"/>
+    </row>
+    <row r="670">
+      <c r="H670" s="4" t="n"/>
+      <c r="Q670" s="5" t="n"/>
+      <c r="R670" s="6" t="n"/>
+      <c r="S670" s="5" t="n"/>
+      <c r="T670" s="6" t="n"/>
+    </row>
+    <row r="671">
+      <c r="H671" s="4" t="n"/>
+      <c r="Q671" s="5" t="n"/>
+      <c r="R671" s="6" t="n"/>
+      <c r="S671" s="5" t="n"/>
+      <c r="T671" s="6" t="n"/>
+    </row>
+    <row r="672">
+      <c r="H672" s="4" t="n"/>
+      <c r="Q672" s="5" t="n"/>
+      <c r="R672" s="6" t="n"/>
+      <c r="S672" s="5" t="n"/>
+      <c r="T672" s="6" t="n"/>
+    </row>
+    <row r="673">
+      <c r="H673" s="4" t="n"/>
+      <c r="Q673" s="5" t="n"/>
+      <c r="R673" s="6" t="n"/>
+      <c r="S673" s="5" t="n"/>
+      <c r="T673" s="6" t="n"/>
+    </row>
+    <row r="674">
+      <c r="H674" s="4" t="n"/>
+      <c r="Q674" s="5" t="n"/>
+      <c r="R674" s="6" t="n"/>
+      <c r="S674" s="5" t="n"/>
+      <c r="T674" s="6" t="n"/>
+    </row>
+    <row r="675">
+      <c r="H675" s="4" t="n"/>
+      <c r="Q675" s="5" t="n"/>
+      <c r="R675" s="6" t="n"/>
+      <c r="S675" s="5" t="n"/>
+      <c r="T675" s="6" t="n"/>
+    </row>
+    <row r="676">
+      <c r="H676" s="4" t="n"/>
+      <c r="Q676" s="5" t="n"/>
+      <c r="R676" s="6" t="n"/>
+      <c r="S676" s="5" t="n"/>
+      <c r="T676" s="6" t="n"/>
+    </row>
+    <row r="677">
+      <c r="H677" s="4" t="n"/>
+      <c r="Q677" s="5" t="n"/>
+      <c r="R677" s="6" t="n"/>
+      <c r="S677" s="5" t="n"/>
+      <c r="T677" s="6" t="n"/>
+    </row>
+    <row r="678">
+      <c r="H678" s="4" t="n"/>
+      <c r="Q678" s="5" t="n"/>
+      <c r="R678" s="6" t="n"/>
+      <c r="S678" s="5" t="n"/>
+      <c r="T678" s="6" t="n"/>
+    </row>
+    <row r="679">
+      <c r="H679" s="4" t="n"/>
+      <c r="Q679" s="5" t="n"/>
+      <c r="R679" s="6" t="n"/>
+      <c r="S679" s="5" t="n"/>
+      <c r="T679" s="6" t="n"/>
+    </row>
+    <row r="680">
+      <c r="H680" s="4" t="n"/>
+      <c r="Q680" s="5" t="n"/>
+      <c r="R680" s="6" t="n"/>
+      <c r="S680" s="5" t="n"/>
+      <c r="T680" s="6" t="n"/>
+    </row>
+    <row r="681">
+      <c r="H681" s="4" t="n"/>
+      <c r="Q681" s="5" t="n"/>
+      <c r="R681" s="6" t="n"/>
+      <c r="S681" s="5" t="n"/>
+      <c r="T681" s="6" t="n"/>
+    </row>
+    <row r="682">
+      <c r="H682" s="4" t="n"/>
+      <c r="Q682" s="5" t="n"/>
+      <c r="R682" s="6" t="n"/>
+      <c r="S682" s="5" t="n"/>
+      <c r="T682" s="6" t="n"/>
+    </row>
+    <row r="683">
+      <c r="H683" s="4" t="n"/>
+      <c r="Q683" s="5" t="n"/>
+      <c r="R683" s="6" t="n"/>
+      <c r="S683" s="5" t="n"/>
+      <c r="T683" s="6" t="n"/>
+    </row>
+    <row r="684">
+      <c r="H684" s="4" t="n"/>
+      <c r="Q684" s="5" t="n"/>
+      <c r="R684" s="6" t="n"/>
+      <c r="S684" s="5" t="n"/>
+      <c r="T684" s="6" t="n"/>
+    </row>
+    <row r="685">
+      <c r="H685" s="4" t="n"/>
+      <c r="Q685" s="5" t="n"/>
+      <c r="R685" s="6" t="n"/>
+      <c r="S685" s="5" t="n"/>
+      <c r="T685" s="6" t="n"/>
+    </row>
+    <row r="686">
+      <c r="H686" s="4" t="n"/>
+      <c r="Q686" s="5" t="n"/>
+      <c r="R686" s="6" t="n"/>
+      <c r="S686" s="5" t="n"/>
+      <c r="T686" s="6" t="n"/>
+    </row>
+    <row r="687">
+      <c r="H687" s="4" t="n"/>
+      <c r="Q687" s="5" t="n"/>
+      <c r="R687" s="6" t="n"/>
+      <c r="S687" s="5" t="n"/>
+      <c r="T687" s="6" t="n"/>
+    </row>
+    <row r="688">
+      <c r="H688" s="4" t="n"/>
+      <c r="Q688" s="5" t="n"/>
+      <c r="R688" s="6" t="n"/>
+      <c r="S688" s="5" t="n"/>
+      <c r="T688" s="6" t="n"/>
+    </row>
+    <row r="689">
+      <c r="H689" s="4" t="n"/>
+      <c r="Q689" s="5" t="n"/>
+      <c r="R689" s="6" t="n"/>
+      <c r="S689" s="5" t="n"/>
+      <c r="T689" s="6" t="n"/>
+    </row>
+    <row r="690">
+      <c r="H690" s="4" t="n"/>
+      <c r="Q690" s="5" t="n"/>
+      <c r="R690" s="6" t="n"/>
+      <c r="S690" s="5" t="n"/>
+      <c r="T690" s="6" t="n"/>
+    </row>
+    <row r="691">
+      <c r="H691" s="4" t="n"/>
+      <c r="Q691" s="5" t="n"/>
+      <c r="R691" s="6" t="n"/>
+      <c r="S691" s="5" t="n"/>
+      <c r="T691" s="6" t="n"/>
+    </row>
+    <row r="692">
+      <c r="H692" s="4" t="n"/>
+      <c r="Q692" s="5" t="n"/>
+      <c r="R692" s="6" t="n"/>
+      <c r="S692" s="5" t="n"/>
+      <c r="T692" s="6" t="n"/>
+    </row>
+    <row r="693">
+      <c r="H693" s="4" t="n"/>
+      <c r="Q693" s="5" t="n"/>
+      <c r="R693" s="6" t="n"/>
+      <c r="S693" s="5" t="n"/>
+      <c r="T693" s="6" t="n"/>
+    </row>
+    <row r="694">
+      <c r="H694" s="4" t="n"/>
+      <c r="Q694" s="5" t="n"/>
+      <c r="R694" s="6" t="n"/>
+      <c r="S694" s="5" t="n"/>
+      <c r="T694" s="6" t="n"/>
+    </row>
+    <row r="695">
+      <c r="H695" s="4" t="n"/>
+      <c r="Q695" s="5" t="n"/>
+      <c r="R695" s="6" t="n"/>
+      <c r="S695" s="5" t="n"/>
+      <c r="T695" s="6" t="n"/>
+    </row>
+    <row r="696">
+      <c r="H696" s="4" t="n"/>
+      <c r="Q696" s="5" t="n"/>
+      <c r="R696" s="6" t="n"/>
+      <c r="S696" s="5" t="n"/>
+      <c r="T696" s="6" t="n"/>
+    </row>
+    <row r="697">
+      <c r="H697" s="4" t="n"/>
+      <c r="Q697" s="5" t="n"/>
+      <c r="R697" s="6" t="n"/>
+      <c r="S697" s="5" t="n"/>
+      <c r="T697" s="6" t="n"/>
+    </row>
+    <row r="698">
+      <c r="H698" s="4" t="n"/>
+      <c r="Q698" s="5" t="n"/>
+      <c r="R698" s="6" t="n"/>
+      <c r="S698" s="5" t="n"/>
+      <c r="T698" s="6" t="n"/>
+    </row>
+    <row r="699">
+      <c r="H699" s="4" t="n"/>
+      <c r="Q699" s="5" t="n"/>
+      <c r="R699" s="6" t="n"/>
+      <c r="S699" s="5" t="n"/>
+      <c r="T699" s="6" t="n"/>
+    </row>
+    <row r="700">
+      <c r="H700" s="4" t="n"/>
+      <c r="Q700" s="5" t="n"/>
+      <c r="R700" s="6" t="n"/>
+      <c r="S700" s="5" t="n"/>
+      <c r="T700" s="6" t="n"/>
+    </row>
+    <row r="701">
+      <c r="H701" s="4" t="n"/>
+      <c r="Q701" s="5" t="n"/>
+      <c r="R701" s="6" t="n"/>
+      <c r="S701" s="5" t="n"/>
+      <c r="T701" s="6" t="n"/>
+    </row>
+    <row r="702">
+      <c r="H702" s="4" t="n"/>
+      <c r="Q702" s="5" t="n"/>
+      <c r="R702" s="6" t="n"/>
+      <c r="S702" s="5" t="n"/>
+      <c r="T702" s="6" t="n"/>
+    </row>
+    <row r="703">
+      <c r="H703" s="4" t="n"/>
+      <c r="Q703" s="5" t="n"/>
+      <c r="R703" s="6" t="n"/>
+      <c r="S703" s="5" t="n"/>
+      <c r="T703" s="6" t="n"/>
+    </row>
+    <row r="704">
+      <c r="H704" s="4" t="n"/>
+      <c r="Q704" s="5" t="n"/>
+      <c r="R704" s="6" t="n"/>
+      <c r="S704" s="5" t="n"/>
+      <c r="T704" s="6" t="n"/>
+    </row>
+    <row r="705">
+      <c r="H705" s="4" t="n"/>
+      <c r="Q705" s="5" t="n"/>
+      <c r="R705" s="6" t="n"/>
+      <c r="S705" s="5" t="n"/>
+      <c r="T705" s="6" t="n"/>
+    </row>
+    <row r="706">
+      <c r="H706" s="4" t="n"/>
+      <c r="Q706" s="5" t="n"/>
+      <c r="R706" s="6" t="n"/>
+      <c r="S706" s="5" t="n"/>
+      <c r="T706" s="6" t="n"/>
+    </row>
+    <row r="707">
+      <c r="H707" s="4" t="n"/>
+      <c r="Q707" s="5" t="n"/>
+      <c r="R707" s="6" t="n"/>
+      <c r="S707" s="5" t="n"/>
+      <c r="T707" s="6" t="n"/>
+    </row>
+    <row r="708">
+      <c r="H708" s="4" t="n"/>
+      <c r="Q708" s="5" t="n"/>
+      <c r="R708" s="6" t="n"/>
+      <c r="S708" s="5" t="n"/>
+      <c r="T708" s="6" t="n"/>
+    </row>
+    <row r="709">
+      <c r="H709" s="4" t="n"/>
+      <c r="Q709" s="5" t="n"/>
+      <c r="R709" s="6" t="n"/>
+      <c r="S709" s="5" t="n"/>
+      <c r="T709" s="6" t="n"/>
+    </row>
+    <row r="710">
+      <c r="H710" s="4" t="n"/>
+      <c r="Q710" s="5" t="n"/>
+      <c r="R710" s="6" t="n"/>
+      <c r="S710" s="5" t="n"/>
+      <c r="T710" s="6" t="n"/>
+    </row>
+    <row r="711">
+      <c r="H711" s="4" t="n"/>
+      <c r="Q711" s="5" t="n"/>
+      <c r="R711" s="6" t="n"/>
+      <c r="S711" s="5" t="n"/>
+      <c r="T711" s="6" t="n"/>
+    </row>
+    <row r="712">
+      <c r="H712" s="4" t="n"/>
+      <c r="Q712" s="5" t="n"/>
+      <c r="R712" s="6" t="n"/>
+      <c r="S712" s="5" t="n"/>
+      <c r="T712" s="6" t="n"/>
+    </row>
+    <row r="713">
+      <c r="H713" s="4" t="n"/>
+      <c r="Q713" s="5" t="n"/>
+      <c r="R713" s="6" t="n"/>
+      <c r="S713" s="5" t="n"/>
+      <c r="T713" s="6" t="n"/>
+    </row>
+    <row r="714">
+      <c r="H714" s="4" t="n"/>
+      <c r="Q714" s="5" t="n"/>
+      <c r="R714" s="6" t="n"/>
+      <c r="S714" s="5" t="n"/>
+      <c r="T714" s="6" t="n"/>
+    </row>
+    <row r="715">
+      <c r="H715" s="4" t="n"/>
+      <c r="Q715" s="5" t="n"/>
+      <c r="R715" s="6" t="n"/>
+      <c r="S715" s="5" t="n"/>
+      <c r="T715" s="6" t="n"/>
+    </row>
+    <row r="716">
+      <c r="H716" s="4" t="n"/>
+      <c r="Q716" s="5" t="n"/>
+      <c r="R716" s="6" t="n"/>
+      <c r="S716" s="5" t="n"/>
+      <c r="T716" s="6" t="n"/>
+    </row>
+    <row r="717">
+      <c r="H717" s="4" t="n"/>
+      <c r="Q717" s="5" t="n"/>
+      <c r="R717" s="6" t="n"/>
+      <c r="S717" s="5" t="n"/>
+      <c r="T717" s="6" t="n"/>
+    </row>
+    <row r="718">
+      <c r="H718" s="4" t="n"/>
+      <c r="Q718" s="5" t="n"/>
+      <c r="R718" s="6" t="n"/>
+      <c r="S718" s="5" t="n"/>
+      <c r="T718" s="6" t="n"/>
+    </row>
+    <row r="719">
+      <c r="H719" s="4" t="n"/>
+      <c r="Q719" s="5" t="n"/>
+      <c r="R719" s="6" t="n"/>
+      <c r="S719" s="5" t="n"/>
+      <c r="T719" s="6" t="n"/>
+    </row>
+    <row r="720">
+      <c r="H720" s="4" t="n"/>
+      <c r="Q720" s="5" t="n"/>
+      <c r="R720" s="6" t="n"/>
+      <c r="S720" s="5" t="n"/>
+      <c r="T720" s="6" t="n"/>
+    </row>
+    <row r="721">
+      <c r="H721" s="4" t="n"/>
+      <c r="Q721" s="5" t="n"/>
+      <c r="R721" s="6" t="n"/>
+      <c r="S721" s="5" t="n"/>
+      <c r="T721" s="6" t="n"/>
+    </row>
+    <row r="722">
+      <c r="H722" s="4" t="n"/>
+      <c r="Q722" s="5" t="n"/>
+      <c r="R722" s="6" t="n"/>
+      <c r="S722" s="5" t="n"/>
+      <c r="T722" s="6" t="n"/>
+    </row>
+    <row r="723">
+      <c r="H723" s="4" t="n"/>
+      <c r="Q723" s="5" t="n"/>
+      <c r="R723" s="6" t="n"/>
+      <c r="S723" s="5" t="n"/>
+      <c r="T723" s="6" t="n"/>
+    </row>
+    <row r="724">
+      <c r="H724" s="4" t="n"/>
+      <c r="Q724" s="5" t="n"/>
+      <c r="R724" s="6" t="n"/>
+      <c r="S724" s="5" t="n"/>
+      <c r="T724" s="6" t="n"/>
+    </row>
+    <row r="725">
+      <c r="H725" s="4" t="n"/>
+      <c r="Q725" s="5" t="n"/>
+      <c r="R725" s="6" t="n"/>
+      <c r="S725" s="5" t="n"/>
+      <c r="T725" s="6" t="n"/>
+    </row>
+    <row r="726">
+      <c r="H726" s="4" t="n"/>
+      <c r="Q726" s="5" t="n"/>
+      <c r="R726" s="6" t="n"/>
+      <c r="S726" s="5" t="n"/>
+      <c r="T726" s="6" t="n"/>
+    </row>
+    <row r="727">
+      <c r="H727" s="4" t="n"/>
+      <c r="Q727" s="5" t="n"/>
+      <c r="R727" s="6" t="n"/>
+      <c r="S727" s="5" t="n"/>
+      <c r="T727" s="6" t="n"/>
+    </row>
+    <row r="728">
+      <c r="H728" s="4" t="n"/>
+      <c r="Q728" s="5" t="n"/>
+      <c r="R728" s="6" t="n"/>
+      <c r="S728" s="5" t="n"/>
+      <c r="T728" s="6" t="n"/>
+    </row>
+    <row r="729">
+      <c r="H729" s="4" t="n"/>
+      <c r="Q729" s="5" t="n"/>
+      <c r="R729" s="6" t="n"/>
+      <c r="S729" s="5" t="n"/>
+      <c r="T729" s="6" t="n"/>
+    </row>
+    <row r="730">
+      <c r="H730" s="4" t="n"/>
+      <c r="Q730" s="5" t="n"/>
+      <c r="R730" s="6" t="n"/>
+      <c r="S730" s="5" t="n"/>
+      <c r="T730" s="6" t="n"/>
+    </row>
+    <row r="731">
+      <c r="H731" s="4" t="n"/>
+      <c r="Q731" s="5" t="n"/>
+      <c r="R731" s="6" t="n"/>
+      <c r="S731" s="5" t="n"/>
+      <c r="T731" s="6" t="n"/>
+    </row>
+    <row r="732">
+      <c r="H732" s="4" t="n"/>
+      <c r="Q732" s="5" t="n"/>
+      <c r="R732" s="6" t="n"/>
+      <c r="S732" s="5" t="n"/>
+      <c r="T732" s="6" t="n"/>
+    </row>
+    <row r="733">
+      <c r="H733" s="4" t="n"/>
+      <c r="Q733" s="5" t="n"/>
+      <c r="R733" s="6" t="n"/>
+      <c r="S733" s="5" t="n"/>
+      <c r="T733" s="6" t="n"/>
+    </row>
+    <row r="734">
+      <c r="H734" s="4" t="n"/>
+      <c r="Q734" s="5" t="n"/>
+      <c r="R734" s="6" t="n"/>
+      <c r="S734" s="5" t="n"/>
+      <c r="T734" s="6" t="n"/>
+    </row>
+    <row r="735">
+      <c r="H735" s="4" t="n"/>
+      <c r="Q735" s="5" t="n"/>
+      <c r="R735" s="6" t="n"/>
+      <c r="S735" s="5" t="n"/>
+      <c r="T735" s="6" t="n"/>
+    </row>
+    <row r="736">
+      <c r="H736" s="4" t="n"/>
+      <c r="Q736" s="5" t="n"/>
+      <c r="R736" s="6" t="n"/>
+      <c r="S736" s="5" t="n"/>
+      <c r="T736" s="6" t="n"/>
+    </row>
+    <row r="737">
+      <c r="H737" s="4" t="n"/>
+      <c r="Q737" s="5" t="n"/>
+      <c r="R737" s="6" t="n"/>
+      <c r="S737" s="5" t="n"/>
+      <c r="T737" s="6" t="n"/>
+    </row>
+    <row r="738">
+      <c r="H738" s="4" t="n"/>
+      <c r="Q738" s="5" t="n"/>
+      <c r="R738" s="6" t="n"/>
+      <c r="S738" s="5" t="n"/>
+      <c r="T738" s="6" t="n"/>
+    </row>
+    <row r="739">
+      <c r="H739" s="4" t="n"/>
+      <c r="Q739" s="5" t="n"/>
+      <c r="R739" s="6" t="n"/>
+      <c r="S739" s="5" t="n"/>
+      <c r="T739" s="6" t="n"/>
+    </row>
+    <row r="740">
+      <c r="H740" s="4" t="n"/>
+      <c r="Q740" s="5" t="n"/>
+      <c r="R740" s="6" t="n"/>
+      <c r="S740" s="5" t="n"/>
+      <c r="T740" s="6" t="n"/>
+    </row>
+    <row r="741">
+      <c r="H741" s="4" t="n"/>
+      <c r="Q741" s="5" t="n"/>
+      <c r="R741" s="6" t="n"/>
+      <c r="S741" s="5" t="n"/>
+      <c r="T741" s="6" t="n"/>
+    </row>
+    <row r="742">
+      <c r="H742" s="4" t="n"/>
+      <c r="Q742" s="5" t="n"/>
+      <c r="R742" s="6" t="n"/>
+      <c r="S742" s="5" t="n"/>
+      <c r="T742" s="6" t="n"/>
+    </row>
+    <row r="743">
+      <c r="H743" s="4" t="n"/>
+      <c r="Q743" s="5" t="n"/>
+      <c r="R743" s="6" t="n"/>
+      <c r="S743" s="5" t="n"/>
+      <c r="T743" s="6" t="n"/>
+    </row>
+    <row r="744">
+      <c r="H744" s="4" t="n"/>
+      <c r="Q744" s="5" t="n"/>
+      <c r="R744" s="6" t="n"/>
+      <c r="S744" s="5" t="n"/>
+      <c r="T744" s="6" t="n"/>
+    </row>
+    <row r="745">
+      <c r="H745" s="4" t="n"/>
+      <c r="Q745" s="5" t="n"/>
+      <c r="R745" s="6" t="n"/>
+      <c r="S745" s="5" t="n"/>
+      <c r="T745" s="6" t="n"/>
+    </row>
+    <row r="746">
+      <c r="H746" s="4" t="n"/>
+      <c r="Q746" s="5" t="n"/>
+      <c r="R746" s="6" t="n"/>
+      <c r="S746" s="5" t="n"/>
+      <c r="T746" s="6" t="n"/>
+    </row>
+    <row r="747">
+      <c r="H747" s="4" t="n"/>
+      <c r="Q747" s="5" t="n"/>
+      <c r="R747" s="6" t="n"/>
+      <c r="S747" s="5" t="n"/>
+      <c r="T747" s="6" t="n"/>
+    </row>
+    <row r="748">
+      <c r="H748" s="4" t="n"/>
+      <c r="Q748" s="5" t="n"/>
+      <c r="R748" s="6" t="n"/>
+      <c r="S748" s="5" t="n"/>
+      <c r="T748" s="6" t="n"/>
+    </row>
+    <row r="749">
+      <c r="H749" s="4" t="n"/>
+      <c r="Q749" s="5" t="n"/>
+      <c r="R749" s="6" t="n"/>
+      <c r="S749" s="5" t="n"/>
+      <c r="T749" s="6" t="n"/>
+    </row>
+    <row r="750">
+      <c r="H750" s="4" t="n"/>
+      <c r="Q750" s="5" t="n"/>
+      <c r="R750" s="6" t="n"/>
+      <c r="S750" s="5" t="n"/>
+      <c r="T750" s="6" t="n"/>
+    </row>
+    <row r="751">
+      <c r="H751" s="4" t="n"/>
+      <c r="Q751" s="5" t="n"/>
+      <c r="R751" s="6" t="n"/>
+      <c r="S751" s="5" t="n"/>
+      <c r="T751" s="6" t="n"/>
+    </row>
+    <row r="752">
+      <c r="H752" s="4" t="n"/>
+      <c r="Q752" s="5" t="n"/>
+      <c r="R752" s="6" t="n"/>
+      <c r="S752" s="5" t="n"/>
+      <c r="T752" s="6" t="n"/>
+    </row>
+    <row r="753">
+      <c r="H753" s="4" t="n"/>
+      <c r="Q753" s="5" t="n"/>
+      <c r="R753" s="6" t="n"/>
+      <c r="S753" s="5" t="n"/>
+      <c r="T753" s="6" t="n"/>
+    </row>
+    <row r="754">
+      <c r="H754" s="4" t="n"/>
+      <c r="Q754" s="5" t="n"/>
+      <c r="R754" s="6" t="n"/>
+      <c r="S754" s="5" t="n"/>
+      <c r="T754" s="6" t="n"/>
+    </row>
+    <row r="755">
+      <c r="H755" s="4" t="n"/>
+      <c r="Q755" s="5" t="n"/>
+      <c r="R755" s="6" t="n"/>
+      <c r="S755" s="5" t="n"/>
+      <c r="T755" s="6" t="n"/>
+    </row>
+    <row r="756">
+      <c r="H756" s="4" t="n"/>
+      <c r="Q756" s="5" t="n"/>
+      <c r="R756" s="6" t="n"/>
+      <c r="S756" s="5" t="n"/>
+      <c r="T756" s="6" t="n"/>
+    </row>
+    <row r="757">
+      <c r="H757" s="4" t="n"/>
+      <c r="Q757" s="5" t="n"/>
+      <c r="R757" s="6" t="n"/>
+      <c r="S757" s="5" t="n"/>
+      <c r="T757" s="6" t="n"/>
+    </row>
+    <row r="758">
+      <c r="H758" s="4" t="n"/>
+      <c r="Q758" s="5" t="n"/>
+      <c r="R758" s="6" t="n"/>
+      <c r="S758" s="5" t="n"/>
+      <c r="T758" s="6" t="n"/>
+    </row>
+    <row r="759">
+      <c r="H759" s="4" t="n"/>
+      <c r="Q759" s="5" t="n"/>
+      <c r="R759" s="6" t="n"/>
+      <c r="S759" s="5" t="n"/>
+      <c r="T759" s="6" t="n"/>
+    </row>
+    <row r="760">
+      <c r="H760" s="4" t="n"/>
+      <c r="Q760" s="5" t="n"/>
+      <c r="R760" s="6" t="n"/>
+      <c r="S760" s="5" t="n"/>
+      <c r="T760" s="6" t="n"/>
+    </row>
+    <row r="761">
+      <c r="H761" s="4" t="n"/>
+      <c r="Q761" s="5" t="n"/>
+      <c r="R761" s="6" t="n"/>
+      <c r="S761" s="5" t="n"/>
+      <c r="T761" s="6" t="n"/>
+    </row>
+    <row r="762">
+      <c r="H762" s="4" t="n"/>
+      <c r="Q762" s="5" t="n"/>
+      <c r="R762" s="6" t="n"/>
+      <c r="S762" s="5" t="n"/>
+      <c r="T762" s="6" t="n"/>
+    </row>
+    <row r="763">
+      <c r="H763" s="4" t="n"/>
+      <c r="Q763" s="5" t="n"/>
+      <c r="R763" s="6" t="n"/>
+      <c r="S763" s="5" t="n"/>
+      <c r="T763" s="6" t="n"/>
+    </row>
+    <row r="764">
+      <c r="H764" s="4" t="n"/>
+      <c r="Q764" s="5" t="n"/>
+      <c r="R764" s="6" t="n"/>
+      <c r="S764" s="5" t="n"/>
+      <c r="T764" s="6" t="n"/>
+    </row>
+    <row r="765">
+      <c r="H765" s="4" t="n"/>
+      <c r="Q765" s="5" t="n"/>
+      <c r="R765" s="6" t="n"/>
+      <c r="S765" s="5" t="n"/>
+      <c r="T765" s="6" t="n"/>
+    </row>
+    <row r="766">
+      <c r="H766" s="4" t="n"/>
+      <c r="Q766" s="5" t="n"/>
+      <c r="R766" s="6" t="n"/>
+      <c r="S766" s="5" t="n"/>
+      <c r="T766" s="6" t="n"/>
+    </row>
+    <row r="767">
+      <c r="H767" s="4" t="n"/>
+      <c r="Q767" s="5" t="n"/>
+      <c r="R767" s="6" t="n"/>
+      <c r="S767" s="5" t="n"/>
+      <c r="T767" s="6" t="n"/>
+    </row>
+    <row r="768">
+      <c r="H768" s="4" t="n"/>
+      <c r="Q768" s="5" t="n"/>
+      <c r="R768" s="6" t="n"/>
+      <c r="S768" s="5" t="n"/>
+      <c r="T768" s="6" t="n"/>
+    </row>
+    <row r="769">
+      <c r="H769" s="4" t="n"/>
+      <c r="Q769" s="5" t="n"/>
+      <c r="R769" s="6" t="n"/>
+      <c r="S769" s="5" t="n"/>
+      <c r="T769" s="6" t="n"/>
+    </row>
+    <row r="770">
+      <c r="H770" s="4" t="n"/>
+      <c r="Q770" s="5" t="n"/>
+      <c r="R770" s="6" t="n"/>
+      <c r="S770" s="5" t="n"/>
+      <c r="T770" s="6" t="n"/>
+    </row>
+    <row r="771">
+      <c r="H771" s="4" t="n"/>
+      <c r="Q771" s="5" t="n"/>
+      <c r="R771" s="6" t="n"/>
+      <c r="S771" s="5" t="n"/>
+      <c r="T771" s="6" t="n"/>
+    </row>
+    <row r="772">
+      <c r="H772" s="4" t="n"/>
+      <c r="Q772" s="5" t="n"/>
+      <c r="R772" s="6" t="n"/>
+      <c r="S772" s="5" t="n"/>
+      <c r="T772" s="6" t="n"/>
+    </row>
+    <row r="773">
+      <c r="H773" s="4" t="n"/>
+      <c r="Q773" s="5" t="n"/>
+      <c r="R773" s="6" t="n"/>
+      <c r="S773" s="5" t="n"/>
+      <c r="T773" s="6" t="n"/>
+    </row>
+    <row r="774">
+      <c r="H774" s="4" t="n"/>
+      <c r="Q774" s="5" t="n"/>
+      <c r="R774" s="6" t="n"/>
+      <c r="S774" s="5" t="n"/>
+      <c r="T774" s="6" t="n"/>
+    </row>
+    <row r="775">
+      <c r="H775" s="4" t="n"/>
+      <c r="Q775" s="5" t="n"/>
+      <c r="R775" s="6" t="n"/>
+      <c r="S775" s="5" t="n"/>
+      <c r="T775" s="6" t="n"/>
+    </row>
+    <row r="776">
+      <c r="H776" s="4" t="n"/>
+      <c r="Q776" s="5" t="n"/>
+      <c r="R776" s="6" t="n"/>
+      <c r="S776" s="5" t="n"/>
+      <c r="T776" s="6" t="n"/>
+    </row>
+    <row r="777">
+      <c r="H777" s="4" t="n"/>
+      <c r="Q777" s="5" t="n"/>
+      <c r="R777" s="6" t="n"/>
+      <c r="S777" s="5" t="n"/>
+      <c r="T777" s="6" t="n"/>
+    </row>
+    <row r="778">
+      <c r="H778" s="4" t="n"/>
+      <c r="Q778" s="5" t="n"/>
+      <c r="R778" s="6" t="n"/>
+      <c r="S778" s="5" t="n"/>
+      <c r="T778" s="6" t="n"/>
+    </row>
+    <row r="779">
+      <c r="H779" s="4" t="n"/>
+      <c r="Q779" s="5" t="n"/>
+      <c r="R779" s="6" t="n"/>
+      <c r="S779" s="5" t="n"/>
+      <c r="T779" s="6" t="n"/>
+    </row>
+    <row r="780">
+      <c r="H780" s="4" t="n"/>
+      <c r="Q780" s="5" t="n"/>
+      <c r="R780" s="6" t="n"/>
+      <c r="S780" s="5" t="n"/>
+      <c r="T780" s="6" t="n"/>
+    </row>
+    <row r="781">
+      <c r="H781" s="4" t="n"/>
+      <c r="Q781" s="5" t="n"/>
+      <c r="R781" s="6" t="n"/>
+      <c r="S781" s="5" t="n"/>
+      <c r="T781" s="6" t="n"/>
+    </row>
+    <row r="782">
+      <c r="H782" s="4" t="n"/>
+      <c r="Q782" s="5" t="n"/>
+      <c r="R782" s="6" t="n"/>
+      <c r="S782" s="5" t="n"/>
+      <c r="T782" s="6" t="n"/>
+    </row>
+    <row r="783">
+      <c r="H783" s="4" t="n"/>
+      <c r="Q783" s="5" t="n"/>
+      <c r="R783" s="6" t="n"/>
+      <c r="S783" s="5" t="n"/>
+      <c r="T783" s="6" t="n"/>
+    </row>
+    <row r="784">
+      <c r="H784" s="4" t="n"/>
+      <c r="Q784" s="5" t="n"/>
+      <c r="R784" s="6" t="n"/>
+      <c r="S784" s="5" t="n"/>
+      <c r="T784" s="6" t="n"/>
+    </row>
+    <row r="785">
+      <c r="H785" s="4" t="n"/>
+      <c r="Q785" s="5" t="n"/>
+      <c r="R785" s="6" t="n"/>
+      <c r="S785" s="5" t="n"/>
+      <c r="T785" s="6" t="n"/>
+    </row>
+    <row r="786">
+      <c r="H786" s="4" t="n"/>
+      <c r="Q786" s="5" t="n"/>
+      <c r="R786" s="6" t="n"/>
+      <c r="S786" s="5" t="n"/>
+      <c r="T786" s="6" t="n"/>
+    </row>
+    <row r="787">
+      <c r="H787" s="4" t="n"/>
+      <c r="Q787" s="5" t="n"/>
+      <c r="R787" s="6" t="n"/>
+      <c r="S787" s="5" t="n"/>
+      <c r="T787" s="6" t="n"/>
+    </row>
+    <row r="788">
+      <c r="H788" s="4" t="n"/>
+      <c r="Q788" s="5" t="n"/>
+      <c r="R788" s="6" t="n"/>
+      <c r="S788" s="5" t="n"/>
+      <c r="T788" s="6" t="n"/>
+    </row>
+    <row r="789">
+      <c r="H789" s="4" t="n"/>
+      <c r="Q789" s="5" t="n"/>
+      <c r="R789" s="6" t="n"/>
+      <c r="S789" s="5" t="n"/>
+      <c r="T789" s="6" t="n"/>
+    </row>
+    <row r="790">
+      <c r="H790" s="4" t="n"/>
+      <c r="Q790" s="5" t="n"/>
+      <c r="R790" s="6" t="n"/>
+      <c r="S790" s="5" t="n"/>
+      <c r="T790" s="6" t="n"/>
+    </row>
+    <row r="791">
+      <c r="H791" s="4" t="n"/>
+      <c r="Q791" s="5" t="n"/>
+      <c r="R791" s="6" t="n"/>
+      <c r="S791" s="5" t="n"/>
+      <c r="T791" s="6" t="n"/>
+    </row>
+    <row r="792">
+      <c r="H792" s="4" t="n"/>
+      <c r="Q792" s="5" t="n"/>
+      <c r="R792" s="6" t="n"/>
+      <c r="S792" s="5" t="n"/>
+      <c r="T792" s="6" t="n"/>
+    </row>
+    <row r="793">
+      <c r="H793" s="4" t="n"/>
+      <c r="Q793" s="5" t="n"/>
+      <c r="R793" s="6" t="n"/>
+      <c r="S793" s="5" t="n"/>
+      <c r="T793" s="6" t="n"/>
+    </row>
+    <row r="794">
+      <c r="H794" s="4" t="n"/>
+      <c r="Q794" s="5" t="n"/>
+      <c r="R794" s="6" t="n"/>
+      <c r="S794" s="5" t="n"/>
+      <c r="T794" s="6" t="n"/>
+    </row>
+    <row r="795">
+      <c r="H795" s="4" t="n"/>
+      <c r="Q795" s="5" t="n"/>
+      <c r="R795" s="6" t="n"/>
+      <c r="S795" s="5" t="n"/>
+      <c r="T795" s="6" t="n"/>
+    </row>
+    <row r="796">
+      <c r="H796" s="4" t="n"/>
+      <c r="Q796" s="5" t="n"/>
+      <c r="R796" s="6" t="n"/>
+      <c r="S796" s="5" t="n"/>
+      <c r="T796" s="6" t="n"/>
+    </row>
+    <row r="797">
+      <c r="H797" s="4" t="n"/>
+      <c r="Q797" s="5" t="n"/>
+      <c r="R797" s="6" t="n"/>
+      <c r="S797" s="5" t="n"/>
+      <c r="T797" s="6" t="n"/>
+    </row>
+    <row r="798">
+      <c r="H798" s="4" t="n"/>
+      <c r="Q798" s="5" t="n"/>
+      <c r="R798" s="6" t="n"/>
+      <c r="S798" s="5" t="n"/>
+      <c r="T798" s="6" t="n"/>
+    </row>
+    <row r="799">
+      <c r="H799" s="4" t="n"/>
+      <c r="Q799" s="5" t="n"/>
+      <c r="R799" s="6" t="n"/>
+      <c r="S799" s="5" t="n"/>
+      <c r="T799" s="6" t="n"/>
+    </row>
+    <row r="800">
+      <c r="H800" s="4" t="n"/>
+      <c r="Q800" s="5" t="n"/>
+      <c r="R800" s="6" t="n"/>
+      <c r="S800" s="5" t="n"/>
+      <c r="T800" s="6" t="n"/>
+    </row>
+    <row r="801">
+      <c r="H801" s="4" t="n"/>
+      <c r="Q801" s="5" t="n"/>
+      <c r="R801" s="6" t="n"/>
+      <c r="S801" s="5" t="n"/>
+      <c r="T801" s="6" t="n"/>
+    </row>
+    <row r="802">
+      <c r="H802" s="4" t="n"/>
+      <c r="Q802" s="5" t="n"/>
+      <c r="R802" s="6" t="n"/>
+      <c r="S802" s="5" t="n"/>
+      <c r="T802" s="6" t="n"/>
+    </row>
+    <row r="803">
+      <c r="H803" s="4" t="n"/>
+      <c r="Q803" s="5" t="n"/>
+      <c r="R803" s="6" t="n"/>
+      <c r="S803" s="5" t="n"/>
+      <c r="T803" s="6" t="n"/>
+    </row>
+    <row r="804">
+      <c r="H804" s="4" t="n"/>
+      <c r="Q804" s="5" t="n"/>
+      <c r="R804" s="6" t="n"/>
+      <c r="S804" s="5" t="n"/>
+      <c r="T804" s="6" t="n"/>
+    </row>
+    <row r="805">
+      <c r="H805" s="4" t="n"/>
+      <c r="Q805" s="5" t="n"/>
+      <c r="R805" s="6" t="n"/>
+      <c r="S805" s="5" t="n"/>
+      <c r="T805" s="6" t="n"/>
+    </row>
+    <row r="806">
+      <c r="H806" s="4" t="n"/>
+      <c r="Q806" s="5" t="n"/>
+      <c r="R806" s="6" t="n"/>
+      <c r="S806" s="5" t="n"/>
+      <c r="T806" s="6" t="n"/>
+    </row>
+    <row r="807">
+      <c r="H807" s="4" t="n"/>
+      <c r="Q807" s="5" t="n"/>
+      <c r="R807" s="6" t="n"/>
+      <c r="S807" s="5" t="n"/>
+      <c r="T807" s="6" t="n"/>
+    </row>
+    <row r="808">
+      <c r="H808" s="4" t="n"/>
+      <c r="Q808" s="5" t="n"/>
+      <c r="R808" s="6" t="n"/>
+      <c r="S808" s="5" t="n"/>
+      <c r="T808" s="6" t="n"/>
+    </row>
+    <row r="809">
+      <c r="H809" s="4" t="n"/>
+      <c r="Q809" s="5" t="n"/>
+      <c r="R809" s="6" t="n"/>
+      <c r="S809" s="5" t="n"/>
+      <c r="T809" s="6" t="n"/>
+    </row>
+    <row r="810">
+      <c r="H810" s="4" t="n"/>
+      <c r="Q810" s="5" t="n"/>
+      <c r="R810" s="6" t="n"/>
+      <c r="S810" s="5" t="n"/>
+      <c r="T810" s="6" t="n"/>
+    </row>
+    <row r="811">
+      <c r="H811" s="4" t="n"/>
+      <c r="Q811" s="5" t="n"/>
+      <c r="R811" s="6" t="n"/>
+      <c r="S811" s="5" t="n"/>
+      <c r="T811" s="6" t="n"/>
+    </row>
+    <row r="812">
+      <c r="H812" s="4" t="n"/>
+      <c r="Q812" s="5" t="n"/>
+      <c r="R812" s="6" t="n"/>
+      <c r="S812" s="5" t="n"/>
+      <c r="T812" s="6" t="n"/>
+    </row>
+    <row r="813">
+      <c r="H813" s="4" t="n"/>
+      <c r="Q813" s="5" t="n"/>
+      <c r="R813" s="6" t="n"/>
+      <c r="S813" s="5" t="n"/>
+      <c r="T813" s="6" t="n"/>
+    </row>
+    <row r="814">
+      <c r="H814" s="4" t="n"/>
+      <c r="Q814" s="5" t="n"/>
+      <c r="R814" s="6" t="n"/>
+      <c r="S814" s="5" t="n"/>
+      <c r="T814" s="6" t="n"/>
+    </row>
+    <row r="815">
+      <c r="H815" s="4" t="n"/>
+      <c r="Q815" s="5" t="n"/>
+      <c r="R815" s="6" t="n"/>
+      <c r="S815" s="5" t="n"/>
+      <c r="T815" s="6" t="n"/>
+    </row>
+    <row r="816">
+      <c r="H816" s="4" t="n"/>
+      <c r="Q816" s="5" t="n"/>
+      <c r="R816" s="6" t="n"/>
+      <c r="S816" s="5" t="n"/>
+      <c r="T816" s="6" t="n"/>
+    </row>
+    <row r="817">
+      <c r="H817" s="4" t="n"/>
+      <c r="Q817" s="5" t="n"/>
+      <c r="R817" s="6" t="n"/>
+      <c r="S817" s="5" t="n"/>
+      <c r="T817" s="6" t="n"/>
+    </row>
+    <row r="818">
+      <c r="H818" s="4" t="n"/>
+      <c r="Q818" s="5" t="n"/>
+      <c r="R818" s="6" t="n"/>
+      <c r="S818" s="5" t="n"/>
+      <c r="T818" s="6" t="n"/>
+    </row>
+    <row r="819">
+      <c r="H819" s="4" t="n"/>
+      <c r="Q819" s="5" t="n"/>
+      <c r="R819" s="6" t="n"/>
+      <c r="S819" s="5" t="n"/>
+      <c r="T819" s="6" t="n"/>
+    </row>
+    <row r="820">
+      <c r="H820" s="4" t="n"/>
+      <c r="Q820" s="5" t="n"/>
+      <c r="R820" s="6" t="n"/>
+      <c r="S820" s="5" t="n"/>
+      <c r="T820" s="6" t="n"/>
+    </row>
+    <row r="821">
+      <c r="H821" s="4" t="n"/>
+      <c r="Q821" s="5" t="n"/>
+      <c r="R821" s="6" t="n"/>
+      <c r="S821" s="5" t="n"/>
+      <c r="T821" s="6" t="n"/>
+    </row>
+    <row r="822">
+      <c r="H822" s="4" t="n"/>
+      <c r="Q822" s="5" t="n"/>
+      <c r="R822" s="6" t="n"/>
+      <c r="S822" s="5" t="n"/>
+      <c r="T822" s="6" t="n"/>
+    </row>
+    <row r="823">
+      <c r="H823" s="4" t="n"/>
+      <c r="Q823" s="5" t="n"/>
+      <c r="R823" s="6" t="n"/>
+      <c r="S823" s="5" t="n"/>
+      <c r="T823" s="6" t="n"/>
+    </row>
+    <row r="824">
+      <c r="H824" s="4" t="n"/>
+      <c r="Q824" s="5" t="n"/>
+      <c r="R824" s="6" t="n"/>
+      <c r="S824" s="5" t="n"/>
+      <c r="T824" s="6" t="n"/>
+    </row>
+    <row r="825">
+      <c r="H825" s="4" t="n"/>
+      <c r="Q825" s="5" t="n"/>
+      <c r="R825" s="6" t="n"/>
+      <c r="S825" s="5" t="n"/>
+      <c r="T825" s="6" t="n"/>
+    </row>
+    <row r="826">
+      <c r="H826" s="4" t="n"/>
+      <c r="Q826" s="5" t="n"/>
+      <c r="R826" s="6" t="n"/>
+      <c r="S826" s="5" t="n"/>
+      <c r="T826" s="6" t="n"/>
+    </row>
+    <row r="827">
+      <c r="H827" s="4" t="n"/>
+      <c r="Q827" s="5" t="n"/>
+      <c r="R827" s="6" t="n"/>
+      <c r="S827" s="5" t="n"/>
+      <c r="T827" s="6" t="n"/>
+    </row>
+    <row r="828">
+      <c r="H828" s="4" t="n"/>
+      <c r="Q828" s="5" t="n"/>
+      <c r="R828" s="6" t="n"/>
+      <c r="S828" s="5" t="n"/>
+      <c r="T828" s="6" t="n"/>
+    </row>
+    <row r="829">
+      <c r="H829" s="4" t="n"/>
+      <c r="Q829" s="5" t="n"/>
+      <c r="R829" s="6" t="n"/>
+      <c r="S829" s="5" t="n"/>
+      <c r="T829" s="6" t="n"/>
+    </row>
+    <row r="830">
+      <c r="H830" s="4" t="n"/>
+      <c r="Q830" s="5" t="n"/>
+      <c r="R830" s="6" t="n"/>
+      <c r="S830" s="5" t="n"/>
+      <c r="T830" s="6" t="n"/>
+    </row>
+    <row r="831">
+      <c r="H831" s="4" t="n"/>
+      <c r="Q831" s="5" t="n"/>
+      <c r="R831" s="6" t="n"/>
+      <c r="S831" s="5" t="n"/>
+      <c r="T831" s="6" t="n"/>
+    </row>
+    <row r="832">
+      <c r="H832" s="4" t="n"/>
+      <c r="Q832" s="5" t="n"/>
+      <c r="R832" s="6" t="n"/>
+      <c r="S832" s="5" t="n"/>
+      <c r="T832" s="6" t="n"/>
+    </row>
+    <row r="833">
+      <c r="H833" s="4" t="n"/>
+      <c r="Q833" s="5" t="n"/>
+      <c r="R833" s="6" t="n"/>
+      <c r="S833" s="5" t="n"/>
+      <c r="T833" s="6" t="n"/>
+    </row>
+    <row r="834">
+      <c r="H834" s="4" t="n"/>
+      <c r="Q834" s="5" t="n"/>
+      <c r="R834" s="6" t="n"/>
+      <c r="S834" s="5" t="n"/>
+      <c r="T834" s="6" t="n"/>
+    </row>
+    <row r="835">
+      <c r="H835" s="4" t="n"/>
+      <c r="Q835" s="5" t="n"/>
+      <c r="R835" s="6" t="n"/>
+      <c r="S835" s="5" t="n"/>
+      <c r="T835" s="6" t="n"/>
+    </row>
+    <row r="836">
+      <c r="H836" s="4" t="n"/>
+      <c r="Q836" s="5" t="n"/>
+      <c r="R836" s="6" t="n"/>
+      <c r="S836" s="5" t="n"/>
+      <c r="T836" s="6" t="n"/>
+    </row>
+    <row r="837">
+      <c r="H837" s="4" t="n"/>
+      <c r="Q837" s="5" t="n"/>
+      <c r="R837" s="6" t="n"/>
+      <c r="S837" s="5" t="n"/>
+      <c r="T837" s="6" t="n"/>
+    </row>
+    <row r="838">
+      <c r="H838" s="4" t="n"/>
+      <c r="Q838" s="5" t="n"/>
+      <c r="R838" s="6" t="n"/>
+      <c r="S838" s="5" t="n"/>
+      <c r="T838" s="6" t="n"/>
+    </row>
+    <row r="839">
+      <c r="H839" s="4" t="n"/>
+      <c r="Q839" s="5" t="n"/>
+      <c r="R839" s="6" t="n"/>
+      <c r="S839" s="5" t="n"/>
+      <c r="T839" s="6" t="n"/>
+    </row>
+    <row r="840">
+      <c r="H840" s="4" t="n"/>
+      <c r="Q840" s="5" t="n"/>
+      <c r="R840" s="6" t="n"/>
+      <c r="S840" s="5" t="n"/>
+      <c r="T840" s="6" t="n"/>
+    </row>
+    <row r="841">
+      <c r="H841" s="4" t="n"/>
+      <c r="Q841" s="5" t="n"/>
+      <c r="R841" s="6" t="n"/>
+      <c r="S841" s="5" t="n"/>
+      <c r="T841" s="6" t="n"/>
+    </row>
+    <row r="842">
+      <c r="H842" s="4" t="n"/>
+      <c r="Q842" s="5" t="n"/>
+      <c r="R842" s="6" t="n"/>
+      <c r="S842" s="5" t="n"/>
+      <c r="T842" s="6" t="n"/>
+    </row>
+    <row r="843">
+      <c r="H843" s="4" t="n"/>
+      <c r="Q843" s="5" t="n"/>
+      <c r="R843" s="6" t="n"/>
+      <c r="S843" s="5" t="n"/>
+      <c r="T843" s="6" t="n"/>
+    </row>
+    <row r="844">
+      <c r="H844" s="4" t="n"/>
+      <c r="Q844" s="5" t="n"/>
+      <c r="R844" s="6" t="n"/>
+      <c r="S844" s="5" t="n"/>
+      <c r="T844" s="6" t="n"/>
+    </row>
+    <row r="845">
+      <c r="H845" s="4" t="n"/>
+      <c r="Q845" s="5" t="n"/>
+      <c r="R845" s="6" t="n"/>
+      <c r="S845" s="5" t="n"/>
+      <c r="T845" s="6" t="n"/>
+    </row>
+    <row r="846">
+      <c r="H846" s="4" t="n"/>
+      <c r="Q846" s="5" t="n"/>
+      <c r="R846" s="6" t="n"/>
+      <c r="S846" s="5" t="n"/>
+      <c r="T846" s="6" t="n"/>
+    </row>
+    <row r="847">
+      <c r="H847" s="4" t="n"/>
+      <c r="Q847" s="5" t="n"/>
+      <c r="R847" s="6" t="n"/>
+      <c r="S847" s="5" t="n"/>
+      <c r="T847" s="6" t="n"/>
+    </row>
+    <row r="848">
+      <c r="H848" s="4" t="n"/>
+      <c r="Q848" s="5" t="n"/>
+      <c r="R848" s="6" t="n"/>
+      <c r="S848" s="5" t="n"/>
+      <c r="T848" s="6" t="n"/>
+    </row>
+    <row r="849">
+      <c r="H849" s="4" t="n"/>
+      <c r="Q849" s="5" t="n"/>
+      <c r="R849" s="6" t="n"/>
+      <c r="S849" s="5" t="n"/>
+      <c r="T849" s="6" t="n"/>
+    </row>
+    <row r="850">
+      <c r="H850" s="4" t="n"/>
+      <c r="Q850" s="5" t="n"/>
+      <c r="R850" s="6" t="n"/>
+      <c r="S850" s="5" t="n"/>
+      <c r="T850" s="6" t="n"/>
+    </row>
+    <row r="851">
+      <c r="H851" s="4" t="n"/>
+      <c r="Q851" s="5" t="n"/>
+      <c r="R851" s="6" t="n"/>
+      <c r="S851" s="5" t="n"/>
+      <c r="T851" s="6" t="n"/>
+    </row>
+    <row r="852">
+      <c r="H852" s="4" t="n"/>
+      <c r="Q852" s="5" t="n"/>
+      <c r="R852" s="6" t="n"/>
+      <c r="S852" s="5" t="n"/>
+      <c r="T852" s="6" t="n"/>
+    </row>
+    <row r="853">
+      <c r="H853" s="4" t="n"/>
+      <c r="Q853" s="5" t="n"/>
+      <c r="R853" s="6" t="n"/>
+      <c r="S853" s="5" t="n"/>
+      <c r="T853" s="6" t="n"/>
+    </row>
+    <row r="854">
+      <c r="H854" s="4" t="n"/>
+      <c r="Q854" s="5" t="n"/>
+      <c r="R854" s="6" t="n"/>
+      <c r="S854" s="5" t="n"/>
+      <c r="T854" s="6" t="n"/>
+    </row>
+    <row r="855">
+      <c r="H855" s="4" t="n"/>
+      <c r="Q855" s="5" t="n"/>
+      <c r="R855" s="6" t="n"/>
+      <c r="S855" s="5" t="n"/>
+      <c r="T855" s="6" t="n"/>
+    </row>
+    <row r="856">
+      <c r="H856" s="4" t="n"/>
+      <c r="Q856" s="5" t="n"/>
+      <c r="R856" s="6" t="n"/>
+      <c r="S856" s="5" t="n"/>
+      <c r="T856" s="6" t="n"/>
+    </row>
+    <row r="857">
+      <c r="H857" s="4" t="n"/>
+      <c r="Q857" s="5" t="n"/>
+      <c r="R857" s="6" t="n"/>
+      <c r="S857" s="5" t="n"/>
+      <c r="T857" s="6" t="n"/>
+    </row>
+    <row r="858">
+      <c r="H858" s="4" t="n"/>
+      <c r="Q858" s="5" t="n"/>
+      <c r="R858" s="6" t="n"/>
+      <c r="S858" s="5" t="n"/>
+      <c r="T858" s="6" t="n"/>
+    </row>
+    <row r="859">
+      <c r="H859" s="4" t="n"/>
+      <c r="Q859" s="5" t="n"/>
+      <c r="R859" s="6" t="n"/>
+      <c r="S859" s="5" t="n"/>
+      <c r="T859" s="6" t="n"/>
+    </row>
+    <row r="860">
+      <c r="H860" s="4" t="n"/>
+      <c r="Q860" s="5" t="n"/>
+      <c r="R860" s="6" t="n"/>
+      <c r="S860" s="5" t="n"/>
+      <c r="T860" s="6" t="n"/>
+    </row>
+    <row r="861">
+      <c r="H861" s="4" t="n"/>
+      <c r="Q861" s="5" t="n"/>
+      <c r="R861" s="6" t="n"/>
+      <c r="S861" s="5" t="n"/>
+      <c r="T861" s="6" t="n"/>
+    </row>
+    <row r="862">
+      <c r="H862" s="4" t="n"/>
+      <c r="Q862" s="5" t="n"/>
+      <c r="R862" s="6" t="n"/>
+      <c r="S862" s="5" t="n"/>
+      <c r="T862" s="6" t="n"/>
+    </row>
+    <row r="863">
+      <c r="H863" s="4" t="n"/>
+      <c r="Q863" s="5" t="n"/>
+      <c r="R863" s="6" t="n"/>
+      <c r="S863" s="5" t="n"/>
+      <c r="T863" s="6" t="n"/>
+    </row>
+    <row r="864">
+      <c r="H864" s="4" t="n"/>
+      <c r="Q864" s="5" t="n"/>
+      <c r="R864" s="6" t="n"/>
+      <c r="S864" s="5" t="n"/>
+      <c r="T864" s="6" t="n"/>
+    </row>
+    <row r="865">
+      <c r="H865" s="4" t="n"/>
+      <c r="Q865" s="5" t="n"/>
+      <c r="R865" s="6" t="n"/>
+      <c r="S865" s="5" t="n"/>
+      <c r="T865" s="6" t="n"/>
+    </row>
+    <row r="866">
+      <c r="H866" s="4" t="n"/>
+      <c r="Q866" s="5" t="n"/>
+      <c r="R866" s="6" t="n"/>
+      <c r="S866" s="5" t="n"/>
+      <c r="T866" s="6" t="n"/>
+    </row>
+    <row r="867">
+      <c r="H867" s="4" t="n"/>
+      <c r="Q867" s="5" t="n"/>
+      <c r="R867" s="6" t="n"/>
+      <c r="S867" s="5" t="n"/>
+      <c r="T867" s="6" t="n"/>
+    </row>
+    <row r="868">
+      <c r="H868" s="4" t="n"/>
+      <c r="Q868" s="5" t="n"/>
+      <c r="R868" s="6" t="n"/>
+      <c r="S868" s="5" t="n"/>
+      <c r="T868" s="6" t="n"/>
+    </row>
+    <row r="869">
+      <c r="H869" s="4" t="n"/>
+      <c r="Q869" s="5" t="n"/>
+      <c r="R869" s="6" t="n"/>
+      <c r="S869" s="5" t="n"/>
+      <c r="T869" s="6" t="n"/>
+    </row>
+    <row r="870">
+      <c r="H870" s="4" t="n"/>
+      <c r="Q870" s="5" t="n"/>
+      <c r="R870" s="6" t="n"/>
+      <c r="S870" s="5" t="n"/>
+      <c r="T870" s="6" t="n"/>
+    </row>
+    <row r="871">
+      <c r="H871" s="4" t="n"/>
+      <c r="Q871" s="5" t="n"/>
+      <c r="R871" s="6" t="n"/>
+      <c r="S871" s="5" t="n"/>
+      <c r="T871" s="6" t="n"/>
+    </row>
+    <row r="872">
+      <c r="H872" s="4" t="n"/>
+      <c r="Q872" s="5" t="n"/>
+      <c r="R872" s="6" t="n"/>
+      <c r="S872" s="5" t="n"/>
+      <c r="T872" s="6" t="n"/>
+    </row>
+    <row r="873">
+      <c r="H873" s="4" t="n"/>
+      <c r="Q873" s="5" t="n"/>
+      <c r="R873" s="6" t="n"/>
+      <c r="S873" s="5" t="n"/>
+      <c r="T873" s="6" t="n"/>
+    </row>
+    <row r="874">
+      <c r="H874" s="4" t="n"/>
+      <c r="Q874" s="5" t="n"/>
+      <c r="R874" s="6" t="n"/>
+      <c r="S874" s="5" t="n"/>
+      <c r="T874" s="6" t="n"/>
+    </row>
+    <row r="875">
+      <c r="H875" s="4" t="n"/>
+      <c r="Q875" s="5" t="n"/>
+      <c r="R875" s="6" t="n"/>
+      <c r="S875" s="5" t="n"/>
+      <c r="T875" s="6" t="n"/>
+    </row>
+    <row r="876">
+      <c r="H876" s="4" t="n"/>
+      <c r="Q876" s="5" t="n"/>
+      <c r="R876" s="6" t="n"/>
+      <c r="S876" s="5" t="n"/>
+      <c r="T876" s="6" t="n"/>
+    </row>
+    <row r="877">
+      <c r="H877" s="4" t="n"/>
+      <c r="Q877" s="5" t="n"/>
+      <c r="R877" s="6" t="n"/>
+      <c r="S877" s="5" t="n"/>
+      <c r="T877" s="6" t="n"/>
+    </row>
+    <row r="878">
+      <c r="H878" s="4" t="n"/>
+      <c r="Q878" s="5" t="n"/>
+      <c r="R878" s="6" t="n"/>
+      <c r="S878" s="5" t="n"/>
+      <c r="T878" s="6" t="n"/>
+    </row>
+    <row r="879">
+      <c r="H879" s="4" t="n"/>
+      <c r="Q879" s="5" t="n"/>
+      <c r="R879" s="6" t="n"/>
+      <c r="S879" s="5" t="n"/>
+      <c r="T879" s="6" t="n"/>
+    </row>
+    <row r="880">
+      <c r="H880" s="4" t="n"/>
+      <c r="Q880" s="5" t="n"/>
+      <c r="R880" s="6" t="n"/>
+      <c r="S880" s="5" t="n"/>
+      <c r="T880" s="6" t="n"/>
+    </row>
+    <row r="881">
+      <c r="H881" s="4" t="n"/>
+      <c r="Q881" s="5" t="n"/>
+      <c r="R881" s="6" t="n"/>
+      <c r="S881" s="5" t="n"/>
+      <c r="T881" s="6" t="n"/>
+    </row>
+    <row r="882">
+      <c r="H882" s="4" t="n"/>
+      <c r="Q882" s="5" t="n"/>
+      <c r="R882" s="6" t="n"/>
+      <c r="S882" s="5" t="n"/>
+      <c r="T882" s="6" t="n"/>
+    </row>
+    <row r="883">
+      <c r="H883" s="4" t="n"/>
+      <c r="Q883" s="5" t="n"/>
+      <c r="R883" s="6" t="n"/>
+      <c r="S883" s="5" t="n"/>
+      <c r="T883" s="6" t="n"/>
+    </row>
+    <row r="884">
+      <c r="H884" s="4" t="n"/>
+      <c r="Q884" s="5" t="n"/>
+      <c r="R884" s="6" t="n"/>
+      <c r="S884" s="5" t="n"/>
+      <c r="T884" s="6" t="n"/>
+    </row>
+    <row r="885">
+      <c r="H885" s="4" t="n"/>
+      <c r="Q885" s="5" t="n"/>
+      <c r="R885" s="6" t="n"/>
+      <c r="S885" s="5" t="n"/>
+      <c r="T885" s="6" t="n"/>
+    </row>
+    <row r="886">
+      <c r="H886" s="4" t="n"/>
+      <c r="Q886" s="5" t="n"/>
+      <c r="R886" s="6" t="n"/>
+      <c r="S886" s="5" t="n"/>
+      <c r="T886" s="6" t="n"/>
+    </row>
+    <row r="887">
+      <c r="H887" s="4" t="n"/>
+      <c r="Q887" s="5" t="n"/>
+      <c r="R887" s="6" t="n"/>
+      <c r="S887" s="5" t="n"/>
+      <c r="T887" s="6" t="n"/>
+    </row>
+    <row r="888">
+      <c r="H888" s="4" t="n"/>
+      <c r="Q888" s="5" t="n"/>
+      <c r="R888" s="6" t="n"/>
+      <c r="S888" s="5" t="n"/>
+      <c r="T888" s="6" t="n"/>
+    </row>
+    <row r="889">
+      <c r="H889" s="4" t="n"/>
+      <c r="Q889" s="5" t="n"/>
+      <c r="R889" s="6" t="n"/>
+      <c r="S889" s="5" t="n"/>
+      <c r="T889" s="6" t="n"/>
+    </row>
+    <row r="890">
+      <c r="H890" s="4" t="n"/>
+      <c r="Q890" s="5" t="n"/>
+      <c r="R890" s="6" t="n"/>
+      <c r="S890" s="5" t="n"/>
+      <c r="T890" s="6" t="n"/>
+    </row>
+    <row r="891">
+      <c r="H891" s="4" t="n"/>
+      <c r="Q891" s="5" t="n"/>
+      <c r="R891" s="6" t="n"/>
+      <c r="S891" s="5" t="n"/>
+      <c r="T891" s="6" t="n"/>
+    </row>
+    <row r="892">
+      <c r="H892" s="4" t="n"/>
+      <c r="Q892" s="5" t="n"/>
+      <c r="R892" s="6" t="n"/>
+      <c r="S892" s="5" t="n"/>
+      <c r="T892" s="6" t="n"/>
+    </row>
+    <row r="893">
+      <c r="H893" s="4" t="n"/>
+      <c r="Q893" s="5" t="n"/>
+      <c r="R893" s="6" t="n"/>
+      <c r="S893" s="5" t="n"/>
+      <c r="T893" s="6" t="n"/>
+    </row>
+    <row r="894">
+      <c r="H894" s="4" t="n"/>
+      <c r="Q894" s="5" t="n"/>
+      <c r="R894" s="6" t="n"/>
+      <c r="S894" s="5" t="n"/>
+      <c r="T894" s="6" t="n"/>
+    </row>
+    <row r="895">
+      <c r="H895" s="4" t="n"/>
+      <c r="Q895" s="5" t="n"/>
+      <c r="R895" s="6" t="n"/>
+      <c r="S895" s="5" t="n"/>
+      <c r="T895" s="6" t="n"/>
+    </row>
+    <row r="896">
+      <c r="H896" s="4" t="n"/>
+      <c r="Q896" s="5" t="n"/>
+      <c r="R896" s="6" t="n"/>
+      <c r="S896" s="5" t="n"/>
+      <c r="T896" s="6" t="n"/>
+    </row>
+    <row r="897">
+      <c r="H897" s="4" t="n"/>
+      <c r="Q897" s="5" t="n"/>
+      <c r="R897" s="6" t="n"/>
+      <c r="S897" s="5" t="n"/>
+      <c r="T897" s="6" t="n"/>
+    </row>
+    <row r="898">
+      <c r="H898" s="4" t="n"/>
+      <c r="Q898" s="5" t="n"/>
+      <c r="R898" s="6" t="n"/>
+      <c r="S898" s="5" t="n"/>
+      <c r="T898" s="6" t="n"/>
+    </row>
+    <row r="899">
+      <c r="H899" s="4" t="n"/>
+      <c r="Q899" s="5" t="n"/>
+      <c r="R899" s="6" t="n"/>
+      <c r="S899" s="5" t="n"/>
+      <c r="T899" s="6" t="n"/>
+    </row>
+    <row r="900">
+      <c r="H900" s="4" t="n"/>
+      <c r="Q900" s="5" t="n"/>
+      <c r="R900" s="6" t="n"/>
+      <c r="S900" s="5" t="n"/>
+      <c r="T900" s="6" t="n"/>
+    </row>
+    <row r="901">
+      <c r="H901" s="4" t="n"/>
+      <c r="Q901" s="5" t="n"/>
+      <c r="R901" s="6" t="n"/>
+      <c r="S901" s="5" t="n"/>
+      <c r="T901" s="6" t="n"/>
+    </row>
+    <row r="902">
+      <c r="H902" s="4" t="n"/>
+      <c r="Q902" s="5" t="n"/>
+      <c r="R902" s="6" t="n"/>
+      <c r="S902" s="5" t="n"/>
+      <c r="T902" s="6" t="n"/>
+    </row>
+    <row r="903">
+      <c r="H903" s="4" t="n"/>
+      <c r="Q903" s="5" t="n"/>
+      <c r="R903" s="6" t="n"/>
+      <c r="S903" s="5" t="n"/>
+      <c r="T903" s="6" t="n"/>
+    </row>
+    <row r="904">
+      <c r="H904" s="4" t="n"/>
+      <c r="Q904" s="5" t="n"/>
+      <c r="R904" s="6" t="n"/>
+      <c r="S904" s="5" t="n"/>
+      <c r="T904" s="6" t="n"/>
+    </row>
+    <row r="905">
+      <c r="H905" s="4" t="n"/>
+      <c r="Q905" s="5" t="n"/>
+      <c r="R905" s="6" t="n"/>
+      <c r="S905" s="5" t="n"/>
+      <c r="T905" s="6" t="n"/>
+    </row>
+    <row r="906">
+      <c r="H906" s="4" t="n"/>
+      <c r="Q906" s="5" t="n"/>
+      <c r="R906" s="6" t="n"/>
+      <c r="S906" s="5" t="n"/>
+      <c r="T906" s="6" t="n"/>
+    </row>
+    <row r="907">
+      <c r="H907" s="4" t="n"/>
+      <c r="Q907" s="5" t="n"/>
+      <c r="R907" s="6" t="n"/>
+      <c r="S907" s="5" t="n"/>
+      <c r="T907" s="6" t="n"/>
+    </row>
+    <row r="908">
+      <c r="H908" s="4" t="n"/>
+      <c r="Q908" s="5" t="n"/>
+      <c r="R908" s="6" t="n"/>
+      <c r="S908" s="5" t="n"/>
+      <c r="T908" s="6" t="n"/>
+    </row>
+    <row r="909">
+      <c r="H909" s="4" t="n"/>
+      <c r="Q909" s="5" t="n"/>
+      <c r="R909" s="6" t="n"/>
+      <c r="S909" s="5" t="n"/>
+      <c r="T909" s="6" t="n"/>
+    </row>
+    <row r="910">
+      <c r="H910" s="4" t="n"/>
+      <c r="Q910" s="5" t="n"/>
+      <c r="R910" s="6" t="n"/>
+      <c r="S910" s="5" t="n"/>
+      <c r="T910" s="6" t="n"/>
+    </row>
+    <row r="911">
+      <c r="H911" s="4" t="n"/>
+      <c r="Q911" s="5" t="n"/>
+      <c r="R911" s="6" t="n"/>
+      <c r="S911" s="5" t="n"/>
+      <c r="T911" s="6" t="n"/>
+    </row>
+    <row r="912">
+      <c r="H912" s="4" t="n"/>
+      <c r="Q912" s="5" t="n"/>
+      <c r="R912" s="6" t="n"/>
+      <c r="S912" s="5" t="n"/>
+      <c r="T912" s="6" t="n"/>
+    </row>
+    <row r="913">
+      <c r="H913" s="4" t="n"/>
+      <c r="Q913" s="5" t="n"/>
+      <c r="R913" s="6" t="n"/>
+      <c r="S913" s="5" t="n"/>
+      <c r="T913" s="6" t="n"/>
+    </row>
+    <row r="914">
+      <c r="H914" s="4" t="n"/>
+      <c r="Q914" s="5" t="n"/>
+      <c r="R914" s="6" t="n"/>
+      <c r="S914" s="5" t="n"/>
+      <c r="T914" s="6" t="n"/>
+    </row>
+    <row r="915">
+      <c r="H915" s="4" t="n"/>
+      <c r="Q915" s="5" t="n"/>
+      <c r="R915" s="6" t="n"/>
+      <c r="S915" s="5" t="n"/>
+      <c r="T915" s="6" t="n"/>
+    </row>
+    <row r="916">
+      <c r="H916" s="4" t="n"/>
+      <c r="Q916" s="5" t="n"/>
+      <c r="R916" s="6" t="n"/>
+      <c r="S916" s="5" t="n"/>
+      <c r="T916" s="6" t="n"/>
+    </row>
+    <row r="917">
+      <c r="H917" s="4" t="n"/>
+      <c r="Q917" s="5" t="n"/>
+      <c r="R917" s="6" t="n"/>
+      <c r="S917" s="5" t="n"/>
+      <c r="T917" s="6" t="n"/>
+    </row>
+    <row r="918">
+      <c r="H918" s="4" t="n"/>
+      <c r="Q918" s="5" t="n"/>
+      <c r="R918" s="6" t="n"/>
+      <c r="S918" s="5" t="n"/>
+      <c r="T918" s="6" t="n"/>
+    </row>
+    <row r="919">
+      <c r="H919" s="4" t="n"/>
+      <c r="Q919" s="5" t="n"/>
+      <c r="R919" s="6" t="n"/>
+      <c r="S919" s="5" t="n"/>
+      <c r="T919" s="6" t="n"/>
+    </row>
+    <row r="920">
+      <c r="H920" s="4" t="n"/>
+      <c r="Q920" s="5" t="n"/>
+      <c r="R920" s="6" t="n"/>
+      <c r="S920" s="5" t="n"/>
+      <c r="T920" s="6" t="n"/>
+    </row>
+    <row r="921">
+      <c r="H921" s="4" t="n"/>
+      <c r="Q921" s="5" t="n"/>
+      <c r="R921" s="6" t="n"/>
+      <c r="S921" s="5" t="n"/>
+      <c r="T921" s="6" t="n"/>
+    </row>
+    <row r="922">
+      <c r="H922" s="4" t="n"/>
+      <c r="Q922" s="5" t="n"/>
+      <c r="R922" s="6" t="n"/>
+      <c r="S922" s="5" t="n"/>
+      <c r="T922" s="6" t="n"/>
+    </row>
+    <row r="923">
+      <c r="H923" s="4" t="n"/>
+      <c r="Q923" s="5" t="n"/>
+      <c r="R923" s="6" t="n"/>
+      <c r="S923" s="5" t="n"/>
+      <c r="T923" s="6" t="n"/>
+    </row>
+    <row r="924">
+      <c r="H924" s="4" t="n"/>
+      <c r="Q924" s="5" t="n"/>
+      <c r="R924" s="6" t="n"/>
+      <c r="S924" s="5" t="n"/>
+      <c r="T924" s="6" t="n"/>
+    </row>
+    <row r="925">
+      <c r="H925" s="4" t="n"/>
+      <c r="Q925" s="5" t="n"/>
+      <c r="R925" s="6" t="n"/>
+      <c r="S925" s="5" t="n"/>
+      <c r="T925" s="6" t="n"/>
+    </row>
+    <row r="926">
+      <c r="H926" s="4" t="n"/>
+      <c r="Q926" s="5" t="n"/>
+      <c r="R926" s="6" t="n"/>
+      <c r="S926" s="5" t="n"/>
+      <c r="T926" s="6" t="n"/>
+    </row>
+    <row r="927">
+      <c r="H927" s="4" t="n"/>
+      <c r="Q927" s="5" t="n"/>
+      <c r="R927" s="6" t="n"/>
+      <c r="S927" s="5" t="n"/>
+      <c r="T927" s="6" t="n"/>
+    </row>
+    <row r="928">
+      <c r="H928" s="4" t="n"/>
+      <c r="Q928" s="5" t="n"/>
+      <c r="R928" s="6" t="n"/>
+      <c r="S928" s="5" t="n"/>
+      <c r="T928" s="6" t="n"/>
+    </row>
+    <row r="929">
+      <c r="H929" s="4" t="n"/>
+      <c r="Q929" s="5" t="n"/>
+      <c r="R929" s="6" t="n"/>
+      <c r="S929" s="5" t="n"/>
+      <c r="T929" s="6" t="n"/>
+    </row>
+    <row r="930">
+      <c r="H930" s="4" t="n"/>
+      <c r="Q930" s="5" t="n"/>
+      <c r="R930" s="6" t="n"/>
+      <c r="S930" s="5" t="n"/>
+      <c r="T930" s="6" t="n"/>
+    </row>
+    <row r="931">
+      <c r="H931" s="4" t="n"/>
+      <c r="Q931" s="5" t="n"/>
+      <c r="R931" s="6" t="n"/>
+      <c r="S931" s="5" t="n"/>
+      <c r="T931" s="6" t="n"/>
+    </row>
+    <row r="932">
+      <c r="H932" s="4" t="n"/>
+      <c r="Q932" s="5" t="n"/>
+      <c r="R932" s="6" t="n"/>
+      <c r="S932" s="5" t="n"/>
+      <c r="T932" s="6" t="n"/>
+    </row>
+    <row r="933">
+      <c r="H933" s="4" t="n"/>
+      <c r="Q933" s="5" t="n"/>
+      <c r="R933" s="6" t="n"/>
+      <c r="S933" s="5" t="n"/>
+      <c r="T933" s="6" t="n"/>
+    </row>
+    <row r="934">
+      <c r="H934" s="4" t="n"/>
+      <c r="Q934" s="5" t="n"/>
+      <c r="R934" s="6" t="n"/>
+      <c r="S934" s="5" t="n"/>
+      <c r="T934" s="6" t="n"/>
+    </row>
+    <row r="935">
+      <c r="H935" s="4" t="n"/>
+      <c r="Q935" s="5" t="n"/>
+      <c r="R935" s="6" t="n"/>
+      <c r="S935" s="5" t="n"/>
+      <c r="T935" s="6" t="n"/>
+    </row>
+    <row r="936">
+      <c r="H936" s="4" t="n"/>
+      <c r="Q936" s="5" t="n"/>
+      <c r="R936" s="6" t="n"/>
+      <c r="S936" s="5" t="n"/>
+      <c r="T936" s="6" t="n"/>
+    </row>
+    <row r="937">
+      <c r="H937" s="4" t="n"/>
+      <c r="Q937" s="5" t="n"/>
+      <c r="R937" s="6" t="n"/>
+      <c r="S937" s="5" t="n"/>
+      <c r="T937" s="6" t="n"/>
+    </row>
+    <row r="938">
+      <c r="H938" s="4" t="n"/>
+      <c r="Q938" s="5" t="n"/>
+      <c r="R938" s="6" t="n"/>
+      <c r="S938" s="5" t="n"/>
+      <c r="T938" s="6" t="n"/>
+    </row>
+    <row r="939">
+      <c r="H939" s="4" t="n"/>
+      <c r="Q939" s="5" t="n"/>
+      <c r="R939" s="6" t="n"/>
+      <c r="S939" s="5" t="n"/>
+      <c r="T939" s="6" t="n"/>
+    </row>
+    <row r="940">
+      <c r="H940" s="4" t="n"/>
+      <c r="Q940" s="5" t="n"/>
+      <c r="R940" s="6" t="n"/>
+      <c r="S940" s="5" t="n"/>
+      <c r="T940" s="6" t="n"/>
+    </row>
+    <row r="941">
+      <c r="H941" s="4" t="n"/>
+      <c r="Q941" s="5" t="n"/>
+      <c r="R941" s="6" t="n"/>
+      <c r="S941" s="5" t="n"/>
+      <c r="T941" s="6" t="n"/>
+    </row>
+    <row r="942">
+      <c r="H942" s="4" t="n"/>
+      <c r="Q942" s="5" t="n"/>
+      <c r="R942" s="6" t="n"/>
+      <c r="S942" s="5" t="n"/>
+      <c r="T942" s="6" t="n"/>
+    </row>
+    <row r="943">
+      <c r="H943" s="4" t="n"/>
+      <c r="Q943" s="5" t="n"/>
+      <c r="R943" s="6" t="n"/>
+      <c r="S943" s="5" t="n"/>
+      <c r="T943" s="6" t="n"/>
+    </row>
+    <row r="944">
+      <c r="H944" s="4" t="n"/>
+      <c r="Q944" s="5" t="n"/>
+      <c r="R944" s="6" t="n"/>
+      <c r="S944" s="5" t="n"/>
+      <c r="T944" s="6" t="n"/>
+    </row>
+    <row r="945">
+      <c r="H945" s="4" t="n"/>
+      <c r="Q945" s="5" t="n"/>
+      <c r="R945" s="6" t="n"/>
+      <c r="S945" s="5" t="n"/>
+      <c r="T945" s="6" t="n"/>
+    </row>
+    <row r="946">
+      <c r="H946" s="4" t="n"/>
+      <c r="Q946" s="5" t="n"/>
+      <c r="R946" s="6" t="n"/>
+      <c r="S946" s="5" t="n"/>
+      <c r="T946" s="6" t="n"/>
+    </row>
+    <row r="947">
+      <c r="H947" s="4" t="n"/>
+      <c r="Q947" s="5" t="n"/>
+      <c r="R947" s="6" t="n"/>
+      <c r="S947" s="5" t="n"/>
+      <c r="T947" s="6" t="n"/>
+    </row>
+    <row r="948">
+      <c r="H948" s="4" t="n"/>
+      <c r="Q948" s="5" t="n"/>
+      <c r="R948" s="6" t="n"/>
+      <c r="S948" s="5" t="n"/>
+      <c r="T948" s="6" t="n"/>
+    </row>
+    <row r="949">
+      <c r="H949" s="4" t="n"/>
+      <c r="Q949" s="5" t="n"/>
+      <c r="R949" s="6" t="n"/>
+      <c r="S949" s="5" t="n"/>
+      <c r="T949" s="6" t="n"/>
+    </row>
+    <row r="950">
+      <c r="H950" s="4" t="n"/>
+      <c r="Q950" s="5" t="n"/>
+      <c r="R950" s="6" t="n"/>
+      <c r="S950" s="5" t="n"/>
+      <c r="T950" s="6" t="n"/>
+    </row>
+    <row r="951">
+      <c r="H951" s="4" t="n"/>
+      <c r="Q951" s="5" t="n"/>
+      <c r="R951" s="6" t="n"/>
+      <c r="S951" s="5" t="n"/>
+      <c r="T951" s="6" t="n"/>
+    </row>
+    <row r="952">
+      <c r="H952" s="4" t="n"/>
+      <c r="Q952" s="5" t="n"/>
+      <c r="R952" s="6" t="n"/>
+      <c r="S952" s="5" t="n"/>
+      <c r="T952" s="6" t="n"/>
+    </row>
+    <row r="953">
+      <c r="H953" s="4" t="n"/>
+      <c r="Q953" s="5" t="n"/>
+      <c r="R953" s="6" t="n"/>
+      <c r="S953" s="5" t="n"/>
+      <c r="T953" s="6" t="n"/>
+    </row>
+    <row r="954">
+      <c r="H954" s="4" t="n"/>
+      <c r="Q954" s="5" t="n"/>
+      <c r="R954" s="6" t="n"/>
+      <c r="S954" s="5" t="n"/>
+      <c r="T954" s="6" t="n"/>
+    </row>
+    <row r="955">
+      <c r="H955" s="4" t="n"/>
+      <c r="Q955" s="5" t="n"/>
+      <c r="R955" s="6" t="n"/>
+      <c r="S955" s="5" t="n"/>
+      <c r="T955" s="6" t="n"/>
+    </row>
+    <row r="956">
+      <c r="H956" s="4" t="n"/>
+      <c r="Q956" s="5" t="n"/>
+      <c r="R956" s="6" t="n"/>
+      <c r="S956" s="5" t="n"/>
+      <c r="T956" s="6" t="n"/>
+    </row>
+    <row r="957">
+      <c r="H957" s="4" t="n"/>
+      <c r="Q957" s="5" t="n"/>
+      <c r="R957" s="6" t="n"/>
+      <c r="S957" s="5" t="n"/>
+      <c r="T957" s="6" t="n"/>
+    </row>
+    <row r="958">
+      <c r="H958" s="4" t="n"/>
+      <c r="Q958" s="5" t="n"/>
+      <c r="R958" s="6" t="n"/>
+      <c r="S958" s="5" t="n"/>
+      <c r="T958" s="6" t="n"/>
+    </row>
+    <row r="959">
+      <c r="H959" s="4" t="n"/>
+      <c r="Q959" s="5" t="n"/>
+      <c r="R959" s="6" t="n"/>
+      <c r="S959" s="5" t="n"/>
+      <c r="T959" s="6" t="n"/>
+    </row>
+    <row r="960">
+      <c r="H960" s="4" t="n"/>
+      <c r="Q960" s="5" t="n"/>
+      <c r="R960" s="6" t="n"/>
+      <c r="S960" s="5" t="n"/>
+      <c r="T960" s="6" t="n"/>
+    </row>
+    <row r="961">
+      <c r="H961" s="4" t="n"/>
+      <c r="Q961" s="5" t="n"/>
+      <c r="R961" s="6" t="n"/>
+      <c r="S961" s="5" t="n"/>
+      <c r="T961" s="6" t="n"/>
+    </row>
+    <row r="962">
+      <c r="H962" s="4" t="n"/>
+      <c r="Q962" s="5" t="n"/>
+      <c r="R962" s="6" t="n"/>
+      <c r="S962" s="5" t="n"/>
+      <c r="T962" s="6" t="n"/>
+    </row>
+    <row r="963">
+      <c r="H963" s="4" t="n"/>
+      <c r="Q963" s="5" t="n"/>
+      <c r="R963" s="6" t="n"/>
+      <c r="S963" s="5" t="n"/>
+      <c r="T963" s="6" t="n"/>
+    </row>
+    <row r="964">
+      <c r="H964" s="4" t="n"/>
+      <c r="Q964" s="5" t="n"/>
+      <c r="R964" s="6" t="n"/>
+      <c r="S964" s="5" t="n"/>
+      <c r="T964" s="6" t="n"/>
+    </row>
+    <row r="965">
+      <c r="H965" s="4" t="n"/>
+      <c r="Q965" s="5" t="n"/>
+      <c r="R965" s="6" t="n"/>
+      <c r="S965" s="5" t="n"/>
+      <c r="T965" s="6" t="n"/>
+    </row>
+    <row r="966">
+      <c r="H966" s="4" t="n"/>
+      <c r="Q966" s="5" t="n"/>
+      <c r="R966" s="6" t="n"/>
+      <c r="S966" s="5" t="n"/>
+      <c r="T966" s="6" t="n"/>
+    </row>
+    <row r="967">
+      <c r="H967" s="4" t="n"/>
+      <c r="Q967" s="5" t="n"/>
+      <c r="R967" s="6" t="n"/>
+      <c r="S967" s="5" t="n"/>
+      <c r="T967" s="6" t="n"/>
+    </row>
+    <row r="968">
+      <c r="H968" s="4" t="n"/>
+      <c r="Q968" s="5" t="n"/>
+      <c r="R968" s="6" t="n"/>
+      <c r="S968" s="5" t="n"/>
+      <c r="T968" s="6" t="n"/>
+    </row>
+    <row r="969">
+      <c r="H969" s="4" t="n"/>
+      <c r="Q969" s="5" t="n"/>
+      <c r="R969" s="6" t="n"/>
+      <c r="S969" s="5" t="n"/>
+      <c r="T969" s="6" t="n"/>
+    </row>
+    <row r="970">
+      <c r="H970" s="4" t="n"/>
+      <c r="Q970" s="5" t="n"/>
+      <c r="R970" s="6" t="n"/>
+      <c r="S970" s="5" t="n"/>
+      <c r="T970" s="6" t="n"/>
+    </row>
+    <row r="971">
+      <c r="H971" s="4" t="n"/>
+      <c r="Q971" s="5" t="n"/>
+      <c r="R971" s="6" t="n"/>
+      <c r="S971" s="5" t="n"/>
+      <c r="T971" s="6" t="n"/>
+    </row>
+    <row r="972">
+      <c r="H972" s="4" t="n"/>
+      <c r="Q972" s="5" t="n"/>
+      <c r="R972" s="6" t="n"/>
+      <c r="S972" s="5" t="n"/>
+      <c r="T972" s="6" t="n"/>
+    </row>
+    <row r="973">
+      <c r="H973" s="4" t="n"/>
+      <c r="Q973" s="5" t="n"/>
+      <c r="R973" s="6" t="n"/>
+      <c r="S973" s="5" t="n"/>
+      <c r="T973" s="6" t="n"/>
+    </row>
+    <row r="974">
+      <c r="H974" s="4" t="n"/>
+      <c r="Q974" s="5" t="n"/>
+      <c r="R974" s="6" t="n"/>
+      <c r="S974" s="5" t="n"/>
+      <c r="T974" s="6" t="n"/>
+    </row>
+    <row r="975">
+      <c r="H975" s="4" t="n"/>
+      <c r="Q975" s="5" t="n"/>
+      <c r="R975" s="6" t="n"/>
+      <c r="S975" s="5" t="n"/>
+      <c r="T975" s="6" t="n"/>
+    </row>
+    <row r="976">
+      <c r="H976" s="4" t="n"/>
+      <c r="Q976" s="5" t="n"/>
+      <c r="R976" s="6" t="n"/>
+      <c r="S976" s="5" t="n"/>
+      <c r="T976" s="6" t="n"/>
+    </row>
+    <row r="977">
+      <c r="H977" s="4" t="n"/>
+      <c r="Q977" s="5" t="n"/>
+      <c r="R977" s="6" t="n"/>
+      <c r="S977" s="5" t="n"/>
+      <c r="T977" s="6" t="n"/>
+    </row>
+    <row r="978">
+      <c r="H978" s="4" t="n"/>
+      <c r="Q978" s="5" t="n"/>
+      <c r="R978" s="6" t="n"/>
+      <c r="S978" s="5" t="n"/>
+      <c r="T978" s="6" t="n"/>
+    </row>
+    <row r="979">
+      <c r="H979" s="4" t="n"/>
+      <c r="Q979" s="5" t="n"/>
+      <c r="R979" s="6" t="n"/>
+      <c r="S979" s="5" t="n"/>
+      <c r="T979" s="6" t="n"/>
+    </row>
+    <row r="980">
+      <c r="H980" s="4" t="n"/>
+      <c r="Q980" s="5" t="n"/>
+      <c r="R980" s="6" t="n"/>
+      <c r="S980" s="5" t="n"/>
+      <c r="T980" s="6" t="n"/>
+    </row>
+    <row r="981">
+      <c r="H981" s="4" t="n"/>
+      <c r="Q981" s="5" t="n"/>
+      <c r="R981" s="6" t="n"/>
+      <c r="S981" s="5" t="n"/>
+      <c r="T981" s="6" t="n"/>
+    </row>
+    <row r="982">
+      <c r="H982" s="4" t="n"/>
+      <c r="Q982" s="5" t="n"/>
+      <c r="R982" s="6" t="n"/>
+      <c r="S982" s="5" t="n"/>
+      <c r="T982" s="6" t="n"/>
+    </row>
+    <row r="983">
+      <c r="H983" s="4" t="n"/>
+      <c r="Q983" s="5" t="n"/>
+      <c r="R983" s="6" t="n"/>
+      <c r="S983" s="5" t="n"/>
+      <c r="T983" s="6" t="n"/>
+    </row>
+    <row r="984">
+      <c r="H984" s="4" t="n"/>
+      <c r="Q984" s="5" t="n"/>
+      <c r="R984" s="6" t="n"/>
+      <c r="S984" s="5" t="n"/>
+      <c r="T984" s="6" t="n"/>
+    </row>
+    <row r="985">
+      <c r="H985" s="4" t="n"/>
+      <c r="Q985" s="5" t="n"/>
+      <c r="R985" s="6" t="n"/>
+      <c r="S985" s="5" t="n"/>
+      <c r="T985" s="6" t="n"/>
+    </row>
+    <row r="986">
+      <c r="H986" s="4" t="n"/>
+      <c r="Q986" s="5" t="n"/>
+      <c r="R986" s="6" t="n"/>
+      <c r="S986" s="5" t="n"/>
+      <c r="T986" s="6" t="n"/>
+    </row>
+    <row r="987">
+      <c r="H987" s="4" t="n"/>
+      <c r="Q987" s="5" t="n"/>
+      <c r="R987" s="6" t="n"/>
+      <c r="S987" s="5" t="n"/>
+      <c r="T987" s="6" t="n"/>
+    </row>
+    <row r="988">
+      <c r="H988" s="4" t="n"/>
+      <c r="Q988" s="5" t="n"/>
+      <c r="R988" s="6" t="n"/>
+      <c r="S988" s="5" t="n"/>
+      <c r="T988" s="6" t="n"/>
+    </row>
+    <row r="989">
+      <c r="H989" s="4" t="n"/>
+      <c r="Q989" s="5" t="n"/>
+      <c r="R989" s="6" t="n"/>
+      <c r="S989" s="5" t="n"/>
+      <c r="T989" s="6" t="n"/>
+    </row>
+    <row r="990">
+      <c r="H990" s="4" t="n"/>
+      <c r="Q990" s="5" t="n"/>
+      <c r="R990" s="6" t="n"/>
+      <c r="S990" s="5" t="n"/>
+      <c r="T990" s="6" t="n"/>
+    </row>
+    <row r="991">
+      <c r="H991" s="4" t="n"/>
+      <c r="Q991" s="5" t="n"/>
+      <c r="R991" s="6" t="n"/>
+      <c r="S991" s="5" t="n"/>
+      <c r="T991" s="6" t="n"/>
+    </row>
+    <row r="992">
+      <c r="H992" s="4" t="n"/>
+      <c r="Q992" s="5" t="n"/>
+      <c r="R992" s="6" t="n"/>
+      <c r="S992" s="5" t="n"/>
+      <c r="T992" s="6" t="n"/>
+    </row>
+    <row r="993">
+      <c r="H993" s="4" t="n"/>
+      <c r="Q993" s="5" t="n"/>
+      <c r="R993" s="6" t="n"/>
+      <c r="S993" s="5" t="n"/>
+      <c r="T993" s="6" t="n"/>
+    </row>
+    <row r="994">
+      <c r="H994" s="4" t="n"/>
+      <c r="Q994" s="5" t="n"/>
+      <c r="R994" s="6" t="n"/>
+      <c r="S994" s="5" t="n"/>
+      <c r="T994" s="6" t="n"/>
+    </row>
+    <row r="995">
+      <c r="H995" s="4" t="n"/>
+      <c r="Q995" s="5" t="n"/>
+      <c r="R995" s="6" t="n"/>
+      <c r="S995" s="5" t="n"/>
+      <c r="T995" s="6" t="n"/>
+    </row>
+    <row r="996">
+      <c r="H996" s="4" t="n"/>
+      <c r="Q996" s="5" t="n"/>
+      <c r="R996" s="6" t="n"/>
+      <c r="S996" s="5" t="n"/>
+      <c r="T996" s="6" t="n"/>
+    </row>
+    <row r="997">
+      <c r="H997" s="4" t="n"/>
+      <c r="Q997" s="5" t="n"/>
+      <c r="R997" s="6" t="n"/>
+      <c r="S997" s="5" t="n"/>
+      <c r="T997" s="6" t="n"/>
+    </row>
+    <row r="998">
+      <c r="H998" s="4" t="n"/>
+      <c r="Q998" s="5" t="n"/>
+      <c r="R998" s="6" t="n"/>
+      <c r="S998" s="5" t="n"/>
+      <c r="T998" s="6" t="n"/>
+    </row>
+    <row r="999">
+      <c r="H999" s="4" t="n"/>
+      <c r="Q999" s="5" t="n"/>
+      <c r="R999" s="6" t="n"/>
+      <c r="S999" s="5" t="n"/>
+      <c r="T999" s="6" t="n"/>
+    </row>
+    <row r="1000">
+      <c r="H1000" s="4" t="n"/>
+      <c r="Q1000" s="5" t="n"/>
+      <c r="R1000" s="6" t="n"/>
+      <c r="S1000" s="5" t="n"/>
+      <c r="T1000" s="6" t="n"/>
+    </row>
+    <row r="1001">
+      <c r="H1001" s="4" t="n"/>
+      <c r="Q1001" s="5" t="n"/>
+      <c r="R1001" s="6" t="n"/>
+      <c r="S1001" s="5" t="n"/>
+      <c r="T1001" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:T1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>property_id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>district_name</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>station_name</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>station_line</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>station_latitude</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>station_longitude</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>area_m2</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>floor_plan</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>building_age</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>renovation</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>city_planning</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>floor_area_ratio</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>listing_date</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>asking_price</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>contract_date</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>contract_price</t>
         </is>
@@ -544,61 +7738,550 @@
           <t>千住</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>北千住</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>65.2</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>3LDK</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="J2" t="n">
         <v>12</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>未改装</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>住宅</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>商業地域</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="O2" t="n">
         <v>80</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>400</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>45000000</v>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="P2" t="n">
-        <v>42000000</v>
+      <c r="T2" t="n">
+        <v>72000000</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:T2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>項目名</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>入力区分</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>入力例</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>property_id</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>物件を識別するID</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>東京都の市区町村</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>足立区</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>district_name</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>町・地区名</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>千住</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>station_name</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>最寄駅名。入力されている場合はこの駅を優先</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>北千住</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>station_line</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>路線名。空欄の場合は駅情報から補完可能</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>常磐線</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>station_latitude</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>駅緯度。空欄の場合は駅情報から補完可能</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>35.749</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>station_longitude</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>駅経度。空欄の場合は駅情報から補完可能</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>139.805</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>area_m2</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>専有面積（㎡）</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>65.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>floor_plan</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>間取り</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3LDK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>building_age</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>売出時点の築年数</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>structure</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>建物構造</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>renovation</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>リフォーム・改装状況</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>未改装</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>use</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>物件用途</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>住宅</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>city_planning</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>都市計画・用途地域</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>商業地域</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>建ぺい率（%）</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>floor_area_ratio</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>容積率（%）</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>listing_date</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>販売を開始した日</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>asking_price</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>販売開始時点の売出価格（円）</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>75000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>contract_date</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>成約した日</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>contract_price</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>推奨</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>実際の成約価格（円）。評価・確認用</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>72000000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>